--- a/artfynd/A 5791-2026 artfynd.xlsx
+++ b/artfynd/A 5791-2026 artfynd.xlsx
@@ -6219,7 +6219,7 @@
         <v>129430383</v>
       </c>
       <c r="B44" t="n">
-        <v>57740</v>
+        <v>57898</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 5791-2026 artfynd.xlsx
+++ b/artfynd/A 5791-2026 artfynd.xlsx
@@ -6219,7 +6219,7 @@
         <v>129430383</v>
       </c>
       <c r="B44" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 5791-2026 artfynd.xlsx
+++ b/artfynd/A 5791-2026 artfynd.xlsx
@@ -6219,7 +6219,7 @@
         <v>129430383</v>
       </c>
       <c r="B44" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 5791-2026 artfynd.xlsx
+++ b/artfynd/A 5791-2026 artfynd.xlsx
@@ -6219,7 +6219,7 @@
         <v>129430383</v>
       </c>
       <c r="B44" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 5791-2026 artfynd.xlsx
+++ b/artfynd/A 5791-2026 artfynd.xlsx
@@ -6219,7 +6219,7 @@
         <v>129430383</v>
       </c>
       <c r="B44" t="n">
-        <v>57904</v>
+        <v>57905</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 5791-2026 artfynd.xlsx
+++ b/artfynd/A 5791-2026 artfynd.xlsx
@@ -6219,7 +6219,7 @@
         <v>129430383</v>
       </c>
       <c r="B44" t="n">
-        <v>57905</v>
+        <v>57907</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 5791-2026 artfynd.xlsx
+++ b/artfynd/A 5791-2026 artfynd.xlsx
@@ -6219,7 +6219,7 @@
         <v>129430383</v>
       </c>
       <c r="B44" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 5791-2026 artfynd.xlsx
+++ b/artfynd/A 5791-2026 artfynd.xlsx
@@ -6219,7 +6219,7 @@
         <v>129430383</v>
       </c>
       <c r="B44" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 5791-2026 artfynd.xlsx
+++ b/artfynd/A 5791-2026 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>122361219</v>
       </c>
       <c r="B2" t="n">
-        <v>79742</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -812,65 +807,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122364212</v>
+        <v>122355540</v>
       </c>
       <c r="B3" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494582</v>
+        <v>494535</v>
       </c>
       <c r="R3" t="n">
-        <v>7006726</v>
+        <v>7006574</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -902,11 +880,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska ringhack några meter upp på en granstam.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -921,11 +894,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Grandominerad skog men inslag av tall, björk, sälg och asp. Här finns gott om stående och liggande död ved.</t>
-        </is>
-      </c>
       <c r="AJ3" t="inlineStr">
         <is>
           <t>gran</t>
@@ -938,12 +906,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -961,65 +929,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122364729</v>
+        <v>122355933</v>
       </c>
       <c r="B4" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494499</v>
+        <v>494462</v>
       </c>
       <c r="R4" t="n">
-        <v>7006492</v>
+        <v>7006583</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1051,11 +1002,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska inhack vid ca 2 meters höjd upp på en granstam.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1070,11 +1016,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
-        </is>
-      </c>
       <c r="AJ4" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1087,12 +1028,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1110,19 +1051,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122355933</v>
+        <v>122358929</v>
       </c>
       <c r="B5" t="n">
-        <v>78660</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1150,13 +1086,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494462</v>
+        <v>494550</v>
       </c>
       <c r="R5" t="n">
-        <v>7006583</v>
+        <v>7006504</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1237,63 +1173,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122359111</v>
+        <v>122359011</v>
       </c>
       <c r="B6" t="n">
-        <v>57400</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494496</v>
+        <v>494502</v>
       </c>
       <c r="R6" t="n">
-        <v>7006482</v>
+        <v>7006489</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1325,11 +1246,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska hackspår/födosökspår i stående död tall.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1346,22 +1262,22 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1379,60 +1295,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122357658</v>
+        <v>122359691</v>
       </c>
       <c r="B7" t="n">
-        <v>57400</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494515</v>
+        <v>494410</v>
       </c>
       <c r="R7" t="n">
-        <v>7006545</v>
+        <v>7006434</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1467,11 +1368,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska hackspår och födosökspår med avskalad bark.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1498,12 +1394,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1521,55 +1417,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122360500</v>
+        <v>122360218</v>
       </c>
       <c r="B8" t="n">
-        <v>79777</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494402</v>
+        <v>494394</v>
       </c>
       <c r="R8" t="n">
-        <v>7006360</v>
+        <v>7006412</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1620,22 +1506,22 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1653,19 +1539,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122360218</v>
+        <v>122361005</v>
       </c>
       <c r="B9" t="n">
-        <v>78660</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1693,13 +1574,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494394</v>
+        <v>494444</v>
       </c>
       <c r="R9" t="n">
-        <v>7006412</v>
+        <v>7006335</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1780,63 +1661,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122355606</v>
+        <v>122361037</v>
       </c>
       <c r="B10" t="n">
-        <v>57400</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494524</v>
+        <v>494456</v>
       </c>
       <c r="R10" t="n">
-        <v>7006571</v>
+        <v>7006360</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1868,11 +1734,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska hackspår/födosökspår.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1899,12 +1760,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1922,63 +1783,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122355822</v>
+        <v>122361274</v>
       </c>
       <c r="B11" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494487</v>
+        <v>494472</v>
       </c>
       <c r="R11" t="n">
-        <v>7006560</v>
+        <v>7006382</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2012,7 +1858,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>På flera granar. Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2041,12 +1887,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2064,65 +1910,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122364537</v>
+        <v>122406516</v>
       </c>
       <c r="B12" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynjeflon, Kyrkås, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494454</v>
+        <v>494604</v>
       </c>
       <c r="R12" t="n">
-        <v>7006579</v>
+        <v>7006665</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2146,17 +1975,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack några meter upp på en granstam med kådaflöden.</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2173,11 +1997,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
-        </is>
-      </c>
       <c r="AJ12" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2190,12 +2009,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2213,19 +2032,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122359011</v>
+        <v>122406983</v>
       </c>
       <c r="B13" t="n">
-        <v>78660</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -2249,14 +2063,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494502</v>
+        <v>494621</v>
       </c>
       <c r="R13" t="n">
-        <v>7006489</v>
+        <v>7006636</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2283,12 +2097,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2340,53 +2154,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122360161</v>
+        <v>122407975</v>
       </c>
       <c r="B14" t="n">
-        <v>79741</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494380</v>
+        <v>494572</v>
       </c>
       <c r="R14" t="n">
-        <v>7006419</v>
+        <v>7006632</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2410,17 +2219,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2439,22 +2243,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2472,15 +2276,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122361274</v>
+        <v>122360161</v>
       </c>
       <c r="B15" t="n">
-        <v>78660</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2488,21 +2287,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2512,13 +2311,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494472</v>
+        <v>494380</v>
       </c>
       <c r="R15" t="n">
-        <v>7006382</v>
+        <v>7006419</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2552,7 +2351,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På flera granar. Långväxta bålar.</t>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2571,22 +2370,22 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2604,15 +2403,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122357863</v>
+        <v>122360599</v>
       </c>
       <c r="B16" t="n">
-        <v>57537</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2620,48 +2414,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494497</v>
+        <v>494411</v>
       </c>
       <c r="R16" t="n">
-        <v>7006523</v>
+        <v>7006366</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2696,6 +2476,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Enstaka bålar.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2708,6 +2493,26 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2725,15 +2530,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122357683</v>
+        <v>122361119</v>
       </c>
       <c r="B17" t="n">
-        <v>90855</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2741,27 +2541,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2770,13 +2570,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494501</v>
+        <v>494460</v>
       </c>
       <c r="R17" t="n">
-        <v>7006553</v>
+        <v>7006357</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2808,6 +2608,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ymnig påväxt av lunglav på en gammal grov skadad sälg.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2824,22 +2629,22 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2857,53 +2662,53 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122361037</v>
+        <v>122360113</v>
       </c>
       <c r="B18" t="n">
-        <v>78660</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494456</v>
+        <v>494392</v>
       </c>
       <c r="R18" t="n">
-        <v>7006360</v>
+        <v>7006448</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2951,22 +2756,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2984,50 +2789,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122361005</v>
+        <v>122360490</v>
       </c>
       <c r="B19" t="n">
-        <v>78660</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494444</v>
+        <v>494402</v>
       </c>
       <c r="R19" t="n">
-        <v>7006335</v>
+        <v>7006360</v>
       </c>
       <c r="S19" t="n">
         <v>8</v>
@@ -3078,22 +2883,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3111,50 +2916,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122355540</v>
+        <v>122360500</v>
       </c>
       <c r="B20" t="n">
-        <v>78660</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494535</v>
+        <v>494402</v>
       </c>
       <c r="R20" t="n">
-        <v>7006574</v>
+        <v>7006360</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3205,22 +3010,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3238,55 +3043,55 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122361119</v>
+        <v>122354497</v>
       </c>
       <c r="B21" t="n">
-        <v>79741</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>494460</v>
+        <v>494602</v>
       </c>
       <c r="R21" t="n">
-        <v>7006357</v>
+        <v>7006702</v>
       </c>
       <c r="S21" t="n">
         <v>7</v>
@@ -3323,7 +3128,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ymnig påväxt av lunglav på en gammal grov skadad sälg.</t>
+          <t>Äldre hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3342,22 +3147,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3375,15 +3180,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122360113</v>
+        <v>122355606</v>
       </c>
       <c r="B22" t="n">
-        <v>79770</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3391,39 +3191,44 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494392</v>
+        <v>494524</v>
       </c>
       <c r="R22" t="n">
-        <v>7006448</v>
+        <v>7006571</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3458,6 +3263,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska hackspår/födosökspår.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3474,22 +3284,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3507,32 +3317,27 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122364318</v>
+        <v>122357658</v>
       </c>
       <c r="B23" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3541,27 +3346,29 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494511</v>
+        <v>494515</v>
       </c>
       <c r="R23" t="n">
-        <v>7006626</v>
+        <v>7006545</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3595,7 +3402,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Färska ringhack några meter upp på en granstam.</t>
+          <t>Färska hackspår och födosökspår med avskalad bark.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3612,11 +3419,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
-        </is>
-      </c>
       <c r="AJ23" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3629,12 +3431,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3652,47 +3454,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122355645</v>
+        <v>122359111</v>
       </c>
       <c r="B24" t="n">
-        <v>57537</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3702,17 +3495,17 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494521</v>
+        <v>494496</v>
       </c>
       <c r="R24" t="n">
-        <v>7006584</v>
+        <v>7006482</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3744,6 +3537,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska hackspår/födosökspår i stående död tall.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3756,6 +3554,26 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3773,50 +3591,55 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122360599</v>
+        <v>122407942</v>
       </c>
       <c r="B25" t="n">
-        <v>79741</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494411</v>
+        <v>494566</v>
       </c>
       <c r="R25" t="n">
-        <v>7006366</v>
+        <v>7006630</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3843,17 +3666,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Enstaka bålar.</t>
+          <t>Färska rejäla hackspår i stambasen av en stående död tall.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3872,22 +3695,22 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3905,15 +3728,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122354497</v>
+        <v>122355822</v>
       </c>
       <c r="B26" t="n">
-        <v>57400</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3921,16 +3739,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3951,17 +3769,17 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494602</v>
+        <v>494487</v>
       </c>
       <c r="R26" t="n">
-        <v>7006702</v>
+        <v>7006560</v>
       </c>
       <c r="S26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3995,7 +3813,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Äldre hackspår i stambasen.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4047,15 +3865,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122359691</v>
+        <v>122364212</v>
       </c>
       <c r="B27" t="n">
-        <v>78660</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4063,37 +3876,49 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494410</v>
+        <v>494582</v>
       </c>
       <c r="R27" t="n">
-        <v>7006434</v>
+        <v>7006726</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4125,6 +3950,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Färska ringhack några meter upp på en granstam.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -4139,6 +3969,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Grandominerad skog men inslag av tall, björk, sälg och asp. Här finns gott om stående och liggande död ved.</t>
+        </is>
+      </c>
       <c r="AJ27" t="inlineStr">
         <is>
           <t>gran</t>
@@ -4151,12 +3986,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4174,58 +4009,56 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122360490</v>
+        <v>122364318</v>
       </c>
       <c r="B28" t="n">
-        <v>79770</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494402</v>
+        <v>494511</v>
       </c>
       <c r="R28" t="n">
-        <v>7006360</v>
+        <v>7006626</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4257,6 +4090,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Färska ringhack några meter upp på en granstam.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4271,24 +4109,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
+        </is>
+      </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4306,15 +4149,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122407671</v>
+        <v>122364537</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4340,9 +4178,11 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -4352,17 +4192,17 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Brynjeflon, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494534</v>
+        <v>494454</v>
       </c>
       <c r="R29" t="n">
-        <v>7006518</v>
+        <v>7006579</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4386,17 +4226,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Färska ringhack på en relativt grov granstam.</t>
+          <t>Äldre ringhack några meter upp på en granstam med kådaflöden.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4411,6 +4251,11 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4448,15 +4293,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122407942</v>
+        <v>122364729</v>
       </c>
       <c r="B30" t="n">
-        <v>57494</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4464,16 +4304,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4482,6 +4322,8 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -4494,17 +4336,17 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494566</v>
+        <v>494499</v>
       </c>
       <c r="R30" t="n">
-        <v>7006630</v>
+        <v>7006492</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4528,17 +4370,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Färska rejäla hackspår i stambasen av en stående död tall.</t>
+          <t>Färska inhack vid ca 2 meters höjd upp på en granstam.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4555,24 +4397,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
+        </is>
+      </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4590,15 +4437,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122406983</v>
+        <v>122407432</v>
       </c>
       <c r="B31" t="n">
-        <v>78762</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4606,34 +4448,44 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494621</v>
+        <v>494548</v>
       </c>
       <c r="R31" t="n">
-        <v>7006636</v>
+        <v>7006529</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4668,6 +4520,11 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4694,12 +4551,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4717,15 +4574,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122408149</v>
+        <v>122407671</v>
       </c>
       <c r="B32" t="n">
-        <v>90958</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4733,39 +4585,44 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494574</v>
+        <v>494534</v>
       </c>
       <c r="R32" t="n">
-        <v>7006638</v>
+        <v>7006518</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4802,7 +4659,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar.</t>
+          <t>Färska ringhack på en relativt grov granstam.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4831,12 +4688,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4854,15 +4711,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122407975</v>
+        <v>122355645</v>
       </c>
       <c r="B33" t="n">
-        <v>78762</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4870,34 +4722,48 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>494572</v>
+        <v>494521</v>
       </c>
       <c r="R33" t="n">
-        <v>7006632</v>
+        <v>7006584</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4924,12 +4790,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4944,26 +4810,6 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4981,15 +4827,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122406373</v>
+        <v>122357863</v>
       </c>
       <c r="B34" t="n">
-        <v>78762</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4997,34 +4838,48 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494674</v>
+        <v>494497</v>
       </c>
       <c r="R34" t="n">
-        <v>7006716</v>
+        <v>7006523</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5051,12 +4906,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5071,26 +4926,6 @@
       <c r="AH34" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5108,53 +4943,53 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122406150</v>
+        <v>129402385</v>
       </c>
       <c r="B35" t="n">
-        <v>78762</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494722</v>
+        <v>494766</v>
       </c>
       <c r="R35" t="n">
-        <v>7006694</v>
+        <v>7006750</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5178,12 +5013,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5198,26 +5043,6 @@
       <c r="AH35" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5235,50 +5060,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122406516</v>
+        <v>129402404</v>
       </c>
       <c r="B36" t="n">
-        <v>78762</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>494604</v>
+        <v>494734</v>
       </c>
       <c r="R36" t="n">
-        <v>7006665</v>
+        <v>7006744</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5305,12 +5130,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5325,26 +5160,6 @@
       <c r="AH36" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5362,63 +5177,53 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122407432</v>
+        <v>129402526</v>
       </c>
       <c r="B37" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>4769</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494548</v>
+        <v>494734</v>
       </c>
       <c r="R37" t="n">
-        <v>7006529</v>
+        <v>7006735</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5442,17 +5247,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5467,26 +5277,6 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5507,16 +5297,11 @@
         <v>122405719</v>
       </c>
       <c r="B38" t="n">
-        <v>78762</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -5631,53 +5416,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129402373</v>
+        <v>122406150</v>
       </c>
       <c r="B39" t="n">
-        <v>100969</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>494761</v>
+        <v>494722</v>
       </c>
       <c r="R39" t="n">
-        <v>7006746</v>
+        <v>7006694</v>
       </c>
       <c r="S39" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5701,22 +5481,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5731,6 +5501,26 @@
       <c r="AH39" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5748,50 +5538,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129402502</v>
+        <v>122406373</v>
       </c>
       <c r="B40" t="n">
-        <v>100969</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>494737</v>
+        <v>494674</v>
       </c>
       <c r="R40" t="n">
-        <v>7006737</v>
+        <v>7006716</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5818,22 +5603,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>12:31</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>12:31</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5848,6 +5623,26 @@
       <c r="AH40" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5865,53 +5660,68 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129402385</v>
+        <v>129430383</v>
       </c>
       <c r="B41" t="n">
-        <v>92554</v>
+        <v>57975</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>494766</v>
+        <v>494727</v>
       </c>
       <c r="R41" t="n">
-        <v>7006750</v>
+        <v>7006751</v>
       </c>
       <c r="S41" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5940,7 +5750,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5950,7 +5760,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>En hona av tretåig hackspett som sågs födosöka långt upp i en stående död gran med full längd. Fyndplatsen finns i gammal granskog med minst höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5965,6 +5780,11 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad skog med gott om stående död ved.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5982,38 +5802,47 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129402526</v>
+        <v>129402814</v>
       </c>
       <c r="B42" t="n">
-        <v>92554</v>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -6022,10 +5851,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>494734</v>
+        <v>494795</v>
       </c>
       <c r="R42" t="n">
-        <v>7006735</v>
+        <v>7006705</v>
       </c>
       <c r="S42" t="n">
         <v>11</v>
@@ -6057,7 +5886,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6067,7 +5896,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Minst 14 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6099,10 +5933,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129402404</v>
+        <v>129402373</v>
       </c>
       <c r="B43" t="n">
-        <v>92554</v>
+        <v>101325</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6110,27 +5944,27 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -6139,13 +5973,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>494734</v>
+        <v>494761</v>
       </c>
       <c r="R43" t="n">
-        <v>7006744</v>
+        <v>7006746</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6174,7 +6008,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6184,7 +6018,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6216,65 +6050,50 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129430383</v>
+        <v>129402502</v>
       </c>
       <c r="B44" t="n">
-        <v>57954</v>
+        <v>101325</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>494727</v>
+        <v>494737</v>
       </c>
       <c r="R44" t="n">
-        <v>7006751</v>
+        <v>7006737</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6306,7 +6125,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6316,12 +6135,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:36</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>En hona av tretåig hackspett som sågs födosöka långt upp i en stående död gran med full längd. Fyndplatsen finns i gammal granskog med minst höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6336,11 +6150,6 @@
       <c r="AH44" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad skog med gott om stående död ved.</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>

--- a/artfynd/A 5791-2026 artfynd.xlsx
+++ b/artfynd/A 5791-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY285"/>
+  <dimension ref="A1:AY281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8906,27 +8906,27 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>134724952</v>
+        <v>134725187</v>
       </c>
       <c r="B70" t="n">
-        <v>57975</v>
+        <v>57153</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -8934,25 +8934,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Bergmyren-Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>494462</v>
+        <v>494535</v>
       </c>
       <c r="R70" t="n">
-        <v>7006595</v>
+        <v>7006526</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8989,7 +8997,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>1 järpe med varningsläte sågs några meter upp i ett träd.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9004,26 +9012,6 @@
       <c r="AH70" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9041,10 +9029,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>134724953</v>
+        <v>122355645</v>
       </c>
       <c r="B71" t="n">
-        <v>57975</v>
+        <v>58114</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9052,42 +9040,48 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Bergmyren-Barnsängbäcken, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>494456</v>
+        <v>494521</v>
       </c>
       <c r="R71" t="n">
-        <v>7006579</v>
+        <v>7006584</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9114,17 +9108,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, längs flera meter på en gran vid kant mot yngre skog.</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9139,26 +9128,6 @@
       <c r="AH71" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9176,10 +9145,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>134724954</v>
+        <v>122357863</v>
       </c>
       <c r="B72" t="n">
-        <v>57975</v>
+        <v>58114</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9187,29 +9156,31 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -9219,14 +9190,14 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Bergmyren-Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>494448</v>
+        <v>494497</v>
       </c>
       <c r="R72" t="n">
-        <v>7006573</v>
+        <v>7006523</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9253,17 +9224,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, längs flera meter på en gran vid kant mot yngre skog.</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9278,26 +9244,6 @@
       <c r="AH72" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -9315,27 +9261,27 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>134724955</v>
+        <v>134724963</v>
       </c>
       <c r="B73" t="n">
-        <v>57975</v>
+        <v>58131</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>103023</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -9349,14 +9295,10 @@
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -9370,10 +9312,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>494391</v>
+        <v>494371</v>
       </c>
       <c r="R73" t="n">
-        <v>7006346</v>
+        <v>7006417</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9408,11 +9350,6 @@
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>1 st hona av tretåig hackspett som sågs födosöka en kort stund på en stående död gran. På fyndplatsen finns stående död ved som indikerar mycket högt livsmiljövärde för tretåig hackspett, bl.a. en stående död gran med full längd och 68 cm i brösthöjdsdiameter.</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -9425,11 +9362,6 @@
       <c r="AH73" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI73" t="inlineStr">
-        <is>
-          <t>Äldre näringsrik granskog.</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9447,10 +9379,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>134725187</v>
+        <v>134725219</v>
       </c>
       <c r="B74" t="n">
-        <v>57153</v>
+        <v>99094</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9458,35 +9390,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>102612</v>
+        <v>219795</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N74" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -9498,10 +9434,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>494535</v>
+        <v>494584</v>
       </c>
       <c r="R74" t="n">
-        <v>7006526</v>
+        <v>7006612</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9538,7 +9474,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>1 järpe med varningsläte sågs några meter upp i ett träd.</t>
+          <t>Minst 7 plantor varav 3 med blomställningar inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9547,6 +9483,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -9570,59 +9507,61 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122355645</v>
+        <v>134725220</v>
       </c>
       <c r="B75" t="n">
-        <v>58114</v>
+        <v>99094</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103021</v>
+        <v>219795</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren-Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>494521</v>
+        <v>494481</v>
       </c>
       <c r="R75" t="n">
-        <v>7006584</v>
+        <v>7006411</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9649,12 +9588,17 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Minst 4 plantor varav 3 i blom samt 2 vinterståndare på ca 2 x 1 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9663,6 +9607,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -9686,59 +9631,53 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122357863</v>
+        <v>134725224</v>
       </c>
       <c r="B76" t="n">
-        <v>58114</v>
+        <v>98219</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>103021</v>
+        <v>219815</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Newman</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Bergmyren-Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>494497</v>
+        <v>494379</v>
       </c>
       <c r="R76" t="n">
-        <v>7006523</v>
+        <v>7006437</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9765,12 +9704,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9779,6 +9718,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -9802,10 +9742,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>134724963</v>
+        <v>134725225</v>
       </c>
       <c r="B77" t="n">
-        <v>58131</v>
+        <v>98219</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9813,50 +9753,42 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>103023</v>
+        <v>219815</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
+          <t>(L.) Newman</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Bergmyren-Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>494371</v>
+        <v>494469</v>
       </c>
       <c r="R77" t="n">
-        <v>7006417</v>
+        <v>7006386</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9897,6 +9829,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -9920,10 +9853,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>134725219</v>
+        <v>134725090</v>
       </c>
       <c r="B78" t="n">
-        <v>99094</v>
+        <v>99533</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9931,54 +9864,42 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>219795</v>
+        <v>219880</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Bergmyren-Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>494584</v>
+        <v>494770</v>
       </c>
       <c r="R78" t="n">
-        <v>7006612</v>
+        <v>7006734</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10011,11 +9932,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Minst 7 plantor varav 3 med blomställningar inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10048,10 +9964,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>134725220</v>
+        <v>134725091</v>
       </c>
       <c r="B79" t="n">
-        <v>99094</v>
+        <v>99533</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10059,33 +9975,25 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>219795</v>
+        <v>219880</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -10099,10 +10007,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>494481</v>
+        <v>494727</v>
       </c>
       <c r="R79" t="n">
-        <v>7006411</v>
+        <v>7006690</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10135,11 +10043,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Minst 4 plantor varav 3 i blom samt 2 vinterståndare på ca 2 x 1 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10172,10 +10075,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>134725224</v>
+        <v>134725093</v>
       </c>
       <c r="B80" t="n">
-        <v>98219</v>
+        <v>99533</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10183,28 +10086,28 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>219815</v>
+        <v>219880</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L80" t="inlineStr"/>
@@ -10215,10 +10118,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>494379</v>
+        <v>494684</v>
       </c>
       <c r="R80" t="n">
-        <v>7006437</v>
+        <v>7006741</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10283,10 +10186,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>134725225</v>
+        <v>134725095</v>
       </c>
       <c r="B81" t="n">
-        <v>98219</v>
+        <v>99533</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10294,28 +10197,28 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>219815</v>
+        <v>219880</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
@@ -10326,10 +10229,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>494469</v>
+        <v>494637</v>
       </c>
       <c r="R81" t="n">
-        <v>7006386</v>
+        <v>7006730</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10394,7 +10297,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>134725090</v>
+        <v>134725096</v>
       </c>
       <c r="B82" t="n">
         <v>99533</v>
@@ -10426,7 +10329,7 @@
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L82" t="inlineStr"/>
@@ -10437,10 +10340,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>494770</v>
+        <v>494628</v>
       </c>
       <c r="R82" t="n">
-        <v>7006734</v>
+        <v>7006712</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10505,7 +10408,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>134725091</v>
+        <v>134725098</v>
       </c>
       <c r="B83" t="n">
         <v>99533</v>
@@ -10548,10 +10451,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>494727</v>
+        <v>494631</v>
       </c>
       <c r="R83" t="n">
-        <v>7006690</v>
+        <v>7006688</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10616,7 +10519,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>134725093</v>
+        <v>134725100</v>
       </c>
       <c r="B84" t="n">
         <v>99533</v>
@@ -10659,10 +10562,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>494684</v>
+        <v>494525</v>
       </c>
       <c r="R84" t="n">
-        <v>7006741</v>
+        <v>7006614</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10727,7 +10630,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>134725095</v>
+        <v>134725101</v>
       </c>
       <c r="B85" t="n">
         <v>99533</v>
@@ -10770,10 +10673,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>494637</v>
+        <v>494474</v>
       </c>
       <c r="R85" t="n">
-        <v>7006730</v>
+        <v>7006605</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10806,6 +10709,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Kransrams bland andra högörter i ett frodigt stråk vid en bäck.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10838,7 +10746,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>134725096</v>
+        <v>134725102</v>
       </c>
       <c r="B86" t="n">
         <v>99533</v>
@@ -10870,7 +10778,7 @@
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L86" t="inlineStr"/>
@@ -10881,10 +10789,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>494628</v>
+        <v>494482</v>
       </c>
       <c r="R86" t="n">
-        <v>7006712</v>
+        <v>7006601</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10949,7 +10857,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>134725098</v>
+        <v>134725104</v>
       </c>
       <c r="B87" t="n">
         <v>99533</v>
@@ -10992,10 +10900,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>494631</v>
+        <v>494515</v>
       </c>
       <c r="R87" t="n">
-        <v>7006688</v>
+        <v>7006595</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11060,7 +10968,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>134725100</v>
+        <v>134725105</v>
       </c>
       <c r="B88" t="n">
         <v>99533</v>
@@ -11103,10 +11011,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>494525</v>
+        <v>494473</v>
       </c>
       <c r="R88" t="n">
-        <v>7006614</v>
+        <v>7006548</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11171,7 +11079,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>134725101</v>
+        <v>134725107</v>
       </c>
       <c r="B89" t="n">
         <v>99533</v>
@@ -11203,7 +11111,7 @@
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L89" t="inlineStr"/>
@@ -11214,10 +11122,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>494474</v>
+        <v>494480</v>
       </c>
       <c r="R89" t="n">
-        <v>7006605</v>
+        <v>7006567</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11250,11 +11158,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Kransrams bland andra högörter i ett frodigt stråk vid en bäck.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11287,7 +11190,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>134725102</v>
+        <v>134725108</v>
       </c>
       <c r="B90" t="n">
         <v>99533</v>
@@ -11330,10 +11233,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>494482</v>
+        <v>494495</v>
       </c>
       <c r="R90" t="n">
-        <v>7006601</v>
+        <v>7006550</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11398,7 +11301,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>134725104</v>
+        <v>134725109</v>
       </c>
       <c r="B91" t="n">
         <v>99533</v>
@@ -11441,10 +11344,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>494515</v>
+        <v>494508</v>
       </c>
       <c r="R91" t="n">
-        <v>7006595</v>
+        <v>7006533</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11509,7 +11412,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>134725105</v>
+        <v>134725110</v>
       </c>
       <c r="B92" t="n">
         <v>99533</v>
@@ -11541,7 +11444,7 @@
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L92" t="inlineStr"/>
@@ -11552,10 +11455,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>494473</v>
+        <v>494567</v>
       </c>
       <c r="R92" t="n">
-        <v>7006548</v>
+        <v>7006557</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11620,7 +11523,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>134725107</v>
+        <v>134725111</v>
       </c>
       <c r="B93" t="n">
         <v>99533</v>
@@ -11652,7 +11555,7 @@
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L93" t="inlineStr"/>
@@ -11663,10 +11566,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>494480</v>
+        <v>494595</v>
       </c>
       <c r="R93" t="n">
-        <v>7006567</v>
+        <v>7006678</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11731,7 +11634,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>134725108</v>
+        <v>134725112</v>
       </c>
       <c r="B94" t="n">
         <v>99533</v>
@@ -11763,7 +11666,7 @@
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L94" t="inlineStr"/>
@@ -11774,10 +11677,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>494495</v>
+        <v>494575</v>
       </c>
       <c r="R94" t="n">
-        <v>7006550</v>
+        <v>7006547</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11842,7 +11745,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>134725109</v>
+        <v>134725113</v>
       </c>
       <c r="B95" t="n">
         <v>99533</v>
@@ -11874,7 +11777,7 @@
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L95" t="inlineStr"/>
@@ -11885,10 +11788,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>494508</v>
+        <v>494457</v>
       </c>
       <c r="R95" t="n">
-        <v>7006533</v>
+        <v>7006490</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11953,7 +11856,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>134725110</v>
+        <v>134725114</v>
       </c>
       <c r="B96" t="n">
         <v>99533</v>
@@ -11996,10 +11899,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>494567</v>
+        <v>494404</v>
       </c>
       <c r="R96" t="n">
-        <v>7006557</v>
+        <v>7006314</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12064,7 +11967,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>134725111</v>
+        <v>134725115</v>
       </c>
       <c r="B97" t="n">
         <v>99533</v>
@@ -12107,10 +12010,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>494595</v>
+        <v>494395</v>
       </c>
       <c r="R97" t="n">
-        <v>7006678</v>
+        <v>7006331</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12175,7 +12078,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>134725112</v>
+        <v>134725116</v>
       </c>
       <c r="B98" t="n">
         <v>99533</v>
@@ -12218,10 +12121,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>494575</v>
+        <v>494395</v>
       </c>
       <c r="R98" t="n">
-        <v>7006547</v>
+        <v>7006324</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12286,7 +12189,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>134725113</v>
+        <v>134725117</v>
       </c>
       <c r="B99" t="n">
         <v>99533</v>
@@ -12318,7 +12221,7 @@
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L99" t="inlineStr"/>
@@ -12329,10 +12232,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>494457</v>
+        <v>494364</v>
       </c>
       <c r="R99" t="n">
-        <v>7006490</v>
+        <v>7006343</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12365,6 +12268,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12397,7 +12305,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>134725114</v>
+        <v>134725118</v>
       </c>
       <c r="B100" t="n">
         <v>99533</v>
@@ -12440,10 +12348,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>494404</v>
+        <v>494383</v>
       </c>
       <c r="R100" t="n">
-        <v>7006314</v>
+        <v>7006414</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12508,7 +12416,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>134725115</v>
+        <v>134725119</v>
       </c>
       <c r="B101" t="n">
         <v>99533</v>
@@ -12551,10 +12459,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>494395</v>
+        <v>494436</v>
       </c>
       <c r="R101" t="n">
-        <v>7006331</v>
+        <v>7006475</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12619,7 +12527,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>134725116</v>
+        <v>134725120</v>
       </c>
       <c r="B102" t="n">
         <v>99533</v>
@@ -12662,10 +12570,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>494395</v>
+        <v>494435</v>
       </c>
       <c r="R102" t="n">
-        <v>7006324</v>
+        <v>7006464</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12698,6 +12606,11 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12730,7 +12643,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>134725117</v>
+        <v>134725121</v>
       </c>
       <c r="B103" t="n">
         <v>99533</v>
@@ -12762,7 +12675,7 @@
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L103" t="inlineStr"/>
@@ -12773,10 +12686,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>494364</v>
+        <v>494440</v>
       </c>
       <c r="R103" t="n">
-        <v>7006343</v>
+        <v>7006481</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12809,11 +12722,6 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12846,7 +12754,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>134725118</v>
+        <v>134725122</v>
       </c>
       <c r="B104" t="n">
         <v>99533</v>
@@ -12889,10 +12797,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>494383</v>
+        <v>494473</v>
       </c>
       <c r="R104" t="n">
-        <v>7006414</v>
+        <v>7006491</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12957,10 +12865,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>134725119</v>
+        <v>134725226</v>
       </c>
       <c r="B105" t="n">
-        <v>99533</v>
+        <v>108205</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12968,28 +12876,28 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>219880</v>
+        <v>220083</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L105" t="inlineStr"/>
@@ -13000,10 +12908,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>494436</v>
+        <v>494763</v>
       </c>
       <c r="R105" t="n">
-        <v>7006475</v>
+        <v>7006744</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -13068,10 +12976,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>134725120</v>
+        <v>134725227</v>
       </c>
       <c r="B106" t="n">
-        <v>99533</v>
+        <v>108205</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13079,21 +12987,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>219880</v>
+        <v>220083</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -13111,10 +13019,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>494435</v>
+        <v>494582</v>
       </c>
       <c r="R106" t="n">
-        <v>7006464</v>
+        <v>7006695</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -13147,11 +13055,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13184,10 +13087,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>134725121</v>
+        <v>134725155</v>
       </c>
       <c r="B107" t="n">
-        <v>99533</v>
+        <v>99099</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13195,28 +13098,36 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>219880</v>
+        <v>220093</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L107" t="inlineStr"/>
@@ -13227,10 +13138,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>494440</v>
+        <v>494460</v>
       </c>
       <c r="R107" t="n">
-        <v>7006481</v>
+        <v>7006572</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13295,10 +13206,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>134725122</v>
+        <v>134725156</v>
       </c>
       <c r="B108" t="n">
-        <v>99533</v>
+        <v>99099</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13306,28 +13217,36 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>219880</v>
+        <v>220093</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L108" t="inlineStr"/>
@@ -13338,10 +13257,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>494473</v>
+        <v>494575</v>
       </c>
       <c r="R108" t="n">
-        <v>7006491</v>
+        <v>7006548</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13406,10 +13325,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>134725226</v>
+        <v>134725068</v>
       </c>
       <c r="B109" t="n">
-        <v>108205</v>
+        <v>108274</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13417,28 +13336,28 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220083</v>
+        <v>220102</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L109" t="inlineStr"/>
@@ -13449,10 +13368,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>494763</v>
+        <v>494743</v>
       </c>
       <c r="R109" t="n">
-        <v>7006744</v>
+        <v>7006752</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13517,10 +13436,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>134725227</v>
+        <v>134725069</v>
       </c>
       <c r="B110" t="n">
-        <v>108205</v>
+        <v>108274</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13528,28 +13447,28 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220083</v>
+        <v>220102</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L110" t="inlineStr"/>
@@ -13560,10 +13479,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>494582</v>
+        <v>494743</v>
       </c>
       <c r="R110" t="n">
-        <v>7006695</v>
+        <v>7006715</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13628,10 +13547,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>134725155</v>
+        <v>134725070</v>
       </c>
       <c r="B111" t="n">
-        <v>99099</v>
+        <v>108274</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13639,36 +13558,28 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>220093</v>
+        <v>220102</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L111" t="inlineStr"/>
@@ -13679,10 +13590,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>494460</v>
+        <v>494717</v>
       </c>
       <c r="R111" t="n">
-        <v>7006572</v>
+        <v>7006747</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13747,10 +13658,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>134725156</v>
+        <v>134725071</v>
       </c>
       <c r="B112" t="n">
-        <v>99099</v>
+        <v>108274</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13758,36 +13669,28 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220093</v>
+        <v>220102</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L112" t="inlineStr"/>
@@ -13798,10 +13701,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>494575</v>
+        <v>494683</v>
       </c>
       <c r="R112" t="n">
-        <v>7006548</v>
+        <v>7006724</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13866,7 +13769,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>134725068</v>
+        <v>134725072</v>
       </c>
       <c r="B113" t="n">
         <v>108274</v>
@@ -13909,10 +13812,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>494743</v>
+        <v>494644</v>
       </c>
       <c r="R113" t="n">
-        <v>7006752</v>
+        <v>7006712</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13977,7 +13880,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>134725069</v>
+        <v>134725073</v>
       </c>
       <c r="B114" t="n">
         <v>108274</v>
@@ -14020,10 +13923,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>494743</v>
+        <v>494634</v>
       </c>
       <c r="R114" t="n">
-        <v>7006715</v>
+        <v>7006699</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -14088,7 +13991,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>134725070</v>
+        <v>134725075</v>
       </c>
       <c r="B115" t="n">
         <v>108274</v>
@@ -14120,7 +14023,7 @@
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L115" t="inlineStr"/>
@@ -14131,10 +14034,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>494717</v>
+        <v>494564</v>
       </c>
       <c r="R115" t="n">
-        <v>7006747</v>
+        <v>7006669</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -14199,7 +14102,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>134725071</v>
+        <v>134725076</v>
       </c>
       <c r="B116" t="n">
         <v>108274</v>
@@ -14231,7 +14134,7 @@
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L116" t="inlineStr"/>
@@ -14242,10 +14145,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>494683</v>
+        <v>494517</v>
       </c>
       <c r="R116" t="n">
-        <v>7006724</v>
+        <v>7006596</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -14310,7 +14213,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>134725072</v>
+        <v>134725078</v>
       </c>
       <c r="B117" t="n">
         <v>108274</v>
@@ -14353,10 +14256,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>494644</v>
+        <v>494462</v>
       </c>
       <c r="R117" t="n">
-        <v>7006712</v>
+        <v>7006579</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -14421,7 +14324,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>134725073</v>
+        <v>134725079</v>
       </c>
       <c r="B118" t="n">
         <v>108274</v>
@@ -14464,10 +14367,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>494634</v>
+        <v>494583</v>
       </c>
       <c r="R118" t="n">
-        <v>7006699</v>
+        <v>7006613</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14532,7 +14435,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>134725075</v>
+        <v>134725081</v>
       </c>
       <c r="B119" t="n">
         <v>108274</v>
@@ -14575,10 +14478,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>494564</v>
+        <v>494595</v>
       </c>
       <c r="R119" t="n">
-        <v>7006669</v>
+        <v>7006635</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14643,7 +14546,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>134725076</v>
+        <v>134725082</v>
       </c>
       <c r="B120" t="n">
         <v>108274</v>
@@ -14675,7 +14578,7 @@
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L120" t="inlineStr"/>
@@ -14686,10 +14589,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>494517</v>
+        <v>494571</v>
       </c>
       <c r="R120" t="n">
-        <v>7006596</v>
+        <v>7006652</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14754,7 +14657,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>134725078</v>
+        <v>134725083</v>
       </c>
       <c r="B121" t="n">
         <v>108274</v>
@@ -14786,7 +14689,7 @@
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L121" t="inlineStr"/>
@@ -14797,10 +14700,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>494462</v>
+        <v>494609</v>
       </c>
       <c r="R121" t="n">
-        <v>7006579</v>
+        <v>7006667</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14865,7 +14768,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>134725079</v>
+        <v>134725085</v>
       </c>
       <c r="B122" t="n">
         <v>108274</v>
@@ -14908,10 +14811,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>494583</v>
+        <v>494497</v>
       </c>
       <c r="R122" t="n">
-        <v>7006613</v>
+        <v>7006507</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14976,7 +14879,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>134725081</v>
+        <v>134725087</v>
       </c>
       <c r="B123" t="n">
         <v>108274</v>
@@ -15019,10 +14922,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>494595</v>
+        <v>494437</v>
       </c>
       <c r="R123" t="n">
-        <v>7006635</v>
+        <v>7006466</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -15087,7 +14990,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>134725082</v>
+        <v>134725088</v>
       </c>
       <c r="B124" t="n">
         <v>108274</v>
@@ -15130,10 +15033,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>494571</v>
+        <v>494447</v>
       </c>
       <c r="R124" t="n">
-        <v>7006652</v>
+        <v>7006468</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -15198,10 +15101,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>134725083</v>
+        <v>134725050</v>
       </c>
       <c r="B125" t="n">
-        <v>108274</v>
+        <v>111153</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15209,21 +15112,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>220102</v>
+        <v>220240</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -15241,10 +15144,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>494609</v>
+        <v>494642</v>
       </c>
       <c r="R125" t="n">
-        <v>7006667</v>
+        <v>7006722</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -15309,10 +15212,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>134725085</v>
+        <v>134725051</v>
       </c>
       <c r="B126" t="n">
-        <v>108274</v>
+        <v>111153</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15320,28 +15223,28 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>220102</v>
+        <v>220240</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L126" t="inlineStr"/>
@@ -15352,10 +15255,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>494497</v>
+        <v>494632</v>
       </c>
       <c r="R126" t="n">
-        <v>7006507</v>
+        <v>7006697</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -15420,10 +15323,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>134725087</v>
+        <v>134725052</v>
       </c>
       <c r="B127" t="n">
-        <v>108274</v>
+        <v>111153</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15431,21 +15334,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220102</v>
+        <v>220240</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -15463,10 +15366,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>494437</v>
+        <v>494521</v>
       </c>
       <c r="R127" t="n">
-        <v>7006466</v>
+        <v>7006593</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15531,10 +15434,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>134725088</v>
+        <v>134725053</v>
       </c>
       <c r="B128" t="n">
-        <v>108274</v>
+        <v>111153</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15542,21 +15445,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220102</v>
+        <v>220240</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -15574,10 +15477,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>494447</v>
+        <v>494611</v>
       </c>
       <c r="R128" t="n">
-        <v>7006468</v>
+        <v>7006598</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15610,6 +15513,11 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15642,7 +15550,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>134725050</v>
+        <v>134725054</v>
       </c>
       <c r="B129" t="n">
         <v>111153</v>
@@ -15685,10 +15593,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>494642</v>
+        <v>494569</v>
       </c>
       <c r="R129" t="n">
-        <v>7006722</v>
+        <v>7006642</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15753,7 +15661,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>134725051</v>
+        <v>134725055</v>
       </c>
       <c r="B130" t="n">
         <v>111153</v>
@@ -15796,10 +15704,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>494632</v>
+        <v>494609</v>
       </c>
       <c r="R130" t="n">
-        <v>7006697</v>
+        <v>7006555</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15864,7 +15772,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>134725052</v>
+        <v>134725056</v>
       </c>
       <c r="B131" t="n">
         <v>111153</v>
@@ -15907,10 +15815,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>494521</v>
+        <v>494421</v>
       </c>
       <c r="R131" t="n">
-        <v>7006593</v>
+        <v>7006395</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15975,7 +15883,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>134725053</v>
+        <v>134725057</v>
       </c>
       <c r="B132" t="n">
         <v>111153</v>
@@ -16007,7 +15915,7 @@
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L132" t="inlineStr"/>
@@ -16018,10 +15926,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>494611</v>
+        <v>494424</v>
       </c>
       <c r="R132" t="n">
-        <v>7006598</v>
+        <v>7006319</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -16054,11 +15962,6 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -16091,7 +15994,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>134725054</v>
+        <v>134725058</v>
       </c>
       <c r="B133" t="n">
         <v>111153</v>
@@ -16134,10 +16037,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>494569</v>
+        <v>494388</v>
       </c>
       <c r="R133" t="n">
-        <v>7006642</v>
+        <v>7006367</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -16202,7 +16105,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>134725055</v>
+        <v>134725059</v>
       </c>
       <c r="B134" t="n">
         <v>111153</v>
@@ -16245,10 +16148,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>494609</v>
+        <v>494373</v>
       </c>
       <c r="R134" t="n">
-        <v>7006555</v>
+        <v>7006369</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -16313,7 +16216,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>134725056</v>
+        <v>134725060</v>
       </c>
       <c r="B135" t="n">
         <v>111153</v>
@@ -16356,10 +16259,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>494421</v>
+        <v>494397</v>
       </c>
       <c r="R135" t="n">
-        <v>7006395</v>
+        <v>7006377</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -16424,7 +16327,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>134725057</v>
+        <v>134725061</v>
       </c>
       <c r="B136" t="n">
         <v>111153</v>
@@ -16456,7 +16359,7 @@
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L136" t="inlineStr"/>
@@ -16467,10 +16370,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>494424</v>
+        <v>494402</v>
       </c>
       <c r="R136" t="n">
-        <v>7006319</v>
+        <v>7006416</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -16535,7 +16438,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>134725058</v>
+        <v>134725063</v>
       </c>
       <c r="B137" t="n">
         <v>111153</v>
@@ -16578,10 +16481,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>494388</v>
+        <v>494446</v>
       </c>
       <c r="R137" t="n">
-        <v>7006367</v>
+        <v>7006452</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16646,7 +16549,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>134725059</v>
+        <v>134725064</v>
       </c>
       <c r="B138" t="n">
         <v>111153</v>
@@ -16678,7 +16581,7 @@
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L138" t="inlineStr"/>
@@ -16689,10 +16592,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>494373</v>
+        <v>494459</v>
       </c>
       <c r="R138" t="n">
-        <v>7006369</v>
+        <v>7006430</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16757,56 +16660,62 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>134725060</v>
+        <v>129402814</v>
       </c>
       <c r="B139" t="n">
-        <v>111153</v>
+        <v>99118</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>220240</v>
+        <v>220787</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K139" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Bergmyren-Barnsängbäcken, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>494397</v>
+        <v>494795</v>
       </c>
       <c r="R139" t="n">
-        <v>7006377</v>
+        <v>7006705</v>
       </c>
       <c r="S139" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -16830,12 +16739,27 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Minst 14 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16844,7 +16768,6 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -16868,39 +16791,47 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>134725061</v>
+        <v>134725158</v>
       </c>
       <c r="B140" t="n">
-        <v>111153</v>
+        <v>99195</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>220240</v>
+        <v>220787</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L140" t="inlineStr"/>
@@ -16911,10 +16842,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>494402</v>
+        <v>494757</v>
       </c>
       <c r="R140" t="n">
-        <v>7006416</v>
+        <v>7006738</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16947,6 +16878,11 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Minst 100 plantor och 1 blomstjälk med knopp på gång inom ca 2 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16979,39 +16915,47 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>134725063</v>
+        <v>134725159</v>
       </c>
       <c r="B141" t="n">
-        <v>111153</v>
+        <v>99195</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>220240</v>
+        <v>220787</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L141" t="inlineStr"/>
@@ -17022,10 +16966,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>494446</v>
+        <v>494756</v>
       </c>
       <c r="R141" t="n">
-        <v>7006452</v>
+        <v>7006724</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -17058,6 +17002,11 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Minst 40 plantor och 10 blomstjälkar med knopp på gång inom ca 1 m2 yta på en liten mossklädd förhöjning i granskog.</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -17090,36 +17039,44 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>134725064</v>
+        <v>134725161</v>
       </c>
       <c r="B142" t="n">
-        <v>111153</v>
+        <v>99195</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>220240</v>
+        <v>220787</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K142" t="inlineStr">
         <is>
           <t>blomknopp</t>
@@ -17133,10 +17090,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>494459</v>
+        <v>494719</v>
       </c>
       <c r="R142" t="n">
-        <v>7006430</v>
+        <v>7006678</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -17169,6 +17126,11 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Minst 35 plantor och 6 blomstjälkar med knopp på gång inom ca 2 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -17201,10 +17163,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129402814</v>
+        <v>134725162</v>
       </c>
       <c r="B143" t="n">
-        <v>99118</v>
+        <v>99195</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17231,7 +17193,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -17241,22 +17203,24 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren-Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>494795</v>
+        <v>494701</v>
       </c>
       <c r="R143" t="n">
-        <v>7006705</v>
+        <v>7006715</v>
       </c>
       <c r="S143" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -17280,27 +17244,17 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>12:46</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>12:46</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>Minst 14 plantor inom ca 0,5 m2 yta.</t>
+          <t>Minst 90 plantor och 11 blomstjälkar med knopp på gång inom ca 2 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -17309,6 +17263,7 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
@@ -17332,7 +17287,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>134725158</v>
+        <v>134725164</v>
       </c>
       <c r="B144" t="n">
         <v>99195</v>
@@ -17362,7 +17317,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -17383,10 +17338,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>494757</v>
+        <v>494696</v>
       </c>
       <c r="R144" t="n">
-        <v>7006738</v>
+        <v>7006695</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -17423,7 +17378,7 @@
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Minst 100 plantor och 1 blomstjälk med knopp på gång inom ca 2 m2 yta i granskog.</t>
+          <t>Minst 12 plantor och 2 blomstjälkar med knopp på gång inom ca 0,5 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -17456,7 +17411,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>134725159</v>
+        <v>134725165</v>
       </c>
       <c r="B145" t="n">
         <v>99195</v>
@@ -17486,7 +17441,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -17507,10 +17462,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>494756</v>
+        <v>494435</v>
       </c>
       <c r="R145" t="n">
-        <v>7006724</v>
+        <v>7006538</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -17547,7 +17502,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>Minst 40 plantor och 10 blomstjälkar med knopp på gång inom ca 1 m2 yta på en liten mossklädd förhöjning i granskog.</t>
+          <t>Minst 35 plantor och 2 blomstjälkar med knopp på gång inom ca 1 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -17580,7 +17535,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>134725161</v>
+        <v>134725167</v>
       </c>
       <c r="B146" t="n">
         <v>99195</v>
@@ -17610,7 +17565,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -17631,10 +17586,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>494719</v>
+        <v>494436</v>
       </c>
       <c r="R146" t="n">
-        <v>7006678</v>
+        <v>7006431</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -17671,7 +17626,7 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>Minst 35 plantor och 6 blomstjälkar med knopp på gång inom ca 2 m2 yta i granskog.</t>
+          <t>Minst 25 plantor och 2 blomstjälkar med knopp på gång inom ca 0,5 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17704,7 +17659,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>134725162</v>
+        <v>134725169</v>
       </c>
       <c r="B147" t="n">
         <v>99195</v>
@@ -17734,7 +17689,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -17755,10 +17710,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>494701</v>
+        <v>494428</v>
       </c>
       <c r="R147" t="n">
-        <v>7006715</v>
+        <v>7006412</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17795,7 +17750,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>Minst 90 plantor och 11 blomstjälkar med knopp på gång inom ca 2 m2 yta i granskog.</t>
+          <t>Minst 13 plantor och 2 blomstjälkar med knopp på gång inom ca 0,5 m2 yta i ett örtrikt stråk i granskog.</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17828,7 +17783,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>134725164</v>
+        <v>134725171</v>
       </c>
       <c r="B148" t="n">
         <v>99195</v>
@@ -17858,7 +17813,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -17879,10 +17834,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>494696</v>
+        <v>494466</v>
       </c>
       <c r="R148" t="n">
-        <v>7006695</v>
+        <v>7006367</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17919,7 +17874,7 @@
       </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>Minst 12 plantor och 2 blomstjälkar med knopp på gång inom ca 0,5 m2 yta i granskog.</t>
+          <t>Minst 15 plantor och 3 blomstjälkar med knopp på gång inom ca 1 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17952,7 +17907,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>134725165</v>
+        <v>134725172</v>
       </c>
       <c r="B149" t="n">
         <v>99195</v>
@@ -17982,7 +17937,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -18003,10 +17958,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>494435</v>
+        <v>494382</v>
       </c>
       <c r="R149" t="n">
-        <v>7006538</v>
+        <v>7006321</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -18043,7 +17998,7 @@
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>Minst 35 plantor och 2 blomstjälkar med knopp på gång inom ca 1 m2 yta i granskog.</t>
+          <t>Minst 30 plantor och 5 blomstjälkar med knopp på gång inom ca 1 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -18076,7 +18031,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>134725167</v>
+        <v>134725174</v>
       </c>
       <c r="B150" t="n">
         <v>99195</v>
@@ -18106,7 +18061,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -18127,10 +18082,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>494436</v>
+        <v>494368</v>
       </c>
       <c r="R150" t="n">
-        <v>7006431</v>
+        <v>7006369</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -18167,7 +18122,7 @@
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>Minst 25 plantor och 2 blomstjälkar med knopp på gång inom ca 0,5 m2 yta i granskog.</t>
+          <t>Minst 60 plantor och 1 blomstjälk med knopp på gång inom ca 2 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -18200,7 +18155,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>134725169</v>
+        <v>134725176</v>
       </c>
       <c r="B151" t="n">
         <v>99195</v>
@@ -18230,7 +18185,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -18251,10 +18206,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>494428</v>
+        <v>494398</v>
       </c>
       <c r="R151" t="n">
-        <v>7006412</v>
+        <v>7006384</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -18291,7 +18246,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>Minst 13 plantor och 2 blomstjälkar med knopp på gång inom ca 0,5 m2 yta i ett örtrikt stråk i granskog.</t>
+          <t>Minst 22 plantor och 1 blomstjälk med knopp på gång inom ca 1 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -18324,7 +18279,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>134725171</v>
+        <v>134725177</v>
       </c>
       <c r="B152" t="n">
         <v>99195</v>
@@ -18354,7 +18309,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -18375,10 +18330,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>494466</v>
+        <v>494375</v>
       </c>
       <c r="R152" t="n">
-        <v>7006367</v>
+        <v>7006421</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -18415,7 +18370,7 @@
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>Minst 15 plantor och 3 blomstjälkar med knopp på gång inom ca 1 m2 yta i granskog.</t>
+          <t>Minst 60 plantor och 30 blomstjälkar med knopp på gång inom ca 2 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -18448,7 +18403,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>134725172</v>
+        <v>134725179</v>
       </c>
       <c r="B153" t="n">
         <v>99195</v>
@@ -18478,7 +18433,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -18499,10 +18454,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>494382</v>
+        <v>494432</v>
       </c>
       <c r="R153" t="n">
-        <v>7006321</v>
+        <v>7006477</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -18539,7 +18494,7 @@
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>Minst 30 plantor och 5 blomstjälkar med knopp på gång inom ca 1 m2 yta i granskog.</t>
+          <t>Minst 27 plantor och 1 blomstjälk med knopp på gång inom ca 1 m2 yta i äldre granskog.</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -18572,7 +18527,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>134725174</v>
+        <v>134725180</v>
       </c>
       <c r="B154" t="n">
         <v>99195</v>
@@ -18602,7 +18557,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -18623,10 +18578,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>494368</v>
+        <v>494483</v>
       </c>
       <c r="R154" t="n">
-        <v>7006369</v>
+        <v>7006405</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -18663,7 +18618,7 @@
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>Minst 60 plantor och 1 blomstjälk med knopp på gång inom ca 2 m2 yta i granskog.</t>
+          <t>Minst 200 plantor och 23 blomstjälkar med knopp på gång inom ca 4 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -18696,7 +18651,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>134725176</v>
+        <v>134725183</v>
       </c>
       <c r="B155" t="n">
         <v>99195</v>
@@ -18726,7 +18681,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>260</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -18747,10 +18702,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>494398</v>
+        <v>494494</v>
       </c>
       <c r="R155" t="n">
-        <v>7006384</v>
+        <v>7006385</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18787,7 +18742,7 @@
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>Minst 22 plantor och 1 blomstjälk med knopp på gång inom ca 1 m2 yta i granskog.</t>
+          <t>Minst 260 plantor och 12 blomstjälkar med knopp på gång inom ca 2 x 1 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18820,7 +18775,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>134725177</v>
+        <v>134725184</v>
       </c>
       <c r="B156" t="n">
         <v>99195</v>
@@ -18871,10 +18826,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>494375</v>
+        <v>494483</v>
       </c>
       <c r="R156" t="n">
-        <v>7006421</v>
+        <v>7006367</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18911,7 +18866,7 @@
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>Minst 60 plantor och 30 blomstjälkar med knopp på gång inom ca 2 m2 yta i granskog.</t>
+          <t>Minst 60 plantor och 4 blomstjälkar med knopp på gång inom ca 2 x 1 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18944,47 +18899,39 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>134725179</v>
+        <v>134724956</v>
       </c>
       <c r="B157" t="n">
-        <v>99195</v>
+        <v>109924</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>220787</v>
+        <v>221184</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Torta</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactuca alpina</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L157" t="inlineStr"/>
@@ -18995,10 +18942,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>494432</v>
+        <v>494484</v>
       </c>
       <c r="R157" t="n">
-        <v>7006477</v>
+        <v>7006603</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -19031,11 +18978,6 @@
       <c r="AA157" t="inlineStr">
         <is>
           <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>Minst 27 plantor och 1 blomstjälk med knopp på gång inom ca 1 m2 yta i äldre granskog.</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -19068,47 +19010,39 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>134725180</v>
+        <v>134724957</v>
       </c>
       <c r="B158" t="n">
-        <v>99195</v>
+        <v>109924</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>220787</v>
+        <v>221184</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Torta</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactuca alpina</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L158" t="inlineStr"/>
@@ -19119,10 +19053,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>494483</v>
+        <v>494462</v>
       </c>
       <c r="R158" t="n">
-        <v>7006405</v>
+        <v>7006579</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -19155,11 +19089,6 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>Minst 200 plantor och 23 blomstjälkar med knopp på gång inom ca 4 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -19192,47 +19121,39 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>134725183</v>
+        <v>134724958</v>
       </c>
       <c r="B159" t="n">
-        <v>99195</v>
+        <v>109924</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>220787</v>
+        <v>221184</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Torta</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactuca alpina</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L159" t="inlineStr"/>
@@ -19243,10 +19164,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>494494</v>
+        <v>494557</v>
       </c>
       <c r="R159" t="n">
-        <v>7006385</v>
+        <v>7006614</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -19279,11 +19200,6 @@
       <c r="AA159" t="inlineStr">
         <is>
           <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>Minst 260 plantor och 12 blomstjälkar med knopp på gång inom ca 2 x 1 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -19316,47 +19232,39 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>134725184</v>
+        <v>134724959</v>
       </c>
       <c r="B160" t="n">
-        <v>99195</v>
+        <v>109924</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>220787</v>
+        <v>221184</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Torta</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactuca alpina</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J160" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L160" t="inlineStr"/>
@@ -19367,10 +19275,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>494483</v>
+        <v>494573</v>
       </c>
       <c r="R160" t="n">
-        <v>7006367</v>
+        <v>7006546</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -19403,11 +19311,6 @@
       <c r="AA160" t="inlineStr">
         <is>
           <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>Minst 60 plantor och 4 blomstjälkar med knopp på gång inom ca 2 x 1 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -19440,7 +19343,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>134724956</v>
+        <v>134724960</v>
       </c>
       <c r="B161" t="n">
         <v>109924</v>
@@ -19483,10 +19386,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>494484</v>
+        <v>494410</v>
       </c>
       <c r="R161" t="n">
-        <v>7006603</v>
+        <v>7006347</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -19551,7 +19454,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>134724957</v>
+        <v>134724961</v>
       </c>
       <c r="B162" t="n">
         <v>109924</v>
@@ -19594,10 +19497,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>494462</v>
+        <v>494440</v>
       </c>
       <c r="R162" t="n">
-        <v>7006579</v>
+        <v>7006466</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -19662,7 +19565,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>134724958</v>
+        <v>134724962</v>
       </c>
       <c r="B163" t="n">
         <v>109924</v>
@@ -19705,10 +19608,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>494557</v>
+        <v>494467</v>
       </c>
       <c r="R163" t="n">
-        <v>7006614</v>
+        <v>7006460</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19773,10 +19676,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>134724959</v>
+        <v>134724939</v>
       </c>
       <c r="B164" t="n">
-        <v>109924</v>
+        <v>106309</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19784,16 +19687,16 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>221184</v>
+        <v>221725</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -19801,11 +19704,19 @@
           <t>(L.) A. Gray</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L164" t="inlineStr"/>
@@ -19816,10 +19727,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>494573</v>
+        <v>494520</v>
       </c>
       <c r="R164" t="n">
-        <v>7006546</v>
+        <v>7006611</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19852,6 +19763,11 @@
       <c r="AA164" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>Minst 10 blomställningar inom ca 3 m2 yta.</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -19884,10 +19800,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>134724960</v>
+        <v>134724940</v>
       </c>
       <c r="B165" t="n">
-        <v>109924</v>
+        <v>106309</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19895,16 +19811,16 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>221184</v>
+        <v>221725</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -19916,7 +19832,7 @@
       <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L165" t="inlineStr"/>
@@ -19927,10 +19843,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>494410</v>
+        <v>494489</v>
       </c>
       <c r="R165" t="n">
-        <v>7006347</v>
+        <v>7006603</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19963,6 +19879,11 @@
       <c r="AA165" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>Minst 2 blomstjälkar.</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19995,10 +19916,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>134724961</v>
+        <v>134724941</v>
       </c>
       <c r="B166" t="n">
-        <v>109924</v>
+        <v>106309</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -20006,16 +19927,16 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>221184</v>
+        <v>221725</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -20027,7 +19948,7 @@
       <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L166" t="inlineStr"/>
@@ -20038,10 +19959,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>494440</v>
+        <v>494485</v>
       </c>
       <c r="R166" t="n">
-        <v>7006466</v>
+        <v>7006591</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -20074,6 +19995,11 @@
       <c r="AA166" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>Minst 2 blomstjälkar.</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -20106,10 +20032,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>134724962</v>
+        <v>134724942</v>
       </c>
       <c r="B167" t="n">
-        <v>109924</v>
+        <v>106309</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -20117,16 +20043,16 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>221184</v>
+        <v>221725</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -20138,7 +20064,7 @@
       <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L167" t="inlineStr"/>
@@ -20149,10 +20075,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>494467</v>
+        <v>494511</v>
       </c>
       <c r="R167" t="n">
-        <v>7006460</v>
+        <v>7006535</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -20185,6 +20111,11 @@
       <c r="AA167" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>Minst 2 blomstjälkar.</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -20217,7 +20148,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>134724939</v>
+        <v>134724943</v>
       </c>
       <c r="B168" t="n">
         <v>106309</v>
@@ -20247,7 +20178,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -20268,10 +20199,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>494520</v>
+        <v>494583</v>
       </c>
       <c r="R168" t="n">
-        <v>7006611</v>
+        <v>7006669</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -20304,11 +20235,6 @@
       <c r="AA168" t="inlineStr">
         <is>
           <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC168" t="inlineStr">
-        <is>
-          <t>Minst 10 blomställningar inom ca 3 m2 yta.</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -20341,7 +20267,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>134724940</v>
+        <v>134724944</v>
       </c>
       <c r="B169" t="n">
         <v>106309</v>
@@ -20369,8 +20295,16 @@
           <t>(L.) A. Gray</t>
         </is>
       </c>
-      <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K169" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -20384,10 +20318,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>494489</v>
+        <v>494437</v>
       </c>
       <c r="R169" t="n">
-        <v>7006603</v>
+        <v>7006395</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -20420,11 +20354,6 @@
       <c r="AA169" t="inlineStr">
         <is>
           <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>Minst 2 blomstjälkar.</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -20457,7 +20386,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>134724941</v>
+        <v>134724945</v>
       </c>
       <c r="B170" t="n">
         <v>106309</v>
@@ -20500,10 +20429,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>494485</v>
+        <v>494436</v>
       </c>
       <c r="R170" t="n">
-        <v>7006591</v>
+        <v>7006408</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -20536,11 +20465,6 @@
       <c r="AA170" t="inlineStr">
         <is>
           <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>Minst 2 blomstjälkar.</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -20573,7 +20497,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>134724942</v>
+        <v>134724947</v>
       </c>
       <c r="B171" t="n">
         <v>106309</v>
@@ -20616,10 +20540,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>494511</v>
+        <v>494450</v>
       </c>
       <c r="R171" t="n">
-        <v>7006535</v>
+        <v>7006398</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -20652,11 +20576,6 @@
       <c r="AA171" t="inlineStr">
         <is>
           <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC171" t="inlineStr">
-        <is>
-          <t>Minst 2 blomstjälkar.</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -20689,7 +20608,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>134724943</v>
+        <v>134724948</v>
       </c>
       <c r="B172" t="n">
         <v>106309</v>
@@ -20717,16 +20636,8 @@
           <t>(L.) A. Gray</t>
         </is>
       </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J172" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -20740,10 +20651,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>494583</v>
+        <v>494409</v>
       </c>
       <c r="R172" t="n">
-        <v>7006669</v>
+        <v>7006335</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -20776,6 +20687,11 @@
       <c r="AA172" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC172" t="inlineStr">
+        <is>
+          <t>Minst 3 blommande plantor.</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -20808,7 +20724,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>134724944</v>
+        <v>134724949</v>
       </c>
       <c r="B173" t="n">
         <v>106309</v>
@@ -20838,7 +20754,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -20859,10 +20775,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>494437</v>
+        <v>494408</v>
       </c>
       <c r="R173" t="n">
-        <v>7006395</v>
+        <v>7006399</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -20895,6 +20811,11 @@
       <c r="AA173" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>Minst 9 blommande plantor inom ca 3 m2 yta.</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -20927,7 +20848,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>134724945</v>
+        <v>134724950</v>
       </c>
       <c r="B174" t="n">
         <v>106309</v>
@@ -20955,8 +20876,16 @@
           <t>(L.) A. Gray</t>
         </is>
       </c>
-      <c r="I174" t="inlineStr"/>
-      <c r="J174" t="inlineStr"/>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K174" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -20970,10 +20899,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>494436</v>
+        <v>494379</v>
       </c>
       <c r="R174" t="n">
-        <v>7006408</v>
+        <v>7006421</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -21006,6 +20935,11 @@
       <c r="AA174" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>Minst två blommande plantor.</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -21038,7 +20972,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>134724947</v>
+        <v>134724951</v>
       </c>
       <c r="B175" t="n">
         <v>106309</v>
@@ -21081,10 +21015,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>494450</v>
+        <v>494420</v>
       </c>
       <c r="R175" t="n">
-        <v>7006398</v>
+        <v>7006474</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -21149,10 +21083,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>134724948</v>
+        <v>134725000</v>
       </c>
       <c r="B176" t="n">
-        <v>106309</v>
+        <v>98060</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21160,30 +21094,26 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>221725</v>
+        <v>221945</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr"/>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K176" t="inlineStr"/>
       <c r="L176" t="inlineStr"/>
       <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
@@ -21192,10 +21122,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>494409</v>
+        <v>494601</v>
       </c>
       <c r="R176" t="n">
-        <v>7006335</v>
+        <v>7006682</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -21232,7 +21162,7 @@
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>Minst 3 blommande plantor.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -21265,10 +21195,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>134724949</v>
+        <v>134725001</v>
       </c>
       <c r="B177" t="n">
-        <v>106309</v>
+        <v>98060</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21276,38 +21206,26 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>221725</v>
+        <v>221945</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr"/>
       <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
@@ -21316,10 +21234,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>494408</v>
+        <v>494477</v>
       </c>
       <c r="R177" t="n">
-        <v>7006399</v>
+        <v>7006369</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -21352,11 +21270,6 @@
       <c r="AA177" t="inlineStr">
         <is>
           <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC177" t="inlineStr">
-        <is>
-          <t>Minst 9 blommande plantor inom ca 3 m2 yta.</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -21389,10 +21302,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>134724950</v>
+        <v>134724974</v>
       </c>
       <c r="B178" t="n">
-        <v>106309</v>
+        <v>99217</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21400,36 +21313,28 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>221725</v>
+        <v>221952</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L178" t="inlineStr"/>
@@ -21440,10 +21345,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>494379</v>
+        <v>494638</v>
       </c>
       <c r="R178" t="n">
-        <v>7006421</v>
+        <v>7006684</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -21476,11 +21381,6 @@
       <c r="AA178" t="inlineStr">
         <is>
           <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC178" t="inlineStr">
-        <is>
-          <t>Minst två blommande plantor.</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -21513,10 +21413,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>134724951</v>
+        <v>134724975</v>
       </c>
       <c r="B179" t="n">
-        <v>106309</v>
+        <v>99217</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21524,21 +21424,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>221725</v>
+        <v>221952</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -21556,10 +21456,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>494420</v>
+        <v>494542</v>
       </c>
       <c r="R179" t="n">
-        <v>7006474</v>
+        <v>7006561</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -21624,10 +21524,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>134725000</v>
+        <v>134724976</v>
       </c>
       <c r="B180" t="n">
-        <v>98060</v>
+        <v>99217</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21635,26 +21535,30 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr"/>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr"/>
       <c r="N180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
@@ -21663,10 +21567,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>494601</v>
+        <v>494597</v>
       </c>
       <c r="R180" t="n">
-        <v>7006682</v>
+        <v>7006574</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -21699,11 +21603,6 @@
       <c r="AA180" t="inlineStr">
         <is>
           <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC180" t="inlineStr">
-        <is>
-          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -21736,10 +21635,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>134725001</v>
+        <v>134724977</v>
       </c>
       <c r="B181" t="n">
-        <v>98060</v>
+        <v>99217</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21747,26 +21646,30 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr"/>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr"/>
       <c r="N181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
@@ -21775,10 +21678,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>494477</v>
+        <v>494573</v>
       </c>
       <c r="R181" t="n">
-        <v>7006369</v>
+        <v>7006537</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -21843,7 +21746,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>134724974</v>
+        <v>134724978</v>
       </c>
       <c r="B182" t="n">
         <v>99217</v>
@@ -21886,10 +21789,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>494638</v>
+        <v>494423</v>
       </c>
       <c r="R182" t="n">
-        <v>7006684</v>
+        <v>7006438</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -21954,7 +21857,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>134724975</v>
+        <v>134724979</v>
       </c>
       <c r="B183" t="n">
         <v>99217</v>
@@ -21997,10 +21900,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>494542</v>
+        <v>494456</v>
       </c>
       <c r="R183" t="n">
-        <v>7006561</v>
+        <v>7006428</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -22065,7 +21968,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>134724976</v>
+        <v>134724980</v>
       </c>
       <c r="B184" t="n">
         <v>99217</v>
@@ -22108,10 +22011,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>494597</v>
+        <v>494430</v>
       </c>
       <c r="R184" t="n">
-        <v>7006574</v>
+        <v>7006412</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -22176,7 +22079,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>134724977</v>
+        <v>134724981</v>
       </c>
       <c r="B185" t="n">
         <v>99217</v>
@@ -22219,10 +22122,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>494573</v>
+        <v>494444</v>
       </c>
       <c r="R185" t="n">
-        <v>7006537</v>
+        <v>7006367</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -22287,7 +22190,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>134724978</v>
+        <v>134724982</v>
       </c>
       <c r="B186" t="n">
         <v>99217</v>
@@ -22319,7 +22222,7 @@
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L186" t="inlineStr"/>
@@ -22330,10 +22233,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>494423</v>
+        <v>494422</v>
       </c>
       <c r="R186" t="n">
-        <v>7006438</v>
+        <v>7006345</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -22398,7 +22301,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>134724979</v>
+        <v>134724983</v>
       </c>
       <c r="B187" t="n">
         <v>99217</v>
@@ -22441,10 +22344,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>494456</v>
+        <v>494422</v>
       </c>
       <c r="R187" t="n">
-        <v>7006428</v>
+        <v>7006322</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -22509,7 +22412,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>134724980</v>
+        <v>134724984</v>
       </c>
       <c r="B188" t="n">
         <v>99217</v>
@@ -22552,10 +22455,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>494430</v>
+        <v>494424</v>
       </c>
       <c r="R188" t="n">
-        <v>7006412</v>
+        <v>7006352</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -22620,7 +22523,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>134724981</v>
+        <v>134724985</v>
       </c>
       <c r="B189" t="n">
         <v>99217</v>
@@ -22663,10 +22566,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>494444</v>
+        <v>494396</v>
       </c>
       <c r="R189" t="n">
-        <v>7006367</v>
+        <v>7006361</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -22731,7 +22634,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>134724982</v>
+        <v>134724986</v>
       </c>
       <c r="B190" t="n">
         <v>99217</v>
@@ -22774,10 +22677,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>494422</v>
+        <v>494373</v>
       </c>
       <c r="R190" t="n">
-        <v>7006345</v>
+        <v>7006366</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -22842,7 +22745,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>134724983</v>
+        <v>134724987</v>
       </c>
       <c r="B191" t="n">
         <v>99217</v>
@@ -22885,10 +22788,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>494422</v>
+        <v>494404</v>
       </c>
       <c r="R191" t="n">
-        <v>7006322</v>
+        <v>7006377</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -22953,7 +22856,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>134724984</v>
+        <v>134724988</v>
       </c>
       <c r="B192" t="n">
         <v>99217</v>
@@ -22996,10 +22899,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>494424</v>
+        <v>494406</v>
       </c>
       <c r="R192" t="n">
-        <v>7006352</v>
+        <v>7006398</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -23064,7 +22967,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>134724985</v>
+        <v>134724989</v>
       </c>
       <c r="B193" t="n">
         <v>99217</v>
@@ -23107,10 +23010,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>494396</v>
+        <v>494379</v>
       </c>
       <c r="R193" t="n">
-        <v>7006361</v>
+        <v>7006433</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -23175,7 +23078,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>134724986</v>
+        <v>134724990</v>
       </c>
       <c r="B194" t="n">
         <v>99217</v>
@@ -23218,10 +23121,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>494373</v>
+        <v>494377</v>
       </c>
       <c r="R194" t="n">
-        <v>7006366</v>
+        <v>7006414</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -23286,7 +23189,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>134724987</v>
+        <v>134724991</v>
       </c>
       <c r="B195" t="n">
         <v>99217</v>
@@ -23329,10 +23232,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>494404</v>
+        <v>494399</v>
       </c>
       <c r="R195" t="n">
-        <v>7006377</v>
+        <v>7006417</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -23397,7 +23300,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>134724988</v>
+        <v>134724992</v>
       </c>
       <c r="B196" t="n">
         <v>99217</v>
@@ -23440,10 +23343,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>494406</v>
+        <v>494413</v>
       </c>
       <c r="R196" t="n">
-        <v>7006398</v>
+        <v>7006440</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -23508,7 +23411,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>134724989</v>
+        <v>134724993</v>
       </c>
       <c r="B197" t="n">
         <v>99217</v>
@@ -23551,10 +23454,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>494379</v>
+        <v>494486</v>
       </c>
       <c r="R197" t="n">
-        <v>7006433</v>
+        <v>7006376</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -23619,7 +23522,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>134724990</v>
+        <v>134724994</v>
       </c>
       <c r="B198" t="n">
         <v>99217</v>
@@ -23662,10 +23565,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>494377</v>
+        <v>494470</v>
       </c>
       <c r="R198" t="n">
-        <v>7006414</v>
+        <v>7006387</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -23730,10 +23633,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>134724991</v>
+        <v>134724964</v>
       </c>
       <c r="B199" t="n">
-        <v>99217</v>
+        <v>104707</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23741,28 +23644,36 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>221952</v>
+        <v>222412</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr"/>
-      <c r="J199" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L199" t="inlineStr"/>
@@ -23773,10 +23684,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>494399</v>
+        <v>494391</v>
       </c>
       <c r="R199" t="n">
-        <v>7006417</v>
+        <v>7006443</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -23841,10 +23752,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>134724992</v>
+        <v>129402373</v>
       </c>
       <c r="B200" t="n">
-        <v>99217</v>
+        <v>101325</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23852,45 +23763,42 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>221952</v>
+        <v>222498</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
-      <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L200" t="inlineStr"/>
-      <c r="N200" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Bergmyren-Barnsängbäcken, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>494413</v>
+        <v>494761</v>
       </c>
       <c r="R200" t="n">
-        <v>7006440</v>
+        <v>7006746</v>
       </c>
       <c r="S200" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -23914,12 +23822,22 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="Z200" t="inlineStr">
+        <is>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB200" t="inlineStr">
+        <is>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -23928,7 +23846,6 @@
       <c r="AE200" t="b">
         <v>0</v>
       </c>
-      <c r="AF200" t="inlineStr"/>
       <c r="AG200" t="b">
         <v>0</v>
       </c>
@@ -23952,10 +23869,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>134724993</v>
+        <v>129402502</v>
       </c>
       <c r="B201" t="n">
-        <v>99217</v>
+        <v>101325</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -23963,42 +23880,39 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>221952</v>
+        <v>222498</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
-      <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L201" t="inlineStr"/>
-      <c r="N201" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Bergmyren-Barnsängbäcken, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>494486</v>
+        <v>494737</v>
       </c>
       <c r="R201" t="n">
-        <v>7006376</v>
+        <v>7006737</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -24025,12 +23939,22 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="Z201" t="inlineStr">
+        <is>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB201" t="inlineStr">
+        <is>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -24039,7 +23963,6 @@
       <c r="AE201" t="b">
         <v>0</v>
       </c>
-      <c r="AF201" t="inlineStr"/>
       <c r="AG201" t="b">
         <v>0</v>
       </c>
@@ -24063,10 +23986,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>134724994</v>
+        <v>134725228</v>
       </c>
       <c r="B202" t="n">
-        <v>99217</v>
+        <v>101403</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24074,28 +23997,28 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>221952</v>
+        <v>222498</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
       <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L202" t="inlineStr"/>
@@ -24106,10 +24029,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>494470</v>
+        <v>494729</v>
       </c>
       <c r="R202" t="n">
-        <v>7006387</v>
+        <v>7006733</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -24174,10 +24097,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>134724964</v>
+        <v>134725229</v>
       </c>
       <c r="B203" t="n">
-        <v>104707</v>
+        <v>101403</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24185,33 +24108,25 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I203" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J203" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr"/>
+      <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -24225,10 +24140,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>494391</v>
+        <v>494684</v>
       </c>
       <c r="R203" t="n">
-        <v>7006443</v>
+        <v>7006730</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -24293,10 +24208,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129402373</v>
+        <v>134725230</v>
       </c>
       <c r="B204" t="n">
-        <v>101325</v>
+        <v>101403</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -24322,24 +24237,27 @@
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
+      <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L204" t="inlineStr"/>
+      <c r="N204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren-Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>494761</v>
+        <v>494561</v>
       </c>
       <c r="R204" t="n">
-        <v>7006746</v>
+        <v>7006650</v>
       </c>
       <c r="S204" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -24363,22 +24281,12 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="Z204" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB204" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -24387,6 +24295,7 @@
       <c r="AE204" t="b">
         <v>0</v>
       </c>
+      <c r="AF204" t="inlineStr"/>
       <c r="AG204" t="b">
         <v>0</v>
       </c>
@@ -24410,10 +24319,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129402502</v>
+        <v>134725231</v>
       </c>
       <c r="B205" t="n">
-        <v>101325</v>
+        <v>101403</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24439,21 +24348,24 @@
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
+      <c r="J205" t="inlineStr"/>
       <c r="K205" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L205" t="inlineStr"/>
+      <c r="N205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren-Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>494737</v>
+        <v>494575</v>
       </c>
       <c r="R205" t="n">
-        <v>7006737</v>
+        <v>7006614</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -24480,22 +24392,12 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="Z205" t="inlineStr">
-        <is>
-          <t>12:31</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB205" t="inlineStr">
-        <is>
-          <t>12:31</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -24504,6 +24406,7 @@
       <c r="AE205" t="b">
         <v>0</v>
       </c>
+      <c r="AF205" t="inlineStr"/>
       <c r="AG205" t="b">
         <v>0</v>
       </c>
@@ -24527,7 +24430,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>134725228</v>
+        <v>134725232</v>
       </c>
       <c r="B206" t="n">
         <v>101403</v>
@@ -24570,10 +24473,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>494729</v>
+        <v>494431</v>
       </c>
       <c r="R206" t="n">
-        <v>7006733</v>
+        <v>7006385</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -24638,7 +24541,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>134725229</v>
+        <v>134725233</v>
       </c>
       <c r="B207" t="n">
         <v>101403</v>
@@ -24681,10 +24584,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>494684</v>
+        <v>494410</v>
       </c>
       <c r="R207" t="n">
-        <v>7006730</v>
+        <v>7006372</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -24749,7 +24652,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>134725230</v>
+        <v>134725234</v>
       </c>
       <c r="B208" t="n">
         <v>101403</v>
@@ -24792,10 +24695,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>494561</v>
+        <v>494461</v>
       </c>
       <c r="R208" t="n">
-        <v>7006650</v>
+        <v>7006391</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -24860,7 +24763,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>134725231</v>
+        <v>134725235</v>
       </c>
       <c r="B209" t="n">
         <v>101403</v>
@@ -24903,10 +24806,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>494575</v>
+        <v>494467</v>
       </c>
       <c r="R209" t="n">
-        <v>7006614</v>
+        <v>7006362</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -24971,7 +24874,7 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>134725232</v>
+        <v>134725237</v>
       </c>
       <c r="B210" t="n">
         <v>101403</v>
@@ -25014,10 +24917,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>494431</v>
+        <v>494394</v>
       </c>
       <c r="R210" t="n">
-        <v>7006385</v>
+        <v>7006333</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -25082,7 +24985,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>134725233</v>
+        <v>134725238</v>
       </c>
       <c r="B211" t="n">
         <v>101403</v>
@@ -25125,10 +25028,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>494410</v>
+        <v>494393</v>
       </c>
       <c r="R211" t="n">
-        <v>7006372</v>
+        <v>7006434</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -25193,7 +25096,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>134725234</v>
+        <v>134725239</v>
       </c>
       <c r="B212" t="n">
         <v>101403</v>
@@ -25236,10 +25139,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>494461</v>
+        <v>494417</v>
       </c>
       <c r="R212" t="n">
-        <v>7006391</v>
+        <v>7006455</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -25304,7 +25207,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>134725235</v>
+        <v>134725240</v>
       </c>
       <c r="B213" t="n">
         <v>101403</v>
@@ -25347,10 +25250,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>494467</v>
+        <v>494423</v>
       </c>
       <c r="R213" t="n">
-        <v>7006362</v>
+        <v>7006466</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -25415,7 +25318,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>134725237</v>
+        <v>134725241</v>
       </c>
       <c r="B214" t="n">
         <v>101403</v>
@@ -25458,10 +25361,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>494394</v>
+        <v>494447</v>
       </c>
       <c r="R214" t="n">
-        <v>7006333</v>
+        <v>7006467</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -25526,7 +25429,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>134725238</v>
+        <v>134725242</v>
       </c>
       <c r="B215" t="n">
         <v>101403</v>
@@ -25569,10 +25472,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>494393</v>
+        <v>494490</v>
       </c>
       <c r="R215" t="n">
-        <v>7006434</v>
+        <v>7006391</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -25637,10 +25540,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>134725239</v>
+        <v>134724965</v>
       </c>
       <c r="B216" t="n">
-        <v>101403</v>
+        <v>101305</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -25648,28 +25551,28 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
       <c r="J216" t="inlineStr"/>
       <c r="K216" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L216" t="inlineStr"/>
@@ -25680,10 +25583,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>494417</v>
+        <v>494525</v>
       </c>
       <c r="R216" t="n">
-        <v>7006455</v>
+        <v>7006631</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -25748,10 +25651,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>134725240</v>
+        <v>134724967</v>
       </c>
       <c r="B217" t="n">
-        <v>101403</v>
+        <v>101305</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -25759,28 +25662,28 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
       <c r="J217" t="inlineStr"/>
       <c r="K217" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L217" t="inlineStr"/>
@@ -25791,10 +25694,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>494423</v>
+        <v>494404</v>
       </c>
       <c r="R217" t="n">
-        <v>7006466</v>
+        <v>7006352</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -25859,10 +25762,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>134725241</v>
+        <v>134724970</v>
       </c>
       <c r="B218" t="n">
-        <v>101403</v>
+        <v>101305</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25870,28 +25773,36 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I218" t="inlineStr"/>
-      <c r="J218" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L218" t="inlineStr"/>
@@ -25902,10 +25813,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>494447</v>
+        <v>494394</v>
       </c>
       <c r="R218" t="n">
-        <v>7006467</v>
+        <v>7006335</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -25938,6 +25849,11 @@
       <c r="AA218" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC218" t="inlineStr">
+        <is>
+          <t>Svart trolldruva som här täcker minst 7 m2 yta i ett ca 10-15 meter långt högörtsstråk. Både blomning och utblommad i frukt.</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -25970,10 +25886,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>134725242</v>
+        <v>134725065</v>
       </c>
       <c r="B219" t="n">
-        <v>101403</v>
+        <v>99472</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -25981,28 +25897,28 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>222498</v>
+        <v>222812</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Convallaria majalis</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
       <c r="J219" t="inlineStr"/>
       <c r="K219" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L219" t="inlineStr"/>
@@ -26013,10 +25929,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>494490</v>
+        <v>494588</v>
       </c>
       <c r="R219" t="n">
-        <v>7006391</v>
+        <v>7006682</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -26081,10 +25997,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>134724965</v>
+        <v>134725066</v>
       </c>
       <c r="B220" t="n">
-        <v>101305</v>
+        <v>99472</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -26092,16 +26008,16 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>222771</v>
+        <v>222812</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Convallaria majalis</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -26113,7 +26029,7 @@
       <c r="J220" t="inlineStr"/>
       <c r="K220" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L220" t="inlineStr"/>
@@ -26124,10 +26040,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>494525</v>
+        <v>494575</v>
       </c>
       <c r="R220" t="n">
-        <v>7006631</v>
+        <v>7006657</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -26192,10 +26108,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>134724967</v>
+        <v>134725067</v>
       </c>
       <c r="B221" t="n">
-        <v>101305</v>
+        <v>99472</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26203,16 +26119,16 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>222771</v>
+        <v>222812</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Convallaria majalis</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -26235,10 +26151,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>494404</v>
+        <v>494403</v>
       </c>
       <c r="R221" t="n">
-        <v>7006352</v>
+        <v>7006330</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -26303,10 +26219,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>134724970</v>
+        <v>134725222</v>
       </c>
       <c r="B222" t="n">
-        <v>101305</v>
+        <v>99504</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26314,33 +26230,25 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>222771</v>
+        <v>222857</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ekorrbär</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Maianthemum bifolium</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I222" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J222" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) F. W. Schmidt</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr"/>
+      <c r="J222" t="inlineStr"/>
       <c r="K222" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -26354,10 +26262,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>494394</v>
+        <v>494531</v>
       </c>
       <c r="R222" t="n">
-        <v>7006335</v>
+        <v>7006621</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -26390,11 +26298,6 @@
       <c r="AA222" t="inlineStr">
         <is>
           <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC222" t="inlineStr">
-        <is>
-          <t>Svart trolldruva som här täcker minst 7 m2 yta i ett ca 10-15 meter långt högörtsstråk. Både blomning och utblommad i frukt.</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -26427,10 +26330,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>134725065</v>
+        <v>134725223</v>
       </c>
       <c r="B223" t="n">
-        <v>99472</v>
+        <v>99504</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -26438,21 +26341,21 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>222812</v>
+        <v>222857</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Ekorrbär</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Maianthemum bifolium</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) F. W. Schmidt</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -26470,10 +26373,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>494588</v>
+        <v>494476</v>
       </c>
       <c r="R223" t="n">
-        <v>7006682</v>
+        <v>7006370</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -26538,10 +26441,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>134725066</v>
+        <v>134725190</v>
       </c>
       <c r="B224" t="n">
-        <v>99472</v>
+        <v>102871</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -26549,16 +26452,16 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>222812</v>
+        <v>223037</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Humleblomster</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Geum rivale</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -26581,10 +26484,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>494575</v>
+        <v>494603</v>
       </c>
       <c r="R224" t="n">
-        <v>7006657</v>
+        <v>7006548</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -26649,10 +26552,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>134725067</v>
+        <v>134725192</v>
       </c>
       <c r="B225" t="n">
-        <v>99472</v>
+        <v>102871</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26660,16 +26563,16 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>222812</v>
+        <v>223037</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Humleblomster</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Geum rivale</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -26681,7 +26584,7 @@
       <c r="J225" t="inlineStr"/>
       <c r="K225" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L225" t="inlineStr"/>
@@ -26692,10 +26595,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>494403</v>
+        <v>494533</v>
       </c>
       <c r="R225" t="n">
-        <v>7006330</v>
+        <v>7006513</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -26760,10 +26663,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>134725222</v>
+        <v>134725002</v>
       </c>
       <c r="B226" t="n">
-        <v>99504</v>
+        <v>99001</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -26771,28 +26674,28 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>222857</v>
+        <v>223049</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Ekorrbär</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Maianthemum bifolium</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(L.) F. W. Schmidt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
       <c r="J226" t="inlineStr"/>
       <c r="K226" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L226" t="inlineStr"/>
@@ -26803,10 +26706,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>494531</v>
+        <v>494743</v>
       </c>
       <c r="R226" t="n">
-        <v>7006621</v>
+        <v>7006752</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -26871,10 +26774,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>134725223</v>
+        <v>134725003</v>
       </c>
       <c r="B227" t="n">
-        <v>99504</v>
+        <v>99001</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -26882,28 +26785,28 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>222857</v>
+        <v>223049</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Ekorrbär</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Maianthemum bifolium</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(L.) F. W. Schmidt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
       <c r="J227" t="inlineStr"/>
       <c r="K227" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L227" t="inlineStr"/>
@@ -26914,10 +26817,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>494476</v>
+        <v>494682</v>
       </c>
       <c r="R227" t="n">
-        <v>7006370</v>
+        <v>7006728</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -26982,10 +26885,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>134725190</v>
+        <v>134725004</v>
       </c>
       <c r="B228" t="n">
-        <v>102871</v>
+        <v>99001</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -26993,16 +26896,16 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>223037</v>
+        <v>223049</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Humleblomster</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Geum rivale</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -27014,7 +26917,7 @@
       <c r="J228" t="inlineStr"/>
       <c r="K228" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L228" t="inlineStr"/>
@@ -27025,10 +26928,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>494603</v>
+        <v>494658</v>
       </c>
       <c r="R228" t="n">
-        <v>7006548</v>
+        <v>7006681</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -27093,10 +26996,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>134725192</v>
+        <v>134725005</v>
       </c>
       <c r="B229" t="n">
-        <v>102871</v>
+        <v>99001</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -27104,16 +27007,16 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>223037</v>
+        <v>223049</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Humleblomster</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Geum rivale</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -27125,7 +27028,7 @@
       <c r="J229" t="inlineStr"/>
       <c r="K229" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L229" t="inlineStr"/>
@@ -27136,10 +27039,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>494533</v>
+        <v>494555</v>
       </c>
       <c r="R229" t="n">
-        <v>7006513</v>
+        <v>7006634</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -27204,7 +27107,7 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>134725002</v>
+        <v>134725006</v>
       </c>
       <c r="B230" t="n">
         <v>99001</v>
@@ -27236,7 +27139,7 @@
       <c r="J230" t="inlineStr"/>
       <c r="K230" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L230" t="inlineStr"/>
@@ -27247,10 +27150,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>494743</v>
+        <v>494526</v>
       </c>
       <c r="R230" t="n">
-        <v>7006752</v>
+        <v>7006591</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -27315,7 +27218,7 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>134725003</v>
+        <v>134725007</v>
       </c>
       <c r="B231" t="n">
         <v>99001</v>
@@ -27358,10 +27261,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>494682</v>
+        <v>494592</v>
       </c>
       <c r="R231" t="n">
-        <v>7006728</v>
+        <v>7006574</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -27426,7 +27329,7 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>134725004</v>
+        <v>134725008</v>
       </c>
       <c r="B232" t="n">
         <v>99001</v>
@@ -27469,10 +27372,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>494658</v>
+        <v>494605</v>
       </c>
       <c r="R232" t="n">
-        <v>7006681</v>
+        <v>7006636</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -27537,7 +27440,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>134725005</v>
+        <v>134725009</v>
       </c>
       <c r="B233" t="n">
         <v>99001</v>
@@ -27569,7 +27472,7 @@
       <c r="J233" t="inlineStr"/>
       <c r="K233" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L233" t="inlineStr"/>
@@ -27580,10 +27483,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>494555</v>
+        <v>494569</v>
       </c>
       <c r="R233" t="n">
-        <v>7006634</v>
+        <v>7006663</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -27648,7 +27551,7 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>134725006</v>
+        <v>134725010</v>
       </c>
       <c r="B234" t="n">
         <v>99001</v>
@@ -27691,10 +27594,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>494526</v>
+        <v>494578</v>
       </c>
       <c r="R234" t="n">
-        <v>7006591</v>
+        <v>7006546</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -27759,7 +27662,7 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>134725007</v>
+        <v>134725011</v>
       </c>
       <c r="B235" t="n">
         <v>99001</v>
@@ -27791,7 +27694,7 @@
       <c r="J235" t="inlineStr"/>
       <c r="K235" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L235" t="inlineStr"/>
@@ -27802,10 +27705,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>494592</v>
+        <v>494543</v>
       </c>
       <c r="R235" t="n">
-        <v>7006574</v>
+        <v>7006535</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -27870,7 +27773,7 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>134725008</v>
+        <v>134725012</v>
       </c>
       <c r="B236" t="n">
         <v>99001</v>
@@ -27902,7 +27805,7 @@
       <c r="J236" t="inlineStr"/>
       <c r="K236" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L236" t="inlineStr"/>
@@ -27913,10 +27816,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>494605</v>
+        <v>494505</v>
       </c>
       <c r="R236" t="n">
-        <v>7006636</v>
+        <v>7006509</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -27981,7 +27884,7 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>134725009</v>
+        <v>134725013</v>
       </c>
       <c r="B237" t="n">
         <v>99001</v>
@@ -28024,10 +27927,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>494569</v>
+        <v>494397</v>
       </c>
       <c r="R237" t="n">
-        <v>7006663</v>
+        <v>7006333</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -28092,7 +27995,7 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>134725010</v>
+        <v>134725014</v>
       </c>
       <c r="B238" t="n">
         <v>99001</v>
@@ -28124,7 +28027,7 @@
       <c r="J238" t="inlineStr"/>
       <c r="K238" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L238" t="inlineStr"/>
@@ -28135,10 +28038,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>494578</v>
+        <v>494366</v>
       </c>
       <c r="R238" t="n">
-        <v>7006546</v>
+        <v>7006343</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -28203,7 +28106,7 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>134725011</v>
+        <v>134725015</v>
       </c>
       <c r="B239" t="n">
         <v>99001</v>
@@ -28246,10 +28149,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>494543</v>
+        <v>494447</v>
       </c>
       <c r="R239" t="n">
-        <v>7006535</v>
+        <v>7006486</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -28314,7 +28217,7 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>134725012</v>
+        <v>134725016</v>
       </c>
       <c r="B240" t="n">
         <v>99001</v>
@@ -28346,7 +28249,7 @@
       <c r="J240" t="inlineStr"/>
       <c r="K240" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L240" t="inlineStr"/>
@@ -28357,10 +28260,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>494505</v>
+        <v>494442</v>
       </c>
       <c r="R240" t="n">
-        <v>7006509</v>
+        <v>7006455</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -28425,7 +28328,7 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>134725013</v>
+        <v>134725017</v>
       </c>
       <c r="B241" t="n">
         <v>99001</v>
@@ -28468,10 +28371,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>494397</v>
+        <v>494436</v>
       </c>
       <c r="R241" t="n">
-        <v>7006333</v>
+        <v>7006500</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -28536,7 +28439,7 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>134725014</v>
+        <v>134725018</v>
       </c>
       <c r="B242" t="n">
         <v>99001</v>
@@ -28579,10 +28482,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>494366</v>
+        <v>494469</v>
       </c>
       <c r="R242" t="n">
-        <v>7006343</v>
+        <v>7006406</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -28647,10 +28550,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>134725015</v>
+        <v>134725194</v>
       </c>
       <c r="B243" t="n">
-        <v>99001</v>
+        <v>98249</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -28658,21 +28561,21 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>223049</v>
+        <v>223358</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -28690,10 +28593,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>494447</v>
+        <v>494649</v>
       </c>
       <c r="R243" t="n">
-        <v>7006486</v>
+        <v>7006702</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -28758,10 +28661,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>134725016</v>
+        <v>134725195</v>
       </c>
       <c r="B244" t="n">
-        <v>99001</v>
+        <v>98249</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -28769,21 +28672,21 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>223049</v>
+        <v>223358</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
@@ -28801,10 +28704,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>494442</v>
+        <v>494656</v>
       </c>
       <c r="R244" t="n">
-        <v>7006455</v>
+        <v>7006675</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -28837,6 +28740,11 @@
       <c r="AA244" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC244" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -28869,10 +28777,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>134725017</v>
+        <v>134725197</v>
       </c>
       <c r="B245" t="n">
-        <v>99001</v>
+        <v>98249</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -28880,21 +28788,21 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>223049</v>
+        <v>223358</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -28912,10 +28820,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>494436</v>
+        <v>494555</v>
       </c>
       <c r="R245" t="n">
-        <v>7006500</v>
+        <v>7006667</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -28980,10 +28888,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>134725018</v>
+        <v>134725198</v>
       </c>
       <c r="B246" t="n">
-        <v>99001</v>
+        <v>98249</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -28991,21 +28899,21 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>223049</v>
+        <v>223358</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -29023,10 +28931,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>494469</v>
+        <v>494482</v>
       </c>
       <c r="R246" t="n">
-        <v>7006406</v>
+        <v>7006602</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -29091,7 +28999,7 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>134725194</v>
+        <v>134725200</v>
       </c>
       <c r="B247" t="n">
         <v>98249</v>
@@ -29134,10 +29042,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>494649</v>
+        <v>494610</v>
       </c>
       <c r="R247" t="n">
-        <v>7006702</v>
+        <v>7006669</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -29202,7 +29110,7 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>134725195</v>
+        <v>134725201</v>
       </c>
       <c r="B248" t="n">
         <v>98249</v>
@@ -29245,10 +29153,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>494656</v>
+        <v>494574</v>
       </c>
       <c r="R248" t="n">
-        <v>7006675</v>
+        <v>7006545</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -29281,11 +29189,6 @@
       <c r="AA248" t="inlineStr">
         <is>
           <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC248" t="inlineStr">
-        <is>
-          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -29318,7 +29221,7 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>134725197</v>
+        <v>134725203</v>
       </c>
       <c r="B249" t="n">
         <v>98249</v>
@@ -29361,10 +29264,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>494555</v>
+        <v>494447</v>
       </c>
       <c r="R249" t="n">
-        <v>7006667</v>
+        <v>7006429</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -29429,7 +29332,7 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>134725198</v>
+        <v>134725205</v>
       </c>
       <c r="B250" t="n">
         <v>98249</v>
@@ -29472,10 +29375,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>494482</v>
+        <v>494390</v>
       </c>
       <c r="R250" t="n">
-        <v>7006602</v>
+        <v>7006347</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -29508,6 +29411,11 @@
       <c r="AA250" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC250" t="inlineStr">
+        <is>
+          <t>Rikligt med hultbräken i ett frodigt fältskikt.</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -29540,7 +29448,7 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>134725200</v>
+        <v>134725206</v>
       </c>
       <c r="B251" t="n">
         <v>98249</v>
@@ -29583,10 +29491,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>494610</v>
+        <v>494401</v>
       </c>
       <c r="R251" t="n">
-        <v>7006669</v>
+        <v>7006335</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -29619,6 +29527,11 @@
       <c r="AA251" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC251" t="inlineStr">
+        <is>
+          <t>Rikligt med hultbräken på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -29651,7 +29564,7 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>134725201</v>
+        <v>134725208</v>
       </c>
       <c r="B252" t="n">
         <v>98249</v>
@@ -29694,10 +29607,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>494574</v>
+        <v>494394</v>
       </c>
       <c r="R252" t="n">
-        <v>7006545</v>
+        <v>7006324</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -29762,7 +29675,7 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>134725203</v>
+        <v>134725209</v>
       </c>
       <c r="B253" t="n">
         <v>98249</v>
@@ -29805,10 +29718,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>494447</v>
+        <v>494368</v>
       </c>
       <c r="R253" t="n">
-        <v>7006429</v>
+        <v>7006343</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -29873,7 +29786,7 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>134725205</v>
+        <v>134725211</v>
       </c>
       <c r="B254" t="n">
         <v>98249</v>
@@ -29916,10 +29829,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>494390</v>
+        <v>494422</v>
       </c>
       <c r="R254" t="n">
-        <v>7006347</v>
+        <v>7006467</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -29952,11 +29865,6 @@
       <c r="AA254" t="inlineStr">
         <is>
           <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC254" t="inlineStr">
-        <is>
-          <t>Rikligt med hultbräken i ett frodigt fältskikt.</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -29989,7 +29897,7 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>134725206</v>
+        <v>134725212</v>
       </c>
       <c r="B255" t="n">
         <v>98249</v>
@@ -30032,10 +29940,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>494401</v>
+        <v>494439</v>
       </c>
       <c r="R255" t="n">
-        <v>7006335</v>
+        <v>7006466</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -30068,11 +29976,6 @@
       <c r="AA255" t="inlineStr">
         <is>
           <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC255" t="inlineStr">
-        <is>
-          <t>Rikligt med hultbräken på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -30105,7 +30008,7 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>134725208</v>
+        <v>134725213</v>
       </c>
       <c r="B256" t="n">
         <v>98249</v>
@@ -30148,10 +30051,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>494394</v>
+        <v>494471</v>
       </c>
       <c r="R256" t="n">
-        <v>7006324</v>
+        <v>7006477</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -30216,10 +30119,10 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>134725209</v>
+        <v>134725019</v>
       </c>
       <c r="B257" t="n">
-        <v>98249</v>
+        <v>101293</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -30227,28 +30130,28 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>223358</v>
+        <v>224885</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
       <c r="J257" t="inlineStr"/>
       <c r="K257" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L257" t="inlineStr"/>
@@ -30259,10 +30162,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>494368</v>
+        <v>494758</v>
       </c>
       <c r="R257" t="n">
-        <v>7006343</v>
+        <v>7006733</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -30327,10 +30230,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>134725211</v>
+        <v>134725020</v>
       </c>
       <c r="B258" t="n">
-        <v>98249</v>
+        <v>101293</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -30338,28 +30241,28 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>223358</v>
+        <v>224885</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
       <c r="J258" t="inlineStr"/>
       <c r="K258" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L258" t="inlineStr"/>
@@ -30370,10 +30273,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>494422</v>
+        <v>494754</v>
       </c>
       <c r="R258" t="n">
-        <v>7006467</v>
+        <v>7006740</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -30438,10 +30341,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>134725212</v>
+        <v>134725021</v>
       </c>
       <c r="B259" t="n">
-        <v>98249</v>
+        <v>101293</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -30449,28 +30352,28 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>223358</v>
+        <v>224885</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
       <c r="J259" t="inlineStr"/>
       <c r="K259" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L259" t="inlineStr"/>
@@ -30481,10 +30384,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>494439</v>
+        <v>494727</v>
       </c>
       <c r="R259" t="n">
-        <v>7006466</v>
+        <v>7006747</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -30549,10 +30452,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>134725213</v>
+        <v>134725022</v>
       </c>
       <c r="B260" t="n">
-        <v>98249</v>
+        <v>101293</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -30560,28 +30463,28 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>223358</v>
+        <v>224885</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
       <c r="J260" t="inlineStr"/>
       <c r="K260" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L260" t="inlineStr"/>
@@ -30592,10 +30495,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>494471</v>
+        <v>494537</v>
       </c>
       <c r="R260" t="n">
-        <v>7006477</v>
+        <v>7006666</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -30660,7 +30563,7 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>134725019</v>
+        <v>134725023</v>
       </c>
       <c r="B261" t="n">
         <v>101293</v>
@@ -30703,10 +30606,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>494758</v>
+        <v>494554</v>
       </c>
       <c r="R261" t="n">
-        <v>7006733</v>
+        <v>7006673</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -30771,7 +30674,7 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>134725020</v>
+        <v>134725024</v>
       </c>
       <c r="B262" t="n">
         <v>101293</v>
@@ -30814,10 +30717,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>494754</v>
+        <v>494513</v>
       </c>
       <c r="R262" t="n">
-        <v>7006740</v>
+        <v>7006628</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -30882,7 +30785,7 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>134725021</v>
+        <v>134725025</v>
       </c>
       <c r="B263" t="n">
         <v>101293</v>
@@ -30925,10 +30828,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>494727</v>
+        <v>494500</v>
       </c>
       <c r="R263" t="n">
-        <v>7006747</v>
+        <v>7006617</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -30961,6 +30864,11 @@
       <c r="AA263" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC263" t="inlineStr">
+        <is>
+          <t>Rikligt vid en bäck.</t>
         </is>
       </c>
       <c r="AD263" t="b">
@@ -30993,7 +30901,7 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>134725022</v>
+        <v>134725026</v>
       </c>
       <c r="B264" t="n">
         <v>101293</v>
@@ -31036,10 +30944,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>494537</v>
+        <v>494475</v>
       </c>
       <c r="R264" t="n">
-        <v>7006666</v>
+        <v>7006607</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -31072,6 +30980,11 @@
       <c r="AA264" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC264" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD264" t="b">
@@ -31104,7 +31017,7 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>134725023</v>
+        <v>134725027</v>
       </c>
       <c r="B265" t="n">
         <v>101293</v>
@@ -31147,10 +31060,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>494554</v>
+        <v>494484</v>
       </c>
       <c r="R265" t="n">
-        <v>7006673</v>
+        <v>7006600</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -31183,6 +31096,11 @@
       <c r="AA265" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC265" t="inlineStr">
+        <is>
+          <t>Vid en bäck.</t>
         </is>
       </c>
       <c r="AD265" t="b">
@@ -31215,7 +31133,7 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>134725024</v>
+        <v>134725028</v>
       </c>
       <c r="B266" t="n">
         <v>101293</v>
@@ -31261,7 +31179,7 @@
         <v>494513</v>
       </c>
       <c r="R266" t="n">
-        <v>7006628</v>
+        <v>7006578</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -31326,7 +31244,7 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>134725025</v>
+        <v>134725029</v>
       </c>
       <c r="B267" t="n">
         <v>101293</v>
@@ -31369,10 +31287,10 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>494500</v>
+        <v>494499</v>
       </c>
       <c r="R267" t="n">
-        <v>7006617</v>
+        <v>7006578</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -31405,11 +31323,6 @@
       <c r="AA267" t="inlineStr">
         <is>
           <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC267" t="inlineStr">
-        <is>
-          <t>Rikligt vid en bäck.</t>
         </is>
       </c>
       <c r="AD267" t="b">
@@ -31442,7 +31355,7 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>134725026</v>
+        <v>134725030</v>
       </c>
       <c r="B268" t="n">
         <v>101293</v>
@@ -31485,10 +31398,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>494475</v>
+        <v>494569</v>
       </c>
       <c r="R268" t="n">
-        <v>7006607</v>
+        <v>7006566</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -31521,11 +31434,6 @@
       <c r="AA268" t="inlineStr">
         <is>
           <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC268" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -31558,7 +31466,7 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>134725027</v>
+        <v>134725031</v>
       </c>
       <c r="B269" t="n">
         <v>101293</v>
@@ -31590,7 +31498,7 @@
       <c r="J269" t="inlineStr"/>
       <c r="K269" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L269" t="inlineStr"/>
@@ -31601,10 +31509,10 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>494484</v>
+        <v>494575</v>
       </c>
       <c r="R269" t="n">
-        <v>7006600</v>
+        <v>7006647</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -31637,11 +31545,6 @@
       <c r="AA269" t="inlineStr">
         <is>
           <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC269" t="inlineStr">
-        <is>
-          <t>Vid en bäck.</t>
         </is>
       </c>
       <c r="AD269" t="b">
@@ -31674,7 +31577,7 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>134725028</v>
+        <v>134725032</v>
       </c>
       <c r="B270" t="n">
         <v>101293</v>
@@ -31717,10 +31620,10 @@
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>494513</v>
+        <v>494604</v>
       </c>
       <c r="R270" t="n">
-        <v>7006578</v>
+        <v>7006546</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -31753,6 +31656,11 @@
       <c r="AA270" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC270" t="inlineStr">
+        <is>
+          <t>Relativt rikligt.</t>
         </is>
       </c>
       <c r="AD270" t="b">
@@ -31785,7 +31693,7 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>134725029</v>
+        <v>134725033</v>
       </c>
       <c r="B271" t="n">
         <v>101293</v>
@@ -31817,7 +31725,7 @@
       <c r="J271" t="inlineStr"/>
       <c r="K271" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L271" t="inlineStr"/>
@@ -31828,10 +31736,10 @@
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>494499</v>
+        <v>494563</v>
       </c>
       <c r="R271" t="n">
-        <v>7006578</v>
+        <v>7006546</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -31896,7 +31804,7 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>134725030</v>
+        <v>134725034</v>
       </c>
       <c r="B272" t="n">
         <v>101293</v>
@@ -31928,7 +31836,7 @@
       <c r="J272" t="inlineStr"/>
       <c r="K272" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L272" t="inlineStr"/>
@@ -31939,10 +31847,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>494569</v>
+        <v>494549</v>
       </c>
       <c r="R272" t="n">
-        <v>7006566</v>
+        <v>7006531</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -32007,7 +31915,7 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>134725031</v>
+        <v>134725035</v>
       </c>
       <c r="B273" t="n">
         <v>101293</v>
@@ -32050,10 +31958,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>494575</v>
+        <v>494406</v>
       </c>
       <c r="R273" t="n">
-        <v>7006647</v>
+        <v>7006357</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -32118,7 +32026,7 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>134725032</v>
+        <v>134725036</v>
       </c>
       <c r="B274" t="n">
         <v>101293</v>
@@ -32161,10 +32069,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>494604</v>
+        <v>494388</v>
       </c>
       <c r="R274" t="n">
-        <v>7006546</v>
+        <v>7006347</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -32197,11 +32105,6 @@
       <c r="AA274" t="inlineStr">
         <is>
           <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC274" t="inlineStr">
-        <is>
-          <t>Relativt rikligt.</t>
         </is>
       </c>
       <c r="AD274" t="b">
@@ -32234,7 +32137,7 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>134725033</v>
+        <v>134725037</v>
       </c>
       <c r="B275" t="n">
         <v>101293</v>
@@ -32266,7 +32169,7 @@
       <c r="J275" t="inlineStr"/>
       <c r="K275" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L275" t="inlineStr"/>
@@ -32277,10 +32180,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>494563</v>
+        <v>494401</v>
       </c>
       <c r="R275" t="n">
-        <v>7006546</v>
+        <v>7006327</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -32313,6 +32216,11 @@
       <c r="AA275" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC275" t="inlineStr">
+        <is>
+          <t>Rikligt med nordisk stormhatt i ett högörtsstråk i en lucka i granskogen.</t>
         </is>
       </c>
       <c r="AD275" t="b">
@@ -32345,7 +32253,7 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>134725034</v>
+        <v>134725038</v>
       </c>
       <c r="B276" t="n">
         <v>101293</v>
@@ -32388,10 +32296,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>494549</v>
+        <v>494394</v>
       </c>
       <c r="R276" t="n">
-        <v>7006531</v>
+        <v>7006324</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -32456,7 +32364,7 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>134725035</v>
+        <v>134725039</v>
       </c>
       <c r="B277" t="n">
         <v>101293</v>
@@ -32499,10 +32407,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>494406</v>
+        <v>494370</v>
       </c>
       <c r="R277" t="n">
-        <v>7006357</v>
+        <v>7006343</v>
       </c>
       <c r="S277" t="n">
         <v>10</v>
@@ -32567,7 +32475,7 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>134725036</v>
+        <v>134725040</v>
       </c>
       <c r="B278" t="n">
         <v>101293</v>
@@ -32599,7 +32507,7 @@
       <c r="J278" t="inlineStr"/>
       <c r="K278" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L278" t="inlineStr"/>
@@ -32610,10 +32518,10 @@
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>494388</v>
+        <v>494386</v>
       </c>
       <c r="R278" t="n">
-        <v>7006347</v>
+        <v>7006443</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -32678,7 +32586,7 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>134725037</v>
+        <v>134725041</v>
       </c>
       <c r="B279" t="n">
         <v>101293</v>
@@ -32710,7 +32618,7 @@
       <c r="J279" t="inlineStr"/>
       <c r="K279" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L279" t="inlineStr"/>
@@ -32721,10 +32629,10 @@
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>494401</v>
+        <v>494417</v>
       </c>
       <c r="R279" t="n">
-        <v>7006327</v>
+        <v>7006459</v>
       </c>
       <c r="S279" t="n">
         <v>10</v>
@@ -32757,11 +32665,6 @@
       <c r="AA279" t="inlineStr">
         <is>
           <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC279" t="inlineStr">
-        <is>
-          <t>Rikligt med nordisk stormhatt i ett högörtsstråk i en lucka i granskogen.</t>
         </is>
       </c>
       <c r="AD279" t="b">
@@ -32794,7 +32697,7 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>134725038</v>
+        <v>134725042</v>
       </c>
       <c r="B280" t="n">
         <v>101293</v>
@@ -32837,10 +32740,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>494394</v>
+        <v>494440</v>
       </c>
       <c r="R280" t="n">
-        <v>7006324</v>
+        <v>7006462</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -32905,7 +32808,7 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>134725039</v>
+        <v>134725043</v>
       </c>
       <c r="B281" t="n">
         <v>101293</v>
@@ -32937,7 +32840,7 @@
       <c r="J281" t="inlineStr"/>
       <c r="K281" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L281" t="inlineStr"/>
@@ -32948,10 +32851,10 @@
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>494370</v>
+        <v>494466</v>
       </c>
       <c r="R281" t="n">
-        <v>7006343</v>
+        <v>7006455</v>
       </c>
       <c r="S281" t="n">
         <v>10</v>
@@ -33013,450 +32916,6 @@
         </is>
       </c>
       <c r="AY281" t="inlineStr"/>
-    </row>
-    <row r="282">
-      <c r="A282" t="n">
-        <v>134725040</v>
-      </c>
-      <c r="B282" t="n">
-        <v>101293</v>
-      </c>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E282" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F282" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G282" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H282" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I282" t="inlineStr"/>
-      <c r="J282" t="inlineStr"/>
-      <c r="K282" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L282" t="inlineStr"/>
-      <c r="N282" t="inlineStr"/>
-      <c r="P282" t="inlineStr">
-        <is>
-          <t>Bergmyren-Barnsängbäcken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q282" t="n">
-        <v>494386</v>
-      </c>
-      <c r="R282" t="n">
-        <v>7006443</v>
-      </c>
-      <c r="S282" t="n">
-        <v>10</v>
-      </c>
-      <c r="T282" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U282" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V282" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W282" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y282" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AA282" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AD282" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE282" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF282" t="inlineStr"/>
-      <c r="AG282" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH282" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT282" t="inlineStr"/>
-      <c r="AW282" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX282" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY282" t="inlineStr"/>
-    </row>
-    <row r="283">
-      <c r="A283" t="n">
-        <v>134725041</v>
-      </c>
-      <c r="B283" t="n">
-        <v>101293</v>
-      </c>
-      <c r="D283" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E283" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F283" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G283" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H283" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I283" t="inlineStr"/>
-      <c r="J283" t="inlineStr"/>
-      <c r="K283" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L283" t="inlineStr"/>
-      <c r="N283" t="inlineStr"/>
-      <c r="P283" t="inlineStr">
-        <is>
-          <t>Bergmyren-Barnsängbäcken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q283" t="n">
-        <v>494417</v>
-      </c>
-      <c r="R283" t="n">
-        <v>7006459</v>
-      </c>
-      <c r="S283" t="n">
-        <v>10</v>
-      </c>
-      <c r="T283" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U283" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V283" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W283" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y283" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AA283" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AD283" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE283" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF283" t="inlineStr"/>
-      <c r="AG283" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH283" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT283" t="inlineStr"/>
-      <c r="AW283" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX283" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY283" t="inlineStr"/>
-    </row>
-    <row r="284">
-      <c r="A284" t="n">
-        <v>134725042</v>
-      </c>
-      <c r="B284" t="n">
-        <v>101293</v>
-      </c>
-      <c r="D284" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E284" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F284" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G284" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H284" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I284" t="inlineStr"/>
-      <c r="J284" t="inlineStr"/>
-      <c r="K284" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L284" t="inlineStr"/>
-      <c r="N284" t="inlineStr"/>
-      <c r="P284" t="inlineStr">
-        <is>
-          <t>Bergmyren-Barnsängbäcken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q284" t="n">
-        <v>494440</v>
-      </c>
-      <c r="R284" t="n">
-        <v>7006462</v>
-      </c>
-      <c r="S284" t="n">
-        <v>10</v>
-      </c>
-      <c r="T284" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U284" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V284" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W284" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y284" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AA284" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AD284" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE284" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF284" t="inlineStr"/>
-      <c r="AG284" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH284" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT284" t="inlineStr"/>
-      <c r="AW284" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX284" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY284" t="inlineStr"/>
-    </row>
-    <row r="285">
-      <c r="A285" t="n">
-        <v>134725043</v>
-      </c>
-      <c r="B285" t="n">
-        <v>101293</v>
-      </c>
-      <c r="D285" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E285" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F285" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G285" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H285" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I285" t="inlineStr"/>
-      <c r="J285" t="inlineStr"/>
-      <c r="K285" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L285" t="inlineStr"/>
-      <c r="N285" t="inlineStr"/>
-      <c r="P285" t="inlineStr">
-        <is>
-          <t>Bergmyren-Barnsängbäcken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q285" t="n">
-        <v>494466</v>
-      </c>
-      <c r="R285" t="n">
-        <v>7006455</v>
-      </c>
-      <c r="S285" t="n">
-        <v>10</v>
-      </c>
-      <c r="T285" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U285" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V285" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W285" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y285" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AA285" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AD285" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE285" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF285" t="inlineStr"/>
-      <c r="AG285" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH285" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT285" t="inlineStr"/>
-      <c r="AW285" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX285" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY285" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5791-2026 artfynd.xlsx
+++ b/artfynd/A 5791-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY281"/>
+  <dimension ref="A1:AY285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8906,27 +8906,27 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>134725187</v>
+        <v>134724952</v>
       </c>
       <c r="B70" t="n">
-        <v>57153</v>
+        <v>57975</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -8934,33 +8934,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Bergmyren-Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>494535</v>
+        <v>494462</v>
       </c>
       <c r="R70" t="n">
-        <v>7006526</v>
+        <v>7006595</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8997,7 +8989,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>1 järpe med varningsläte sågs några meter upp i ett träd.</t>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9012,6 +9004,26 @@
       <c r="AH70" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9029,10 +9041,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122355645</v>
+        <v>134724953</v>
       </c>
       <c r="B71" t="n">
-        <v>58114</v>
+        <v>57975</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9040,48 +9052,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren-Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>494521</v>
+        <v>494456</v>
       </c>
       <c r="R71" t="n">
-        <v>7006584</v>
+        <v>7006579</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9108,12 +9114,17 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, längs flera meter på en gran vid kant mot yngre skog.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9128,6 +9139,26 @@
       <c r="AH71" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9145,10 +9176,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122357863</v>
+        <v>134724954</v>
       </c>
       <c r="B72" t="n">
-        <v>58114</v>
+        <v>57975</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9156,31 +9187,29 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -9190,14 +9219,14 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Bergmyren-Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>494497</v>
+        <v>494448</v>
       </c>
       <c r="R72" t="n">
-        <v>7006523</v>
+        <v>7006573</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9224,12 +9253,17 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, längs flera meter på en gran vid kant mot yngre skog.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9244,6 +9278,26 @@
       <c r="AH72" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM72" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -9261,27 +9315,27 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>134724963</v>
+        <v>134724955</v>
       </c>
       <c r="B73" t="n">
-        <v>58131</v>
+        <v>57975</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>103023</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -9295,10 +9349,14 @@
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -9312,10 +9370,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>494371</v>
+        <v>494391</v>
       </c>
       <c r="R73" t="n">
-        <v>7006417</v>
+        <v>7006346</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9350,6 +9408,11 @@
           <t>2026-06-27</t>
         </is>
       </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>1 st hona av tretåig hackspett som sågs födosöka en kort stund på en stående död gran. På fyndplatsen finns stående död ved som indikerar mycket högt livsmiljövärde för tretåig hackspett, bl.a. en stående död gran med full längd och 68 cm i brösthöjdsdiameter.</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -9362,6 +9425,11 @@
       <c r="AH73" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>Äldre näringsrik granskog.</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9379,10 +9447,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>134725219</v>
+        <v>134725187</v>
       </c>
       <c r="B74" t="n">
-        <v>99094</v>
+        <v>57153</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9390,39 +9458,35 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>219795</v>
+        <v>102612</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N74" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -9434,10 +9498,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>494584</v>
+        <v>494535</v>
       </c>
       <c r="R74" t="n">
-        <v>7006612</v>
+        <v>7006526</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9474,7 +9538,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Minst 7 plantor varav 3 med blomställningar inom ca 2 m2 yta.</t>
+          <t>1 järpe med varningsläte sågs några meter upp i ett träd.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9483,7 +9547,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -9507,61 +9570,59 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>134725220</v>
+        <v>122355645</v>
       </c>
       <c r="B75" t="n">
-        <v>99094</v>
+        <v>58114</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>219795</v>
+        <v>103021</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Bergmyren-Barnsängbäcken, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>494481</v>
+        <v>494521</v>
       </c>
       <c r="R75" t="n">
-        <v>7006411</v>
+        <v>7006584</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9588,17 +9649,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Minst 4 plantor varav 3 i blom samt 2 vinterståndare på ca 2 x 1 m2 yta i granskog.</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9607,7 +9663,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -9631,53 +9686,59 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>134725224</v>
+        <v>122357863</v>
       </c>
       <c r="B76" t="n">
-        <v>98219</v>
+        <v>58114</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>219815</v>
+        <v>103021</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Bergmyren-Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>494379</v>
+        <v>494497</v>
       </c>
       <c r="R76" t="n">
-        <v>7006437</v>
+        <v>7006523</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9704,12 +9765,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9718,7 +9779,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -9742,10 +9802,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>134725225</v>
+        <v>134724963</v>
       </c>
       <c r="B77" t="n">
-        <v>98219</v>
+        <v>58131</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9753,42 +9813,50 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>219815</v>
+        <v>103023</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Bergmyren-Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>494469</v>
+        <v>494371</v>
       </c>
       <c r="R77" t="n">
-        <v>7006386</v>
+        <v>7006417</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9829,7 +9897,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -9853,10 +9920,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>134725090</v>
+        <v>134725219</v>
       </c>
       <c r="B78" t="n">
-        <v>99533</v>
+        <v>99094</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9864,42 +9931,54 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>219880</v>
+        <v>219795</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K78" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Bergmyren-Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>494770</v>
+        <v>494584</v>
       </c>
       <c r="R78" t="n">
-        <v>7006734</v>
+        <v>7006612</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9932,6 +10011,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Minst 7 plantor varav 3 med blomställningar inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9964,10 +10048,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>134725091</v>
+        <v>134725220</v>
       </c>
       <c r="B79" t="n">
-        <v>99533</v>
+        <v>99094</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9975,25 +10059,33 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>219880</v>
+        <v>219795</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K79" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -10007,10 +10099,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>494727</v>
+        <v>494481</v>
       </c>
       <c r="R79" t="n">
-        <v>7006690</v>
+        <v>7006411</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10043,6 +10135,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Minst 4 plantor varav 3 i blom samt 2 vinterståndare på ca 2 x 1 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10075,10 +10172,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>134725093</v>
+        <v>134725224</v>
       </c>
       <c r="B80" t="n">
-        <v>99533</v>
+        <v>98219</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10086,28 +10183,28 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>219880</v>
+        <v>219815</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L80" t="inlineStr"/>
@@ -10118,10 +10215,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>494684</v>
+        <v>494379</v>
       </c>
       <c r="R80" t="n">
-        <v>7006741</v>
+        <v>7006437</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10186,10 +10283,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>134725095</v>
+        <v>134725225</v>
       </c>
       <c r="B81" t="n">
-        <v>99533</v>
+        <v>98219</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10197,28 +10294,28 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>219880</v>
+        <v>219815</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
@@ -10229,10 +10326,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>494637</v>
+        <v>494469</v>
       </c>
       <c r="R81" t="n">
-        <v>7006730</v>
+        <v>7006386</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10297,7 +10394,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>134725096</v>
+        <v>134725090</v>
       </c>
       <c r="B82" t="n">
         <v>99533</v>
@@ -10329,7 +10426,7 @@
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L82" t="inlineStr"/>
@@ -10340,10 +10437,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>494628</v>
+        <v>494770</v>
       </c>
       <c r="R82" t="n">
-        <v>7006712</v>
+        <v>7006734</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10408,7 +10505,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>134725098</v>
+        <v>134725091</v>
       </c>
       <c r="B83" t="n">
         <v>99533</v>
@@ -10451,10 +10548,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>494631</v>
+        <v>494727</v>
       </c>
       <c r="R83" t="n">
-        <v>7006688</v>
+        <v>7006690</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10519,7 +10616,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>134725100</v>
+        <v>134725093</v>
       </c>
       <c r="B84" t="n">
         <v>99533</v>
@@ -10562,10 +10659,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>494525</v>
+        <v>494684</v>
       </c>
       <c r="R84" t="n">
-        <v>7006614</v>
+        <v>7006741</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10630,7 +10727,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>134725101</v>
+        <v>134725095</v>
       </c>
       <c r="B85" t="n">
         <v>99533</v>
@@ -10673,10 +10770,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>494474</v>
+        <v>494637</v>
       </c>
       <c r="R85" t="n">
-        <v>7006605</v>
+        <v>7006730</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10709,11 +10806,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Kransrams bland andra högörter i ett frodigt stråk vid en bäck.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10746,7 +10838,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>134725102</v>
+        <v>134725096</v>
       </c>
       <c r="B86" t="n">
         <v>99533</v>
@@ -10778,7 +10870,7 @@
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L86" t="inlineStr"/>
@@ -10789,10 +10881,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>494482</v>
+        <v>494628</v>
       </c>
       <c r="R86" t="n">
-        <v>7006601</v>
+        <v>7006712</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10857,7 +10949,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>134725104</v>
+        <v>134725098</v>
       </c>
       <c r="B87" t="n">
         <v>99533</v>
@@ -10900,10 +10992,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>494515</v>
+        <v>494631</v>
       </c>
       <c r="R87" t="n">
-        <v>7006595</v>
+        <v>7006688</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10968,7 +11060,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>134725105</v>
+        <v>134725100</v>
       </c>
       <c r="B88" t="n">
         <v>99533</v>
@@ -11011,10 +11103,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>494473</v>
+        <v>494525</v>
       </c>
       <c r="R88" t="n">
-        <v>7006548</v>
+        <v>7006614</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11079,7 +11171,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>134725107</v>
+        <v>134725101</v>
       </c>
       <c r="B89" t="n">
         <v>99533</v>
@@ -11111,7 +11203,7 @@
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L89" t="inlineStr"/>
@@ -11122,10 +11214,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>494480</v>
+        <v>494474</v>
       </c>
       <c r="R89" t="n">
-        <v>7006567</v>
+        <v>7006605</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11158,6 +11250,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Kransrams bland andra högörter i ett frodigt stråk vid en bäck.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11190,7 +11287,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>134725108</v>
+        <v>134725102</v>
       </c>
       <c r="B90" t="n">
         <v>99533</v>
@@ -11233,10 +11330,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>494495</v>
+        <v>494482</v>
       </c>
       <c r="R90" t="n">
-        <v>7006550</v>
+        <v>7006601</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11301,7 +11398,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>134725109</v>
+        <v>134725104</v>
       </c>
       <c r="B91" t="n">
         <v>99533</v>
@@ -11344,10 +11441,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>494508</v>
+        <v>494515</v>
       </c>
       <c r="R91" t="n">
-        <v>7006533</v>
+        <v>7006595</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11412,7 +11509,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>134725110</v>
+        <v>134725105</v>
       </c>
       <c r="B92" t="n">
         <v>99533</v>
@@ -11444,7 +11541,7 @@
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L92" t="inlineStr"/>
@@ -11455,10 +11552,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>494567</v>
+        <v>494473</v>
       </c>
       <c r="R92" t="n">
-        <v>7006557</v>
+        <v>7006548</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11523,7 +11620,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>134725111</v>
+        <v>134725107</v>
       </c>
       <c r="B93" t="n">
         <v>99533</v>
@@ -11555,7 +11652,7 @@
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L93" t="inlineStr"/>
@@ -11566,10 +11663,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>494595</v>
+        <v>494480</v>
       </c>
       <c r="R93" t="n">
-        <v>7006678</v>
+        <v>7006567</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11634,7 +11731,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>134725112</v>
+        <v>134725108</v>
       </c>
       <c r="B94" t="n">
         <v>99533</v>
@@ -11666,7 +11763,7 @@
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L94" t="inlineStr"/>
@@ -11677,10 +11774,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>494575</v>
+        <v>494495</v>
       </c>
       <c r="R94" t="n">
-        <v>7006547</v>
+        <v>7006550</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11745,7 +11842,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>134725113</v>
+        <v>134725109</v>
       </c>
       <c r="B95" t="n">
         <v>99533</v>
@@ -11777,7 +11874,7 @@
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L95" t="inlineStr"/>
@@ -11788,10 +11885,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>494457</v>
+        <v>494508</v>
       </c>
       <c r="R95" t="n">
-        <v>7006490</v>
+        <v>7006533</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11856,7 +11953,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>134725114</v>
+        <v>134725110</v>
       </c>
       <c r="B96" t="n">
         <v>99533</v>
@@ -11899,10 +11996,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>494404</v>
+        <v>494567</v>
       </c>
       <c r="R96" t="n">
-        <v>7006314</v>
+        <v>7006557</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11967,7 +12064,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>134725115</v>
+        <v>134725111</v>
       </c>
       <c r="B97" t="n">
         <v>99533</v>
@@ -12010,10 +12107,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>494395</v>
+        <v>494595</v>
       </c>
       <c r="R97" t="n">
-        <v>7006331</v>
+        <v>7006678</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12078,7 +12175,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>134725116</v>
+        <v>134725112</v>
       </c>
       <c r="B98" t="n">
         <v>99533</v>
@@ -12121,10 +12218,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>494395</v>
+        <v>494575</v>
       </c>
       <c r="R98" t="n">
-        <v>7006324</v>
+        <v>7006547</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12189,7 +12286,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>134725117</v>
+        <v>134725113</v>
       </c>
       <c r="B99" t="n">
         <v>99533</v>
@@ -12221,7 +12318,7 @@
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L99" t="inlineStr"/>
@@ -12232,10 +12329,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>494364</v>
+        <v>494457</v>
       </c>
       <c r="R99" t="n">
-        <v>7006343</v>
+        <v>7006490</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12268,11 +12365,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12305,7 +12397,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>134725118</v>
+        <v>134725114</v>
       </c>
       <c r="B100" t="n">
         <v>99533</v>
@@ -12348,10 +12440,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>494383</v>
+        <v>494404</v>
       </c>
       <c r="R100" t="n">
-        <v>7006414</v>
+        <v>7006314</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12416,7 +12508,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>134725119</v>
+        <v>134725115</v>
       </c>
       <c r="B101" t="n">
         <v>99533</v>
@@ -12459,10 +12551,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>494436</v>
+        <v>494395</v>
       </c>
       <c r="R101" t="n">
-        <v>7006475</v>
+        <v>7006331</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12527,7 +12619,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>134725120</v>
+        <v>134725116</v>
       </c>
       <c r="B102" t="n">
         <v>99533</v>
@@ -12570,10 +12662,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>494435</v>
+        <v>494395</v>
       </c>
       <c r="R102" t="n">
-        <v>7006464</v>
+        <v>7006324</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12606,11 +12698,6 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12643,7 +12730,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>134725121</v>
+        <v>134725117</v>
       </c>
       <c r="B103" t="n">
         <v>99533</v>
@@ -12675,7 +12762,7 @@
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L103" t="inlineStr"/>
@@ -12686,10 +12773,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>494440</v>
+        <v>494364</v>
       </c>
       <c r="R103" t="n">
-        <v>7006481</v>
+        <v>7006343</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12722,6 +12809,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12754,7 +12846,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>134725122</v>
+        <v>134725118</v>
       </c>
       <c r="B104" t="n">
         <v>99533</v>
@@ -12797,10 +12889,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>494473</v>
+        <v>494383</v>
       </c>
       <c r="R104" t="n">
-        <v>7006491</v>
+        <v>7006414</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12865,10 +12957,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>134725226</v>
+        <v>134725119</v>
       </c>
       <c r="B105" t="n">
-        <v>108205</v>
+        <v>99533</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12876,28 +12968,28 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220083</v>
+        <v>219880</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L105" t="inlineStr"/>
@@ -12908,10 +13000,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>494763</v>
+        <v>494436</v>
       </c>
       <c r="R105" t="n">
-        <v>7006744</v>
+        <v>7006475</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12976,10 +13068,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>134725227</v>
+        <v>134725120</v>
       </c>
       <c r="B106" t="n">
-        <v>108205</v>
+        <v>99533</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12987,21 +13079,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220083</v>
+        <v>219880</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -13019,10 +13111,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>494582</v>
+        <v>494435</v>
       </c>
       <c r="R106" t="n">
-        <v>7006695</v>
+        <v>7006464</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -13055,6 +13147,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13087,10 +13184,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>134725155</v>
+        <v>134725121</v>
       </c>
       <c r="B107" t="n">
-        <v>99099</v>
+        <v>99533</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13098,36 +13195,28 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220093</v>
+        <v>219880</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L107" t="inlineStr"/>
@@ -13138,10 +13227,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>494460</v>
+        <v>494440</v>
       </c>
       <c r="R107" t="n">
-        <v>7006572</v>
+        <v>7006481</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13206,10 +13295,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>134725156</v>
+        <v>134725122</v>
       </c>
       <c r="B108" t="n">
-        <v>99099</v>
+        <v>99533</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13217,36 +13306,28 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220093</v>
+        <v>219880</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L108" t="inlineStr"/>
@@ -13257,10 +13338,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>494575</v>
+        <v>494473</v>
       </c>
       <c r="R108" t="n">
-        <v>7006548</v>
+        <v>7006491</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13325,10 +13406,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>134725068</v>
+        <v>134725226</v>
       </c>
       <c r="B109" t="n">
-        <v>108274</v>
+        <v>108205</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13336,28 +13417,28 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220102</v>
+        <v>220083</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L109" t="inlineStr"/>
@@ -13368,10 +13449,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>494743</v>
+        <v>494763</v>
       </c>
       <c r="R109" t="n">
-        <v>7006752</v>
+        <v>7006744</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13436,10 +13517,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>134725069</v>
+        <v>134725227</v>
       </c>
       <c r="B110" t="n">
-        <v>108274</v>
+        <v>108205</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13447,28 +13528,28 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220102</v>
+        <v>220083</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L110" t="inlineStr"/>
@@ -13479,10 +13560,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>494743</v>
+        <v>494582</v>
       </c>
       <c r="R110" t="n">
-        <v>7006715</v>
+        <v>7006695</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13547,10 +13628,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>134725070</v>
+        <v>134725155</v>
       </c>
       <c r="B111" t="n">
-        <v>108274</v>
+        <v>99099</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13558,28 +13639,36 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>220102</v>
+        <v>220093</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L111" t="inlineStr"/>
@@ -13590,10 +13679,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>494717</v>
+        <v>494460</v>
       </c>
       <c r="R111" t="n">
-        <v>7006747</v>
+        <v>7006572</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13658,10 +13747,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>134725071</v>
+        <v>134725156</v>
       </c>
       <c r="B112" t="n">
-        <v>108274</v>
+        <v>99099</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13669,28 +13758,36 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220102</v>
+        <v>220093</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L112" t="inlineStr"/>
@@ -13701,10 +13798,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>494683</v>
+        <v>494575</v>
       </c>
       <c r="R112" t="n">
-        <v>7006724</v>
+        <v>7006548</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13769,7 +13866,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>134725072</v>
+        <v>134725068</v>
       </c>
       <c r="B113" t="n">
         <v>108274</v>
@@ -13812,10 +13909,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>494644</v>
+        <v>494743</v>
       </c>
       <c r="R113" t="n">
-        <v>7006712</v>
+        <v>7006752</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13880,7 +13977,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>134725073</v>
+        <v>134725069</v>
       </c>
       <c r="B114" t="n">
         <v>108274</v>
@@ -13923,10 +14020,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>494634</v>
+        <v>494743</v>
       </c>
       <c r="R114" t="n">
-        <v>7006699</v>
+        <v>7006715</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13991,7 +14088,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>134725075</v>
+        <v>134725070</v>
       </c>
       <c r="B115" t="n">
         <v>108274</v>
@@ -14023,7 +14120,7 @@
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L115" t="inlineStr"/>
@@ -14034,10 +14131,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>494564</v>
+        <v>494717</v>
       </c>
       <c r="R115" t="n">
-        <v>7006669</v>
+        <v>7006747</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -14102,7 +14199,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>134725076</v>
+        <v>134725071</v>
       </c>
       <c r="B116" t="n">
         <v>108274</v>
@@ -14134,7 +14231,7 @@
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L116" t="inlineStr"/>
@@ -14145,10 +14242,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>494517</v>
+        <v>494683</v>
       </c>
       <c r="R116" t="n">
-        <v>7006596</v>
+        <v>7006724</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -14213,7 +14310,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>134725078</v>
+        <v>134725072</v>
       </c>
       <c r="B117" t="n">
         <v>108274</v>
@@ -14256,10 +14353,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>494462</v>
+        <v>494644</v>
       </c>
       <c r="R117" t="n">
-        <v>7006579</v>
+        <v>7006712</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -14324,7 +14421,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>134725079</v>
+        <v>134725073</v>
       </c>
       <c r="B118" t="n">
         <v>108274</v>
@@ -14367,10 +14464,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>494583</v>
+        <v>494634</v>
       </c>
       <c r="R118" t="n">
-        <v>7006613</v>
+        <v>7006699</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14435,7 +14532,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>134725081</v>
+        <v>134725075</v>
       </c>
       <c r="B119" t="n">
         <v>108274</v>
@@ -14478,10 +14575,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>494595</v>
+        <v>494564</v>
       </c>
       <c r="R119" t="n">
-        <v>7006635</v>
+        <v>7006669</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14546,7 +14643,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>134725082</v>
+        <v>134725076</v>
       </c>
       <c r="B120" t="n">
         <v>108274</v>
@@ -14578,7 +14675,7 @@
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L120" t="inlineStr"/>
@@ -14589,10 +14686,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>494571</v>
+        <v>494517</v>
       </c>
       <c r="R120" t="n">
-        <v>7006652</v>
+        <v>7006596</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14657,7 +14754,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>134725083</v>
+        <v>134725078</v>
       </c>
       <c r="B121" t="n">
         <v>108274</v>
@@ -14689,7 +14786,7 @@
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L121" t="inlineStr"/>
@@ -14700,10 +14797,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>494609</v>
+        <v>494462</v>
       </c>
       <c r="R121" t="n">
-        <v>7006667</v>
+        <v>7006579</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14768,7 +14865,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>134725085</v>
+        <v>134725079</v>
       </c>
       <c r="B122" t="n">
         <v>108274</v>
@@ -14811,10 +14908,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>494497</v>
+        <v>494583</v>
       </c>
       <c r="R122" t="n">
-        <v>7006507</v>
+        <v>7006613</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14879,7 +14976,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>134725087</v>
+        <v>134725081</v>
       </c>
       <c r="B123" t="n">
         <v>108274</v>
@@ -14922,10 +15019,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>494437</v>
+        <v>494595</v>
       </c>
       <c r="R123" t="n">
-        <v>7006466</v>
+        <v>7006635</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14990,7 +15087,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>134725088</v>
+        <v>134725082</v>
       </c>
       <c r="B124" t="n">
         <v>108274</v>
@@ -15033,10 +15130,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>494447</v>
+        <v>494571</v>
       </c>
       <c r="R124" t="n">
-        <v>7006468</v>
+        <v>7006652</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -15101,10 +15198,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>134725050</v>
+        <v>134725083</v>
       </c>
       <c r="B125" t="n">
-        <v>111153</v>
+        <v>108274</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15112,21 +15209,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>220240</v>
+        <v>220102</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -15144,10 +15241,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>494642</v>
+        <v>494609</v>
       </c>
       <c r="R125" t="n">
-        <v>7006722</v>
+        <v>7006667</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -15212,10 +15309,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>134725051</v>
+        <v>134725085</v>
       </c>
       <c r="B126" t="n">
-        <v>111153</v>
+        <v>108274</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15223,28 +15320,28 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>220240</v>
+        <v>220102</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L126" t="inlineStr"/>
@@ -15255,10 +15352,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>494632</v>
+        <v>494497</v>
       </c>
       <c r="R126" t="n">
-        <v>7006697</v>
+        <v>7006507</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -15323,10 +15420,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>134725052</v>
+        <v>134725087</v>
       </c>
       <c r="B127" t="n">
-        <v>111153</v>
+        <v>108274</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15334,21 +15431,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220240</v>
+        <v>220102</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -15366,10 +15463,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>494521</v>
+        <v>494437</v>
       </c>
       <c r="R127" t="n">
-        <v>7006593</v>
+        <v>7006466</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15434,10 +15531,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>134725053</v>
+        <v>134725088</v>
       </c>
       <c r="B128" t="n">
-        <v>111153</v>
+        <v>108274</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15445,21 +15542,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220240</v>
+        <v>220102</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -15477,10 +15574,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>494611</v>
+        <v>494447</v>
       </c>
       <c r="R128" t="n">
-        <v>7006598</v>
+        <v>7006468</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15513,11 +15610,6 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15550,7 +15642,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>134725054</v>
+        <v>134725050</v>
       </c>
       <c r="B129" t="n">
         <v>111153</v>
@@ -15593,10 +15685,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>494569</v>
+        <v>494642</v>
       </c>
       <c r="R129" t="n">
-        <v>7006642</v>
+        <v>7006722</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15661,7 +15753,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>134725055</v>
+        <v>134725051</v>
       </c>
       <c r="B130" t="n">
         <v>111153</v>
@@ -15704,10 +15796,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>494609</v>
+        <v>494632</v>
       </c>
       <c r="R130" t="n">
-        <v>7006555</v>
+        <v>7006697</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15772,7 +15864,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>134725056</v>
+        <v>134725052</v>
       </c>
       <c r="B131" t="n">
         <v>111153</v>
@@ -15815,10 +15907,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>494421</v>
+        <v>494521</v>
       </c>
       <c r="R131" t="n">
-        <v>7006395</v>
+        <v>7006593</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15883,7 +15975,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>134725057</v>
+        <v>134725053</v>
       </c>
       <c r="B132" t="n">
         <v>111153</v>
@@ -15915,7 +16007,7 @@
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L132" t="inlineStr"/>
@@ -15926,10 +16018,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>494424</v>
+        <v>494611</v>
       </c>
       <c r="R132" t="n">
-        <v>7006319</v>
+        <v>7006598</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15962,6 +16054,11 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15994,7 +16091,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>134725058</v>
+        <v>134725054</v>
       </c>
       <c r="B133" t="n">
         <v>111153</v>
@@ -16037,10 +16134,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>494388</v>
+        <v>494569</v>
       </c>
       <c r="R133" t="n">
-        <v>7006367</v>
+        <v>7006642</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -16105,7 +16202,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>134725059</v>
+        <v>134725055</v>
       </c>
       <c r="B134" t="n">
         <v>111153</v>
@@ -16148,10 +16245,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>494373</v>
+        <v>494609</v>
       </c>
       <c r="R134" t="n">
-        <v>7006369</v>
+        <v>7006555</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -16216,7 +16313,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>134725060</v>
+        <v>134725056</v>
       </c>
       <c r="B135" t="n">
         <v>111153</v>
@@ -16259,10 +16356,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>494397</v>
+        <v>494421</v>
       </c>
       <c r="R135" t="n">
-        <v>7006377</v>
+        <v>7006395</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -16327,7 +16424,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>134725061</v>
+        <v>134725057</v>
       </c>
       <c r="B136" t="n">
         <v>111153</v>
@@ -16359,7 +16456,7 @@
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L136" t="inlineStr"/>
@@ -16370,10 +16467,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>494402</v>
+        <v>494424</v>
       </c>
       <c r="R136" t="n">
-        <v>7006416</v>
+        <v>7006319</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -16438,7 +16535,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>134725063</v>
+        <v>134725058</v>
       </c>
       <c r="B137" t="n">
         <v>111153</v>
@@ -16481,10 +16578,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>494446</v>
+        <v>494388</v>
       </c>
       <c r="R137" t="n">
-        <v>7006452</v>
+        <v>7006367</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16549,7 +16646,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>134725064</v>
+        <v>134725059</v>
       </c>
       <c r="B138" t="n">
         <v>111153</v>
@@ -16581,7 +16678,7 @@
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L138" t="inlineStr"/>
@@ -16592,10 +16689,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>494459</v>
+        <v>494373</v>
       </c>
       <c r="R138" t="n">
-        <v>7006430</v>
+        <v>7006369</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16660,62 +16757,56 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129402814</v>
+        <v>134725060</v>
       </c>
       <c r="B139" t="n">
-        <v>99118</v>
+        <v>111153</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>220787</v>
+        <v>220240</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren-Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>494795</v>
+        <v>494397</v>
       </c>
       <c r="R139" t="n">
-        <v>7006705</v>
+        <v>7006377</v>
       </c>
       <c r="S139" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -16739,27 +16830,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="Z139" t="inlineStr">
-        <is>
-          <t>12:46</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB139" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>Minst 14 plantor inom ca 0,5 m2 yta.</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16768,6 +16844,7 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -16791,47 +16868,39 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>134725158</v>
+        <v>134725061</v>
       </c>
       <c r="B140" t="n">
-        <v>99195</v>
+        <v>111153</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>220787</v>
+        <v>220240</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L140" t="inlineStr"/>
@@ -16842,10 +16911,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>494757</v>
+        <v>494402</v>
       </c>
       <c r="R140" t="n">
-        <v>7006738</v>
+        <v>7006416</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16878,11 +16947,6 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Minst 100 plantor och 1 blomstjälk med knopp på gång inom ca 2 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16915,47 +16979,39 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>134725159</v>
+        <v>134725063</v>
       </c>
       <c r="B141" t="n">
-        <v>99195</v>
+        <v>111153</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>220787</v>
+        <v>220240</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L141" t="inlineStr"/>
@@ -16966,10 +17022,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>494756</v>
+        <v>494446</v>
       </c>
       <c r="R141" t="n">
-        <v>7006724</v>
+        <v>7006452</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -17002,11 +17058,6 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Minst 40 plantor och 10 blomstjälkar med knopp på gång inom ca 1 m2 yta på en liten mossklädd förhöjning i granskog.</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -17039,44 +17090,36 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>134725161</v>
+        <v>134725064</v>
       </c>
       <c r="B142" t="n">
-        <v>99195</v>
+        <v>111153</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>220787</v>
+        <v>220240</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr">
         <is>
           <t>blomknopp</t>
@@ -17090,10 +17133,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>494719</v>
+        <v>494459</v>
       </c>
       <c r="R142" t="n">
-        <v>7006678</v>
+        <v>7006430</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -17126,11 +17169,6 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Minst 35 plantor och 6 blomstjälkar med knopp på gång inom ca 2 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -17163,10 +17201,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>134725162</v>
+        <v>129402814</v>
       </c>
       <c r="B143" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17193,7 +17231,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -17203,24 +17241,22 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Bergmyren-Barnsängbäcken, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>494701</v>
+        <v>494795</v>
       </c>
       <c r="R143" t="n">
-        <v>7006715</v>
+        <v>7006705</v>
       </c>
       <c r="S143" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -17244,17 +17280,27 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>Minst 90 plantor och 11 blomstjälkar med knopp på gång inom ca 2 m2 yta i granskog.</t>
+          <t>Minst 14 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -17263,7 +17309,6 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
-      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
@@ -17287,7 +17332,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>134725164</v>
+        <v>134725158</v>
       </c>
       <c r="B144" t="n">
         <v>99195</v>
@@ -17317,7 +17362,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -17338,10 +17383,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>494696</v>
+        <v>494757</v>
       </c>
       <c r="R144" t="n">
-        <v>7006695</v>
+        <v>7006738</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -17378,7 +17423,7 @@
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Minst 12 plantor och 2 blomstjälkar med knopp på gång inom ca 0,5 m2 yta i granskog.</t>
+          <t>Minst 100 plantor och 1 blomstjälk med knopp på gång inom ca 2 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -17411,7 +17456,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>134725165</v>
+        <v>134725159</v>
       </c>
       <c r="B145" t="n">
         <v>99195</v>
@@ -17441,7 +17486,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -17462,10 +17507,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>494435</v>
+        <v>494756</v>
       </c>
       <c r="R145" t="n">
-        <v>7006538</v>
+        <v>7006724</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -17502,7 +17547,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>Minst 35 plantor och 2 blomstjälkar med knopp på gång inom ca 1 m2 yta i granskog.</t>
+          <t>Minst 40 plantor och 10 blomstjälkar med knopp på gång inom ca 1 m2 yta på en liten mossklädd förhöjning i granskog.</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -17535,7 +17580,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>134725167</v>
+        <v>134725161</v>
       </c>
       <c r="B146" t="n">
         <v>99195</v>
@@ -17565,7 +17610,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -17586,10 +17631,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>494436</v>
+        <v>494719</v>
       </c>
       <c r="R146" t="n">
-        <v>7006431</v>
+        <v>7006678</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -17626,7 +17671,7 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>Minst 25 plantor och 2 blomstjälkar med knopp på gång inom ca 0,5 m2 yta i granskog.</t>
+          <t>Minst 35 plantor och 6 blomstjälkar med knopp på gång inom ca 2 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17659,7 +17704,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>134725169</v>
+        <v>134725162</v>
       </c>
       <c r="B147" t="n">
         <v>99195</v>
@@ -17689,7 +17734,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -17710,10 +17755,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>494428</v>
+        <v>494701</v>
       </c>
       <c r="R147" t="n">
-        <v>7006412</v>
+        <v>7006715</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17750,7 +17795,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>Minst 13 plantor och 2 blomstjälkar med knopp på gång inom ca 0,5 m2 yta i ett örtrikt stråk i granskog.</t>
+          <t>Minst 90 plantor och 11 blomstjälkar med knopp på gång inom ca 2 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17783,7 +17828,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>134725171</v>
+        <v>134725164</v>
       </c>
       <c r="B148" t="n">
         <v>99195</v>
@@ -17813,7 +17858,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -17834,10 +17879,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>494466</v>
+        <v>494696</v>
       </c>
       <c r="R148" t="n">
-        <v>7006367</v>
+        <v>7006695</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17874,7 +17919,7 @@
       </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>Minst 15 plantor och 3 blomstjälkar med knopp på gång inom ca 1 m2 yta i granskog.</t>
+          <t>Minst 12 plantor och 2 blomstjälkar med knopp på gång inom ca 0,5 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17907,7 +17952,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>134725172</v>
+        <v>134725165</v>
       </c>
       <c r="B149" t="n">
         <v>99195</v>
@@ -17937,7 +17982,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -17958,10 +18003,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>494382</v>
+        <v>494435</v>
       </c>
       <c r="R149" t="n">
-        <v>7006321</v>
+        <v>7006538</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17998,7 +18043,7 @@
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>Minst 30 plantor och 5 blomstjälkar med knopp på gång inom ca 1 m2 yta i granskog.</t>
+          <t>Minst 35 plantor och 2 blomstjälkar med knopp på gång inom ca 1 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -18031,7 +18076,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>134725174</v>
+        <v>134725167</v>
       </c>
       <c r="B150" t="n">
         <v>99195</v>
@@ -18061,7 +18106,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -18082,10 +18127,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>494368</v>
+        <v>494436</v>
       </c>
       <c r="R150" t="n">
-        <v>7006369</v>
+        <v>7006431</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -18122,7 +18167,7 @@
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>Minst 60 plantor och 1 blomstjälk med knopp på gång inom ca 2 m2 yta i granskog.</t>
+          <t>Minst 25 plantor och 2 blomstjälkar med knopp på gång inom ca 0,5 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -18155,7 +18200,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>134725176</v>
+        <v>134725169</v>
       </c>
       <c r="B151" t="n">
         <v>99195</v>
@@ -18185,7 +18230,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -18206,10 +18251,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>494398</v>
+        <v>494428</v>
       </c>
       <c r="R151" t="n">
-        <v>7006384</v>
+        <v>7006412</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -18246,7 +18291,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>Minst 22 plantor och 1 blomstjälk med knopp på gång inom ca 1 m2 yta i granskog.</t>
+          <t>Minst 13 plantor och 2 blomstjälkar med knopp på gång inom ca 0,5 m2 yta i ett örtrikt stråk i granskog.</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -18279,7 +18324,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>134725177</v>
+        <v>134725171</v>
       </c>
       <c r="B152" t="n">
         <v>99195</v>
@@ -18309,7 +18354,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -18330,10 +18375,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>494375</v>
+        <v>494466</v>
       </c>
       <c r="R152" t="n">
-        <v>7006421</v>
+        <v>7006367</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -18370,7 +18415,7 @@
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>Minst 60 plantor och 30 blomstjälkar med knopp på gång inom ca 2 m2 yta i granskog.</t>
+          <t>Minst 15 plantor och 3 blomstjälkar med knopp på gång inom ca 1 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -18403,7 +18448,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>134725179</v>
+        <v>134725172</v>
       </c>
       <c r="B153" t="n">
         <v>99195</v>
@@ -18433,7 +18478,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -18454,10 +18499,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>494432</v>
+        <v>494382</v>
       </c>
       <c r="R153" t="n">
-        <v>7006477</v>
+        <v>7006321</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -18494,7 +18539,7 @@
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>Minst 27 plantor och 1 blomstjälk med knopp på gång inom ca 1 m2 yta i äldre granskog.</t>
+          <t>Minst 30 plantor och 5 blomstjälkar med knopp på gång inom ca 1 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -18527,7 +18572,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>134725180</v>
+        <v>134725174</v>
       </c>
       <c r="B154" t="n">
         <v>99195</v>
@@ -18557,7 +18602,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -18578,10 +18623,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>494483</v>
+        <v>494368</v>
       </c>
       <c r="R154" t="n">
-        <v>7006405</v>
+        <v>7006369</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -18618,7 +18663,7 @@
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>Minst 200 plantor och 23 blomstjälkar med knopp på gång inom ca 4 m2 yta i granskog.</t>
+          <t>Minst 60 plantor och 1 blomstjälk med knopp på gång inom ca 2 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -18651,7 +18696,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>134725183</v>
+        <v>134725176</v>
       </c>
       <c r="B155" t="n">
         <v>99195</v>
@@ -18681,7 +18726,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -18702,10 +18747,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>494494</v>
+        <v>494398</v>
       </c>
       <c r="R155" t="n">
-        <v>7006385</v>
+        <v>7006384</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18742,7 +18787,7 @@
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>Minst 260 plantor och 12 blomstjälkar med knopp på gång inom ca 2 x 1 m2 yta i granskog.</t>
+          <t>Minst 22 plantor och 1 blomstjälk med knopp på gång inom ca 1 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18775,7 +18820,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>134725184</v>
+        <v>134725177</v>
       </c>
       <c r="B156" t="n">
         <v>99195</v>
@@ -18826,10 +18871,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>494483</v>
+        <v>494375</v>
       </c>
       <c r="R156" t="n">
-        <v>7006367</v>
+        <v>7006421</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18866,7 +18911,7 @@
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>Minst 60 plantor och 4 blomstjälkar med knopp på gång inom ca 2 x 1 m2 yta i granskog.</t>
+          <t>Minst 60 plantor och 30 blomstjälkar med knopp på gång inom ca 2 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18899,39 +18944,47 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>134724956</v>
+        <v>134725179</v>
       </c>
       <c r="B157" t="n">
-        <v>109924</v>
+        <v>99195</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>221184</v>
+        <v>220787</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L157" t="inlineStr"/>
@@ -18942,10 +18995,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>494484</v>
+        <v>494432</v>
       </c>
       <c r="R157" t="n">
-        <v>7006603</v>
+        <v>7006477</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18978,6 +19031,11 @@
       <c r="AA157" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>Minst 27 plantor och 1 blomstjälk med knopp på gång inom ca 1 m2 yta i äldre granskog.</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -19010,39 +19068,47 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>134724957</v>
+        <v>134725180</v>
       </c>
       <c r="B158" t="n">
-        <v>109924</v>
+        <v>99195</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>221184</v>
+        <v>220787</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L158" t="inlineStr"/>
@@ -19053,10 +19119,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>494462</v>
+        <v>494483</v>
       </c>
       <c r="R158" t="n">
-        <v>7006579</v>
+        <v>7006405</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -19089,6 +19155,11 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Minst 200 plantor och 23 blomstjälkar med knopp på gång inom ca 4 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -19121,39 +19192,47 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>134724958</v>
+        <v>134725183</v>
       </c>
       <c r="B159" t="n">
-        <v>109924</v>
+        <v>99195</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>221184</v>
+        <v>220787</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L159" t="inlineStr"/>
@@ -19164,10 +19243,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>494557</v>
+        <v>494494</v>
       </c>
       <c r="R159" t="n">
-        <v>7006614</v>
+        <v>7006385</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -19200,6 +19279,11 @@
       <c r="AA159" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>Minst 260 plantor och 12 blomstjälkar med knopp på gång inom ca 2 x 1 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -19232,39 +19316,47 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>134724959</v>
+        <v>134725184</v>
       </c>
       <c r="B160" t="n">
-        <v>109924</v>
+        <v>99195</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>221184</v>
+        <v>220787</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L160" t="inlineStr"/>
@@ -19275,10 +19367,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>494573</v>
+        <v>494483</v>
       </c>
       <c r="R160" t="n">
-        <v>7006546</v>
+        <v>7006367</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -19311,6 +19403,11 @@
       <c r="AA160" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>Minst 60 plantor och 4 blomstjälkar med knopp på gång inom ca 2 x 1 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -19343,7 +19440,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>134724960</v>
+        <v>134724956</v>
       </c>
       <c r="B161" t="n">
         <v>109924</v>
@@ -19386,10 +19483,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>494410</v>
+        <v>494484</v>
       </c>
       <c r="R161" t="n">
-        <v>7006347</v>
+        <v>7006603</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -19454,7 +19551,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>134724961</v>
+        <v>134724957</v>
       </c>
       <c r="B162" t="n">
         <v>109924</v>
@@ -19497,10 +19594,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>494440</v>
+        <v>494462</v>
       </c>
       <c r="R162" t="n">
-        <v>7006466</v>
+        <v>7006579</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -19565,7 +19662,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>134724962</v>
+        <v>134724958</v>
       </c>
       <c r="B163" t="n">
         <v>109924</v>
@@ -19608,10 +19705,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>494467</v>
+        <v>494557</v>
       </c>
       <c r="R163" t="n">
-        <v>7006460</v>
+        <v>7006614</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19676,10 +19773,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>134724939</v>
+        <v>134724959</v>
       </c>
       <c r="B164" t="n">
-        <v>106309</v>
+        <v>109924</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19687,16 +19784,16 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>221725</v>
+        <v>221184</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Torta</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lactuca alpina</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -19704,19 +19801,11 @@
           <t>(L.) A. Gray</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L164" t="inlineStr"/>
@@ -19727,10 +19816,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>494520</v>
+        <v>494573</v>
       </c>
       <c r="R164" t="n">
-        <v>7006611</v>
+        <v>7006546</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19763,11 +19852,6 @@
       <c r="AA164" t="inlineStr">
         <is>
           <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>Minst 10 blomställningar inom ca 3 m2 yta.</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -19800,10 +19884,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>134724940</v>
+        <v>134724960</v>
       </c>
       <c r="B165" t="n">
-        <v>106309</v>
+        <v>109924</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19811,16 +19895,16 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>221725</v>
+        <v>221184</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Torta</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lactuca alpina</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -19832,7 +19916,7 @@
       <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L165" t="inlineStr"/>
@@ -19843,10 +19927,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>494489</v>
+        <v>494410</v>
       </c>
       <c r="R165" t="n">
-        <v>7006603</v>
+        <v>7006347</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19879,11 +19963,6 @@
       <c r="AA165" t="inlineStr">
         <is>
           <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC165" t="inlineStr">
-        <is>
-          <t>Minst 2 blomstjälkar.</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19916,10 +19995,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>134724941</v>
+        <v>134724961</v>
       </c>
       <c r="B166" t="n">
-        <v>106309</v>
+        <v>109924</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19927,16 +20006,16 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>221725</v>
+        <v>221184</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Torta</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lactuca alpina</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -19948,7 +20027,7 @@
       <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L166" t="inlineStr"/>
@@ -19959,10 +20038,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>494485</v>
+        <v>494440</v>
       </c>
       <c r="R166" t="n">
-        <v>7006591</v>
+        <v>7006466</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19995,11 +20074,6 @@
       <c r="AA166" t="inlineStr">
         <is>
           <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC166" t="inlineStr">
-        <is>
-          <t>Minst 2 blomstjälkar.</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -20032,10 +20106,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>134724942</v>
+        <v>134724962</v>
       </c>
       <c r="B167" t="n">
-        <v>106309</v>
+        <v>109924</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -20043,16 +20117,16 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>221725</v>
+        <v>221184</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Torta</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lactuca alpina</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -20064,7 +20138,7 @@
       <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L167" t="inlineStr"/>
@@ -20075,10 +20149,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>494511</v>
+        <v>494467</v>
       </c>
       <c r="R167" t="n">
-        <v>7006535</v>
+        <v>7006460</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -20111,11 +20185,6 @@
       <c r="AA167" t="inlineStr">
         <is>
           <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC167" t="inlineStr">
-        <is>
-          <t>Minst 2 blomstjälkar.</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -20148,7 +20217,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>134724943</v>
+        <v>134724939</v>
       </c>
       <c r="B168" t="n">
         <v>106309</v>
@@ -20178,7 +20247,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -20199,10 +20268,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>494583</v>
+        <v>494520</v>
       </c>
       <c r="R168" t="n">
-        <v>7006669</v>
+        <v>7006611</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -20235,6 +20304,11 @@
       <c r="AA168" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>Minst 10 blomställningar inom ca 3 m2 yta.</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -20267,7 +20341,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>134724944</v>
+        <v>134724940</v>
       </c>
       <c r="B169" t="n">
         <v>106309</v>
@@ -20295,16 +20369,8 @@
           <t>(L.) A. Gray</t>
         </is>
       </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J169" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -20318,10 +20384,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>494437</v>
+        <v>494489</v>
       </c>
       <c r="R169" t="n">
-        <v>7006395</v>
+        <v>7006603</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -20354,6 +20420,11 @@
       <c r="AA169" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>Minst 2 blomstjälkar.</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -20386,7 +20457,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>134724945</v>
+        <v>134724941</v>
       </c>
       <c r="B170" t="n">
         <v>106309</v>
@@ -20429,10 +20500,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>494436</v>
+        <v>494485</v>
       </c>
       <c r="R170" t="n">
-        <v>7006408</v>
+        <v>7006591</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -20465,6 +20536,11 @@
       <c r="AA170" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>Minst 2 blomstjälkar.</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -20497,7 +20573,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>134724947</v>
+        <v>134724942</v>
       </c>
       <c r="B171" t="n">
         <v>106309</v>
@@ -20540,10 +20616,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>494450</v>
+        <v>494511</v>
       </c>
       <c r="R171" t="n">
-        <v>7006398</v>
+        <v>7006535</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -20576,6 +20652,11 @@
       <c r="AA171" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>Minst 2 blomstjälkar.</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -20608,7 +20689,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>134724948</v>
+        <v>134724943</v>
       </c>
       <c r="B172" t="n">
         <v>106309</v>
@@ -20636,8 +20717,16 @@
           <t>(L.) A. Gray</t>
         </is>
       </c>
-      <c r="I172" t="inlineStr"/>
-      <c r="J172" t="inlineStr"/>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K172" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -20651,10 +20740,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>494409</v>
+        <v>494583</v>
       </c>
       <c r="R172" t="n">
-        <v>7006335</v>
+        <v>7006669</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -20687,11 +20776,6 @@
       <c r="AA172" t="inlineStr">
         <is>
           <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC172" t="inlineStr">
-        <is>
-          <t>Minst 3 blommande plantor.</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -20724,7 +20808,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>134724949</v>
+        <v>134724944</v>
       </c>
       <c r="B173" t="n">
         <v>106309</v>
@@ -20754,7 +20838,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -20775,10 +20859,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>494408</v>
+        <v>494437</v>
       </c>
       <c r="R173" t="n">
-        <v>7006399</v>
+        <v>7006395</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -20811,11 +20895,6 @@
       <c r="AA173" t="inlineStr">
         <is>
           <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC173" t="inlineStr">
-        <is>
-          <t>Minst 9 blommande plantor inom ca 3 m2 yta.</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -20848,7 +20927,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>134724950</v>
+        <v>134724945</v>
       </c>
       <c r="B174" t="n">
         <v>106309</v>
@@ -20876,16 +20955,8 @@
           <t>(L.) A. Gray</t>
         </is>
       </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J174" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -20899,10 +20970,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>494379</v>
+        <v>494436</v>
       </c>
       <c r="R174" t="n">
-        <v>7006421</v>
+        <v>7006408</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -20935,11 +21006,6 @@
       <c r="AA174" t="inlineStr">
         <is>
           <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC174" t="inlineStr">
-        <is>
-          <t>Minst två blommande plantor.</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -20972,7 +21038,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>134724951</v>
+        <v>134724947</v>
       </c>
       <c r="B175" t="n">
         <v>106309</v>
@@ -21015,10 +21081,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>494420</v>
+        <v>494450</v>
       </c>
       <c r="R175" t="n">
-        <v>7006474</v>
+        <v>7006398</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -21083,10 +21149,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>134725000</v>
+        <v>134724948</v>
       </c>
       <c r="B176" t="n">
-        <v>98060</v>
+        <v>106309</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21094,26 +21160,30 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>221945</v>
+        <v>221725</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr"/>
       <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
@@ -21122,10 +21192,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>494601</v>
+        <v>494409</v>
       </c>
       <c r="R176" t="n">
-        <v>7006682</v>
+        <v>7006335</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -21162,7 +21232,7 @@
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Minst 3 blommande plantor.</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -21195,10 +21265,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>134725001</v>
+        <v>134724949</v>
       </c>
       <c r="B177" t="n">
-        <v>98060</v>
+        <v>106309</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21206,26 +21276,38 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>221945</v>
+        <v>221725</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr"/>
-      <c r="J177" t="inlineStr"/>
-      <c r="K177" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr"/>
       <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
@@ -21234,10 +21316,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>494477</v>
+        <v>494408</v>
       </c>
       <c r="R177" t="n">
-        <v>7006369</v>
+        <v>7006399</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -21270,6 +21352,11 @@
       <c r="AA177" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>Minst 9 blommande plantor inom ca 3 m2 yta.</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -21302,10 +21389,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>134724974</v>
+        <v>134724950</v>
       </c>
       <c r="B178" t="n">
-        <v>99217</v>
+        <v>106309</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21313,28 +21400,36 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr"/>
-      <c r="J178" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L178" t="inlineStr"/>
@@ -21345,10 +21440,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>494638</v>
+        <v>494379</v>
       </c>
       <c r="R178" t="n">
-        <v>7006684</v>
+        <v>7006421</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -21381,6 +21476,11 @@
       <c r="AA178" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC178" t="inlineStr">
+        <is>
+          <t>Minst två blommande plantor.</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -21413,10 +21513,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>134724975</v>
+        <v>134724951</v>
       </c>
       <c r="B179" t="n">
-        <v>99217</v>
+        <v>106309</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21424,21 +21524,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -21456,10 +21556,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>494542</v>
+        <v>494420</v>
       </c>
       <c r="R179" t="n">
-        <v>7006561</v>
+        <v>7006474</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -21524,10 +21624,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>134724976</v>
+        <v>134725000</v>
       </c>
       <c r="B180" t="n">
-        <v>99217</v>
+        <v>98060</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21535,30 +21635,26 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr"/>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K180" t="inlineStr"/>
       <c r="L180" t="inlineStr"/>
       <c r="N180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
@@ -21567,10 +21663,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>494597</v>
+        <v>494601</v>
       </c>
       <c r="R180" t="n">
-        <v>7006574</v>
+        <v>7006682</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -21603,6 +21699,11 @@
       <c r="AA180" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC180" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -21635,10 +21736,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>134724977</v>
+        <v>134725001</v>
       </c>
       <c r="B181" t="n">
-        <v>99217</v>
+        <v>98060</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21646,30 +21747,26 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr"/>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K181" t="inlineStr"/>
       <c r="L181" t="inlineStr"/>
       <c r="N181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
@@ -21678,10 +21775,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>494573</v>
+        <v>494477</v>
       </c>
       <c r="R181" t="n">
-        <v>7006537</v>
+        <v>7006369</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -21746,7 +21843,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>134724978</v>
+        <v>134724974</v>
       </c>
       <c r="B182" t="n">
         <v>99217</v>
@@ -21789,10 +21886,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>494423</v>
+        <v>494638</v>
       </c>
       <c r="R182" t="n">
-        <v>7006438</v>
+        <v>7006684</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -21857,7 +21954,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>134724979</v>
+        <v>134724975</v>
       </c>
       <c r="B183" t="n">
         <v>99217</v>
@@ -21900,10 +21997,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>494456</v>
+        <v>494542</v>
       </c>
       <c r="R183" t="n">
-        <v>7006428</v>
+        <v>7006561</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -21968,7 +22065,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>134724980</v>
+        <v>134724976</v>
       </c>
       <c r="B184" t="n">
         <v>99217</v>
@@ -22011,10 +22108,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>494430</v>
+        <v>494597</v>
       </c>
       <c r="R184" t="n">
-        <v>7006412</v>
+        <v>7006574</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -22079,7 +22176,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>134724981</v>
+        <v>134724977</v>
       </c>
       <c r="B185" t="n">
         <v>99217</v>
@@ -22122,10 +22219,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>494444</v>
+        <v>494573</v>
       </c>
       <c r="R185" t="n">
-        <v>7006367</v>
+        <v>7006537</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -22190,7 +22287,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>134724982</v>
+        <v>134724978</v>
       </c>
       <c r="B186" t="n">
         <v>99217</v>
@@ -22222,7 +22319,7 @@
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L186" t="inlineStr"/>
@@ -22233,10 +22330,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>494422</v>
+        <v>494423</v>
       </c>
       <c r="R186" t="n">
-        <v>7006345</v>
+        <v>7006438</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -22301,7 +22398,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>134724983</v>
+        <v>134724979</v>
       </c>
       <c r="B187" t="n">
         <v>99217</v>
@@ -22344,10 +22441,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>494422</v>
+        <v>494456</v>
       </c>
       <c r="R187" t="n">
-        <v>7006322</v>
+        <v>7006428</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -22412,7 +22509,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>134724984</v>
+        <v>134724980</v>
       </c>
       <c r="B188" t="n">
         <v>99217</v>
@@ -22455,10 +22552,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>494424</v>
+        <v>494430</v>
       </c>
       <c r="R188" t="n">
-        <v>7006352</v>
+        <v>7006412</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -22523,7 +22620,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>134724985</v>
+        <v>134724981</v>
       </c>
       <c r="B189" t="n">
         <v>99217</v>
@@ -22566,10 +22663,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>494396</v>
+        <v>494444</v>
       </c>
       <c r="R189" t="n">
-        <v>7006361</v>
+        <v>7006367</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -22634,7 +22731,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>134724986</v>
+        <v>134724982</v>
       </c>
       <c r="B190" t="n">
         <v>99217</v>
@@ -22677,10 +22774,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>494373</v>
+        <v>494422</v>
       </c>
       <c r="R190" t="n">
-        <v>7006366</v>
+        <v>7006345</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -22745,7 +22842,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>134724987</v>
+        <v>134724983</v>
       </c>
       <c r="B191" t="n">
         <v>99217</v>
@@ -22788,10 +22885,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>494404</v>
+        <v>494422</v>
       </c>
       <c r="R191" t="n">
-        <v>7006377</v>
+        <v>7006322</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -22856,7 +22953,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>134724988</v>
+        <v>134724984</v>
       </c>
       <c r="B192" t="n">
         <v>99217</v>
@@ -22899,10 +22996,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>494406</v>
+        <v>494424</v>
       </c>
       <c r="R192" t="n">
-        <v>7006398</v>
+        <v>7006352</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -22967,7 +23064,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>134724989</v>
+        <v>134724985</v>
       </c>
       <c r="B193" t="n">
         <v>99217</v>
@@ -23010,10 +23107,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>494379</v>
+        <v>494396</v>
       </c>
       <c r="R193" t="n">
-        <v>7006433</v>
+        <v>7006361</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -23078,7 +23175,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>134724990</v>
+        <v>134724986</v>
       </c>
       <c r="B194" t="n">
         <v>99217</v>
@@ -23121,10 +23218,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>494377</v>
+        <v>494373</v>
       </c>
       <c r="R194" t="n">
-        <v>7006414</v>
+        <v>7006366</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -23189,7 +23286,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>134724991</v>
+        <v>134724987</v>
       </c>
       <c r="B195" t="n">
         <v>99217</v>
@@ -23232,10 +23329,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>494399</v>
+        <v>494404</v>
       </c>
       <c r="R195" t="n">
-        <v>7006417</v>
+        <v>7006377</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -23300,7 +23397,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>134724992</v>
+        <v>134724988</v>
       </c>
       <c r="B196" t="n">
         <v>99217</v>
@@ -23343,10 +23440,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>494413</v>
+        <v>494406</v>
       </c>
       <c r="R196" t="n">
-        <v>7006440</v>
+        <v>7006398</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -23411,7 +23508,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>134724993</v>
+        <v>134724989</v>
       </c>
       <c r="B197" t="n">
         <v>99217</v>
@@ -23454,10 +23551,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>494486</v>
+        <v>494379</v>
       </c>
       <c r="R197" t="n">
-        <v>7006376</v>
+        <v>7006433</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -23522,7 +23619,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>134724994</v>
+        <v>134724990</v>
       </c>
       <c r="B198" t="n">
         <v>99217</v>
@@ -23565,10 +23662,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>494470</v>
+        <v>494377</v>
       </c>
       <c r="R198" t="n">
-        <v>7006387</v>
+        <v>7006414</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -23633,10 +23730,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>134724964</v>
+        <v>134724991</v>
       </c>
       <c r="B199" t="n">
-        <v>104707</v>
+        <v>99217</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23644,36 +23741,28 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>222412</v>
+        <v>221952</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr"/>
+      <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L199" t="inlineStr"/>
@@ -23684,10 +23773,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>494391</v>
+        <v>494399</v>
       </c>
       <c r="R199" t="n">
-        <v>7006443</v>
+        <v>7006417</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -23752,10 +23841,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129402373</v>
+        <v>134724992</v>
       </c>
       <c r="B200" t="n">
-        <v>101325</v>
+        <v>99217</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23763,42 +23852,45 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>222498</v>
+        <v>221952</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
+      <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr"/>
+      <c r="N200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren-Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>494761</v>
+        <v>494413</v>
       </c>
       <c r="R200" t="n">
-        <v>7006746</v>
+        <v>7006440</v>
       </c>
       <c r="S200" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -23822,22 +23914,12 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="Z200" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB200" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -23846,6 +23928,7 @@
       <c r="AE200" t="b">
         <v>0</v>
       </c>
+      <c r="AF200" t="inlineStr"/>
       <c r="AG200" t="b">
         <v>0</v>
       </c>
@@ -23869,10 +23952,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129402502</v>
+        <v>134724993</v>
       </c>
       <c r="B201" t="n">
-        <v>101325</v>
+        <v>99217</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -23880,39 +23963,42 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>222498</v>
+        <v>221952</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
+      <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr"/>
+      <c r="N201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren-Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>494737</v>
+        <v>494486</v>
       </c>
       <c r="R201" t="n">
-        <v>7006737</v>
+        <v>7006376</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -23939,22 +24025,12 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="Z201" t="inlineStr">
-        <is>
-          <t>12:31</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB201" t="inlineStr">
-        <is>
-          <t>12:31</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -23963,6 +24039,7 @@
       <c r="AE201" t="b">
         <v>0</v>
       </c>
+      <c r="AF201" t="inlineStr"/>
       <c r="AG201" t="b">
         <v>0</v>
       </c>
@@ -23986,10 +24063,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>134725228</v>
+        <v>134724994</v>
       </c>
       <c r="B202" t="n">
-        <v>101403</v>
+        <v>99217</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -23997,28 +24074,28 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>222498</v>
+        <v>221952</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
       <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L202" t="inlineStr"/>
@@ -24029,10 +24106,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>494729</v>
+        <v>494470</v>
       </c>
       <c r="R202" t="n">
-        <v>7006733</v>
+        <v>7006387</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -24097,10 +24174,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>134725229</v>
+        <v>134724964</v>
       </c>
       <c r="B203" t="n">
-        <v>101403</v>
+        <v>104707</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24108,25 +24185,33 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I203" t="inlineStr"/>
-      <c r="J203" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K203" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -24140,10 +24225,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>494684</v>
+        <v>494391</v>
       </c>
       <c r="R203" t="n">
-        <v>7006730</v>
+        <v>7006443</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -24208,10 +24293,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>134725230</v>
+        <v>129402373</v>
       </c>
       <c r="B204" t="n">
-        <v>101403</v>
+        <v>101325</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -24237,27 +24322,24 @@
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
-      <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L204" t="inlineStr"/>
-      <c r="N204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Bergmyren-Barnsängbäcken, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>494561</v>
+        <v>494761</v>
       </c>
       <c r="R204" t="n">
-        <v>7006650</v>
+        <v>7006746</v>
       </c>
       <c r="S204" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -24281,12 +24363,22 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="Z204" t="inlineStr">
+        <is>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB204" t="inlineStr">
+        <is>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -24295,7 +24387,6 @@
       <c r="AE204" t="b">
         <v>0</v>
       </c>
-      <c r="AF204" t="inlineStr"/>
       <c r="AG204" t="b">
         <v>0</v>
       </c>
@@ -24319,10 +24410,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>134725231</v>
+        <v>129402502</v>
       </c>
       <c r="B205" t="n">
-        <v>101403</v>
+        <v>101325</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24348,24 +24439,21 @@
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
-      <c r="J205" t="inlineStr"/>
       <c r="K205" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L205" t="inlineStr"/>
-      <c r="N205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Bergmyren-Barnsängbäcken, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>494575</v>
+        <v>494737</v>
       </c>
       <c r="R205" t="n">
-        <v>7006614</v>
+        <v>7006737</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -24392,12 +24480,22 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB205" t="inlineStr">
+        <is>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -24406,7 +24504,6 @@
       <c r="AE205" t="b">
         <v>0</v>
       </c>
-      <c r="AF205" t="inlineStr"/>
       <c r="AG205" t="b">
         <v>0</v>
       </c>
@@ -24430,7 +24527,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>134725232</v>
+        <v>134725228</v>
       </c>
       <c r="B206" t="n">
         <v>101403</v>
@@ -24473,10 +24570,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>494431</v>
+        <v>494729</v>
       </c>
       <c r="R206" t="n">
-        <v>7006385</v>
+        <v>7006733</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -24541,7 +24638,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>134725233</v>
+        <v>134725229</v>
       </c>
       <c r="B207" t="n">
         <v>101403</v>
@@ -24584,10 +24681,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>494410</v>
+        <v>494684</v>
       </c>
       <c r="R207" t="n">
-        <v>7006372</v>
+        <v>7006730</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -24652,7 +24749,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>134725234</v>
+        <v>134725230</v>
       </c>
       <c r="B208" t="n">
         <v>101403</v>
@@ -24695,10 +24792,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>494461</v>
+        <v>494561</v>
       </c>
       <c r="R208" t="n">
-        <v>7006391</v>
+        <v>7006650</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -24763,7 +24860,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>134725235</v>
+        <v>134725231</v>
       </c>
       <c r="B209" t="n">
         <v>101403</v>
@@ -24806,10 +24903,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>494467</v>
+        <v>494575</v>
       </c>
       <c r="R209" t="n">
-        <v>7006362</v>
+        <v>7006614</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -24874,7 +24971,7 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>134725237</v>
+        <v>134725232</v>
       </c>
       <c r="B210" t="n">
         <v>101403</v>
@@ -24917,10 +25014,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>494394</v>
+        <v>494431</v>
       </c>
       <c r="R210" t="n">
-        <v>7006333</v>
+        <v>7006385</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -24985,7 +25082,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>134725238</v>
+        <v>134725233</v>
       </c>
       <c r="B211" t="n">
         <v>101403</v>
@@ -25028,10 +25125,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>494393</v>
+        <v>494410</v>
       </c>
       <c r="R211" t="n">
-        <v>7006434</v>
+        <v>7006372</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -25096,7 +25193,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>134725239</v>
+        <v>134725234</v>
       </c>
       <c r="B212" t="n">
         <v>101403</v>
@@ -25139,10 +25236,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>494417</v>
+        <v>494461</v>
       </c>
       <c r="R212" t="n">
-        <v>7006455</v>
+        <v>7006391</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -25207,7 +25304,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>134725240</v>
+        <v>134725235</v>
       </c>
       <c r="B213" t="n">
         <v>101403</v>
@@ -25250,10 +25347,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>494423</v>
+        <v>494467</v>
       </c>
       <c r="R213" t="n">
-        <v>7006466</v>
+        <v>7006362</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -25318,7 +25415,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>134725241</v>
+        <v>134725237</v>
       </c>
       <c r="B214" t="n">
         <v>101403</v>
@@ -25361,10 +25458,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>494447</v>
+        <v>494394</v>
       </c>
       <c r="R214" t="n">
-        <v>7006467</v>
+        <v>7006333</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -25429,7 +25526,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>134725242</v>
+        <v>134725238</v>
       </c>
       <c r="B215" t="n">
         <v>101403</v>
@@ -25472,10 +25569,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>494490</v>
+        <v>494393</v>
       </c>
       <c r="R215" t="n">
-        <v>7006391</v>
+        <v>7006434</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -25540,10 +25637,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>134724965</v>
+        <v>134725239</v>
       </c>
       <c r="B216" t="n">
-        <v>101305</v>
+        <v>101403</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -25551,28 +25648,28 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
       <c r="J216" t="inlineStr"/>
       <c r="K216" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L216" t="inlineStr"/>
@@ -25583,10 +25680,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>494525</v>
+        <v>494417</v>
       </c>
       <c r="R216" t="n">
-        <v>7006631</v>
+        <v>7006455</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -25651,10 +25748,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>134724967</v>
+        <v>134725240</v>
       </c>
       <c r="B217" t="n">
-        <v>101305</v>
+        <v>101403</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -25662,28 +25759,28 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
       <c r="J217" t="inlineStr"/>
       <c r="K217" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L217" t="inlineStr"/>
@@ -25694,10 +25791,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>494404</v>
+        <v>494423</v>
       </c>
       <c r="R217" t="n">
-        <v>7006352</v>
+        <v>7006466</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -25762,10 +25859,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>134724970</v>
+        <v>134725241</v>
       </c>
       <c r="B218" t="n">
-        <v>101305</v>
+        <v>101403</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25773,36 +25870,28 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I218" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J218" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr"/>
+      <c r="J218" t="inlineStr"/>
       <c r="K218" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L218" t="inlineStr"/>
@@ -25813,10 +25902,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>494394</v>
+        <v>494447</v>
       </c>
       <c r="R218" t="n">
-        <v>7006335</v>
+        <v>7006467</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -25849,11 +25938,6 @@
       <c r="AA218" t="inlineStr">
         <is>
           <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC218" t="inlineStr">
-        <is>
-          <t>Svart trolldruva som här täcker minst 7 m2 yta i ett ca 10-15 meter långt högörtsstråk. Både blomning och utblommad i frukt.</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -25886,10 +25970,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>134725065</v>
+        <v>134725242</v>
       </c>
       <c r="B219" t="n">
-        <v>99472</v>
+        <v>101403</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -25897,28 +25981,28 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>222812</v>
+        <v>222498</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
       <c r="J219" t="inlineStr"/>
       <c r="K219" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L219" t="inlineStr"/>
@@ -25929,10 +26013,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>494588</v>
+        <v>494490</v>
       </c>
       <c r="R219" t="n">
-        <v>7006682</v>
+        <v>7006391</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -25997,10 +26081,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>134725066</v>
+        <v>134724965</v>
       </c>
       <c r="B220" t="n">
-        <v>99472</v>
+        <v>101305</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -26008,16 +26092,16 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>222812</v>
+        <v>222771</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -26029,7 +26113,7 @@
       <c r="J220" t="inlineStr"/>
       <c r="K220" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L220" t="inlineStr"/>
@@ -26040,10 +26124,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>494575</v>
+        <v>494525</v>
       </c>
       <c r="R220" t="n">
-        <v>7006657</v>
+        <v>7006631</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -26108,10 +26192,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>134725067</v>
+        <v>134724967</v>
       </c>
       <c r="B221" t="n">
-        <v>99472</v>
+        <v>101305</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26119,16 +26203,16 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>222812</v>
+        <v>222771</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -26151,10 +26235,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>494403</v>
+        <v>494404</v>
       </c>
       <c r="R221" t="n">
-        <v>7006330</v>
+        <v>7006352</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -26219,10 +26303,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>134725222</v>
+        <v>134724970</v>
       </c>
       <c r="B222" t="n">
-        <v>99504</v>
+        <v>101305</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26230,25 +26314,33 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>222857</v>
+        <v>222771</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Ekorrbär</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Maianthemum bifolium</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(L.) F. W. Schmidt</t>
-        </is>
-      </c>
-      <c r="I222" t="inlineStr"/>
-      <c r="J222" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K222" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -26262,10 +26354,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>494531</v>
+        <v>494394</v>
       </c>
       <c r="R222" t="n">
-        <v>7006621</v>
+        <v>7006335</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -26298,6 +26390,11 @@
       <c r="AA222" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC222" t="inlineStr">
+        <is>
+          <t>Svart trolldruva som här täcker minst 7 m2 yta i ett ca 10-15 meter långt högörtsstråk. Både blomning och utblommad i frukt.</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -26330,10 +26427,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>134725223</v>
+        <v>134725065</v>
       </c>
       <c r="B223" t="n">
-        <v>99504</v>
+        <v>99472</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -26341,21 +26438,21 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>222857</v>
+        <v>222812</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Ekorrbär</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Maianthemum bifolium</t>
+          <t>Convallaria majalis</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(L.) F. W. Schmidt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -26373,10 +26470,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>494476</v>
+        <v>494588</v>
       </c>
       <c r="R223" t="n">
-        <v>7006370</v>
+        <v>7006682</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -26441,10 +26538,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>134725190</v>
+        <v>134725066</v>
       </c>
       <c r="B224" t="n">
-        <v>102871</v>
+        <v>99472</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -26452,16 +26549,16 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>223037</v>
+        <v>222812</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Humleblomster</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Geum rivale</t>
+          <t>Convallaria majalis</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -26484,10 +26581,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>494603</v>
+        <v>494575</v>
       </c>
       <c r="R224" t="n">
-        <v>7006548</v>
+        <v>7006657</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -26552,10 +26649,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>134725192</v>
+        <v>134725067</v>
       </c>
       <c r="B225" t="n">
-        <v>102871</v>
+        <v>99472</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26563,16 +26660,16 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>223037</v>
+        <v>222812</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Humleblomster</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Geum rivale</t>
+          <t>Convallaria majalis</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -26584,7 +26681,7 @@
       <c r="J225" t="inlineStr"/>
       <c r="K225" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L225" t="inlineStr"/>
@@ -26595,10 +26692,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>494533</v>
+        <v>494403</v>
       </c>
       <c r="R225" t="n">
-        <v>7006513</v>
+        <v>7006330</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -26663,10 +26760,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>134725002</v>
+        <v>134725222</v>
       </c>
       <c r="B226" t="n">
-        <v>99001</v>
+        <v>99504</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -26674,28 +26771,28 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>223049</v>
+        <v>222857</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Ekorrbär</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Maianthemum bifolium</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) F. W. Schmidt</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
       <c r="J226" t="inlineStr"/>
       <c r="K226" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L226" t="inlineStr"/>
@@ -26706,10 +26803,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>494743</v>
+        <v>494531</v>
       </c>
       <c r="R226" t="n">
-        <v>7006752</v>
+        <v>7006621</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -26774,10 +26871,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>134725003</v>
+        <v>134725223</v>
       </c>
       <c r="B227" t="n">
-        <v>99001</v>
+        <v>99504</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -26785,28 +26882,28 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>223049</v>
+        <v>222857</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Ekorrbär</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Maianthemum bifolium</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) F. W. Schmidt</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
       <c r="J227" t="inlineStr"/>
       <c r="K227" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L227" t="inlineStr"/>
@@ -26817,10 +26914,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>494682</v>
+        <v>494476</v>
       </c>
       <c r="R227" t="n">
-        <v>7006728</v>
+        <v>7006370</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -26885,10 +26982,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>134725004</v>
+        <v>134725190</v>
       </c>
       <c r="B228" t="n">
-        <v>99001</v>
+        <v>102871</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -26896,16 +26993,16 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>223049</v>
+        <v>223037</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Humleblomster</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Geum rivale</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -26917,7 +27014,7 @@
       <c r="J228" t="inlineStr"/>
       <c r="K228" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L228" t="inlineStr"/>
@@ -26928,10 +27025,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>494658</v>
+        <v>494603</v>
       </c>
       <c r="R228" t="n">
-        <v>7006681</v>
+        <v>7006548</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -26996,10 +27093,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>134725005</v>
+        <v>134725192</v>
       </c>
       <c r="B229" t="n">
-        <v>99001</v>
+        <v>102871</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -27007,16 +27104,16 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>223049</v>
+        <v>223037</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Humleblomster</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Geum rivale</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -27028,7 +27125,7 @@
       <c r="J229" t="inlineStr"/>
       <c r="K229" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L229" t="inlineStr"/>
@@ -27039,10 +27136,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>494555</v>
+        <v>494533</v>
       </c>
       <c r="R229" t="n">
-        <v>7006634</v>
+        <v>7006513</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -27107,7 +27204,7 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>134725006</v>
+        <v>134725002</v>
       </c>
       <c r="B230" t="n">
         <v>99001</v>
@@ -27139,7 +27236,7 @@
       <c r="J230" t="inlineStr"/>
       <c r="K230" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L230" t="inlineStr"/>
@@ -27150,10 +27247,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>494526</v>
+        <v>494743</v>
       </c>
       <c r="R230" t="n">
-        <v>7006591</v>
+        <v>7006752</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -27218,7 +27315,7 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>134725007</v>
+        <v>134725003</v>
       </c>
       <c r="B231" t="n">
         <v>99001</v>
@@ -27261,10 +27358,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>494592</v>
+        <v>494682</v>
       </c>
       <c r="R231" t="n">
-        <v>7006574</v>
+        <v>7006728</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -27329,7 +27426,7 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>134725008</v>
+        <v>134725004</v>
       </c>
       <c r="B232" t="n">
         <v>99001</v>
@@ -27372,10 +27469,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>494605</v>
+        <v>494658</v>
       </c>
       <c r="R232" t="n">
-        <v>7006636</v>
+        <v>7006681</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -27440,7 +27537,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>134725009</v>
+        <v>134725005</v>
       </c>
       <c r="B233" t="n">
         <v>99001</v>
@@ -27472,7 +27569,7 @@
       <c r="J233" t="inlineStr"/>
       <c r="K233" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L233" t="inlineStr"/>
@@ -27483,10 +27580,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>494569</v>
+        <v>494555</v>
       </c>
       <c r="R233" t="n">
-        <v>7006663</v>
+        <v>7006634</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -27551,7 +27648,7 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>134725010</v>
+        <v>134725006</v>
       </c>
       <c r="B234" t="n">
         <v>99001</v>
@@ -27594,10 +27691,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>494578</v>
+        <v>494526</v>
       </c>
       <c r="R234" t="n">
-        <v>7006546</v>
+        <v>7006591</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -27662,7 +27759,7 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>134725011</v>
+        <v>134725007</v>
       </c>
       <c r="B235" t="n">
         <v>99001</v>
@@ -27694,7 +27791,7 @@
       <c r="J235" t="inlineStr"/>
       <c r="K235" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L235" t="inlineStr"/>
@@ -27705,10 +27802,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>494543</v>
+        <v>494592</v>
       </c>
       <c r="R235" t="n">
-        <v>7006535</v>
+        <v>7006574</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -27773,7 +27870,7 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>134725012</v>
+        <v>134725008</v>
       </c>
       <c r="B236" t="n">
         <v>99001</v>
@@ -27805,7 +27902,7 @@
       <c r="J236" t="inlineStr"/>
       <c r="K236" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L236" t="inlineStr"/>
@@ -27816,10 +27913,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>494505</v>
+        <v>494605</v>
       </c>
       <c r="R236" t="n">
-        <v>7006509</v>
+        <v>7006636</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -27884,7 +27981,7 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>134725013</v>
+        <v>134725009</v>
       </c>
       <c r="B237" t="n">
         <v>99001</v>
@@ -27927,10 +28024,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>494397</v>
+        <v>494569</v>
       </c>
       <c r="R237" t="n">
-        <v>7006333</v>
+        <v>7006663</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -27995,7 +28092,7 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>134725014</v>
+        <v>134725010</v>
       </c>
       <c r="B238" t="n">
         <v>99001</v>
@@ -28027,7 +28124,7 @@
       <c r="J238" t="inlineStr"/>
       <c r="K238" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L238" t="inlineStr"/>
@@ -28038,10 +28135,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>494366</v>
+        <v>494578</v>
       </c>
       <c r="R238" t="n">
-        <v>7006343</v>
+        <v>7006546</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -28106,7 +28203,7 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>134725015</v>
+        <v>134725011</v>
       </c>
       <c r="B239" t="n">
         <v>99001</v>
@@ -28149,10 +28246,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>494447</v>
+        <v>494543</v>
       </c>
       <c r="R239" t="n">
-        <v>7006486</v>
+        <v>7006535</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -28217,7 +28314,7 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>134725016</v>
+        <v>134725012</v>
       </c>
       <c r="B240" t="n">
         <v>99001</v>
@@ -28249,7 +28346,7 @@
       <c r="J240" t="inlineStr"/>
       <c r="K240" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L240" t="inlineStr"/>
@@ -28260,10 +28357,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>494442</v>
+        <v>494505</v>
       </c>
       <c r="R240" t="n">
-        <v>7006455</v>
+        <v>7006509</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -28328,7 +28425,7 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>134725017</v>
+        <v>134725013</v>
       </c>
       <c r="B241" t="n">
         <v>99001</v>
@@ -28371,10 +28468,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>494436</v>
+        <v>494397</v>
       </c>
       <c r="R241" t="n">
-        <v>7006500</v>
+        <v>7006333</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -28439,7 +28536,7 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>134725018</v>
+        <v>134725014</v>
       </c>
       <c r="B242" t="n">
         <v>99001</v>
@@ -28482,10 +28579,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>494469</v>
+        <v>494366</v>
       </c>
       <c r="R242" t="n">
-        <v>7006406</v>
+        <v>7006343</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -28550,10 +28647,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>134725194</v>
+        <v>134725015</v>
       </c>
       <c r="B243" t="n">
-        <v>98249</v>
+        <v>99001</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -28561,21 +28658,21 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>223358</v>
+        <v>223049</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -28593,10 +28690,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>494649</v>
+        <v>494447</v>
       </c>
       <c r="R243" t="n">
-        <v>7006702</v>
+        <v>7006486</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -28661,10 +28758,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>134725195</v>
+        <v>134725016</v>
       </c>
       <c r="B244" t="n">
-        <v>98249</v>
+        <v>99001</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -28672,21 +28769,21 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>223358</v>
+        <v>223049</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
@@ -28704,10 +28801,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>494656</v>
+        <v>494442</v>
       </c>
       <c r="R244" t="n">
-        <v>7006675</v>
+        <v>7006455</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -28740,11 +28837,6 @@
       <c r="AA244" t="inlineStr">
         <is>
           <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC244" t="inlineStr">
-        <is>
-          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -28777,10 +28869,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>134725197</v>
+        <v>134725017</v>
       </c>
       <c r="B245" t="n">
-        <v>98249</v>
+        <v>99001</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -28788,21 +28880,21 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>223358</v>
+        <v>223049</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -28820,10 +28912,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>494555</v>
+        <v>494436</v>
       </c>
       <c r="R245" t="n">
-        <v>7006667</v>
+        <v>7006500</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -28888,10 +28980,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>134725198</v>
+        <v>134725018</v>
       </c>
       <c r="B246" t="n">
-        <v>98249</v>
+        <v>99001</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -28899,21 +28991,21 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>223358</v>
+        <v>223049</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -28931,10 +29023,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>494482</v>
+        <v>494469</v>
       </c>
       <c r="R246" t="n">
-        <v>7006602</v>
+        <v>7006406</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -28999,7 +29091,7 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>134725200</v>
+        <v>134725194</v>
       </c>
       <c r="B247" t="n">
         <v>98249</v>
@@ -29042,10 +29134,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>494610</v>
+        <v>494649</v>
       </c>
       <c r="R247" t="n">
-        <v>7006669</v>
+        <v>7006702</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -29110,7 +29202,7 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>134725201</v>
+        <v>134725195</v>
       </c>
       <c r="B248" t="n">
         <v>98249</v>
@@ -29153,10 +29245,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>494574</v>
+        <v>494656</v>
       </c>
       <c r="R248" t="n">
-        <v>7006545</v>
+        <v>7006675</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -29189,6 +29281,11 @@
       <c r="AA248" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC248" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -29221,7 +29318,7 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>134725203</v>
+        <v>134725197</v>
       </c>
       <c r="B249" t="n">
         <v>98249</v>
@@ -29264,10 +29361,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>494447</v>
+        <v>494555</v>
       </c>
       <c r="R249" t="n">
-        <v>7006429</v>
+        <v>7006667</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -29332,7 +29429,7 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>134725205</v>
+        <v>134725198</v>
       </c>
       <c r="B250" t="n">
         <v>98249</v>
@@ -29375,10 +29472,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>494390</v>
+        <v>494482</v>
       </c>
       <c r="R250" t="n">
-        <v>7006347</v>
+        <v>7006602</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -29411,11 +29508,6 @@
       <c r="AA250" t="inlineStr">
         <is>
           <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC250" t="inlineStr">
-        <is>
-          <t>Rikligt med hultbräken i ett frodigt fältskikt.</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -29448,7 +29540,7 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>134725206</v>
+        <v>134725200</v>
       </c>
       <c r="B251" t="n">
         <v>98249</v>
@@ -29491,10 +29583,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>494401</v>
+        <v>494610</v>
       </c>
       <c r="R251" t="n">
-        <v>7006335</v>
+        <v>7006669</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -29527,11 +29619,6 @@
       <c r="AA251" t="inlineStr">
         <is>
           <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC251" t="inlineStr">
-        <is>
-          <t>Rikligt med hultbräken på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -29564,7 +29651,7 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>134725208</v>
+        <v>134725201</v>
       </c>
       <c r="B252" t="n">
         <v>98249</v>
@@ -29607,10 +29694,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>494394</v>
+        <v>494574</v>
       </c>
       <c r="R252" t="n">
-        <v>7006324</v>
+        <v>7006545</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -29675,7 +29762,7 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>134725209</v>
+        <v>134725203</v>
       </c>
       <c r="B253" t="n">
         <v>98249</v>
@@ -29718,10 +29805,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>494368</v>
+        <v>494447</v>
       </c>
       <c r="R253" t="n">
-        <v>7006343</v>
+        <v>7006429</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -29786,7 +29873,7 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>134725211</v>
+        <v>134725205</v>
       </c>
       <c r="B254" t="n">
         <v>98249</v>
@@ -29829,10 +29916,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>494422</v>
+        <v>494390</v>
       </c>
       <c r="R254" t="n">
-        <v>7006467</v>
+        <v>7006347</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -29865,6 +29952,11 @@
       <c r="AA254" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC254" t="inlineStr">
+        <is>
+          <t>Rikligt med hultbräken i ett frodigt fältskikt.</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -29897,7 +29989,7 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>134725212</v>
+        <v>134725206</v>
       </c>
       <c r="B255" t="n">
         <v>98249</v>
@@ -29940,10 +30032,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>494439</v>
+        <v>494401</v>
       </c>
       <c r="R255" t="n">
-        <v>7006466</v>
+        <v>7006335</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -29976,6 +30068,11 @@
       <c r="AA255" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC255" t="inlineStr">
+        <is>
+          <t>Rikligt med hultbräken på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -30008,7 +30105,7 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>134725213</v>
+        <v>134725208</v>
       </c>
       <c r="B256" t="n">
         <v>98249</v>
@@ -30051,10 +30148,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>494471</v>
+        <v>494394</v>
       </c>
       <c r="R256" t="n">
-        <v>7006477</v>
+        <v>7006324</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -30119,10 +30216,10 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>134725019</v>
+        <v>134725209</v>
       </c>
       <c r="B257" t="n">
-        <v>101293</v>
+        <v>98249</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -30130,28 +30227,28 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>224885</v>
+        <v>223358</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
       <c r="J257" t="inlineStr"/>
       <c r="K257" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L257" t="inlineStr"/>
@@ -30162,10 +30259,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>494758</v>
+        <v>494368</v>
       </c>
       <c r="R257" t="n">
-        <v>7006733</v>
+        <v>7006343</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -30230,10 +30327,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>134725020</v>
+        <v>134725211</v>
       </c>
       <c r="B258" t="n">
-        <v>101293</v>
+        <v>98249</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -30241,28 +30338,28 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>224885</v>
+        <v>223358</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
       <c r="J258" t="inlineStr"/>
       <c r="K258" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L258" t="inlineStr"/>
@@ -30273,10 +30370,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>494754</v>
+        <v>494422</v>
       </c>
       <c r="R258" t="n">
-        <v>7006740</v>
+        <v>7006467</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -30341,10 +30438,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>134725021</v>
+        <v>134725212</v>
       </c>
       <c r="B259" t="n">
-        <v>101293</v>
+        <v>98249</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -30352,28 +30449,28 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>224885</v>
+        <v>223358</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
       <c r="J259" t="inlineStr"/>
       <c r="K259" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L259" t="inlineStr"/>
@@ -30384,10 +30481,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>494727</v>
+        <v>494439</v>
       </c>
       <c r="R259" t="n">
-        <v>7006747</v>
+        <v>7006466</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -30452,10 +30549,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>134725022</v>
+        <v>134725213</v>
       </c>
       <c r="B260" t="n">
-        <v>101293</v>
+        <v>98249</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -30463,28 +30560,28 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>224885</v>
+        <v>223358</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
       <c r="J260" t="inlineStr"/>
       <c r="K260" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L260" t="inlineStr"/>
@@ -30495,10 +30592,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>494537</v>
+        <v>494471</v>
       </c>
       <c r="R260" t="n">
-        <v>7006666</v>
+        <v>7006477</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -30563,7 +30660,7 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>134725023</v>
+        <v>134725019</v>
       </c>
       <c r="B261" t="n">
         <v>101293</v>
@@ -30606,10 +30703,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>494554</v>
+        <v>494758</v>
       </c>
       <c r="R261" t="n">
-        <v>7006673</v>
+        <v>7006733</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -30674,7 +30771,7 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>134725024</v>
+        <v>134725020</v>
       </c>
       <c r="B262" t="n">
         <v>101293</v>
@@ -30717,10 +30814,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>494513</v>
+        <v>494754</v>
       </c>
       <c r="R262" t="n">
-        <v>7006628</v>
+        <v>7006740</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -30785,7 +30882,7 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>134725025</v>
+        <v>134725021</v>
       </c>
       <c r="B263" t="n">
         <v>101293</v>
@@ -30828,10 +30925,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>494500</v>
+        <v>494727</v>
       </c>
       <c r="R263" t="n">
-        <v>7006617</v>
+        <v>7006747</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -30864,11 +30961,6 @@
       <c r="AA263" t="inlineStr">
         <is>
           <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC263" t="inlineStr">
-        <is>
-          <t>Rikligt vid en bäck.</t>
         </is>
       </c>
       <c r="AD263" t="b">
@@ -30901,7 +30993,7 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>134725026</v>
+        <v>134725022</v>
       </c>
       <c r="B264" t="n">
         <v>101293</v>
@@ -30944,10 +31036,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>494475</v>
+        <v>494537</v>
       </c>
       <c r="R264" t="n">
-        <v>7006607</v>
+        <v>7006666</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -30980,11 +31072,6 @@
       <c r="AA264" t="inlineStr">
         <is>
           <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC264" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD264" t="b">
@@ -31017,7 +31104,7 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>134725027</v>
+        <v>134725023</v>
       </c>
       <c r="B265" t="n">
         <v>101293</v>
@@ -31060,10 +31147,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>494484</v>
+        <v>494554</v>
       </c>
       <c r="R265" t="n">
-        <v>7006600</v>
+        <v>7006673</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -31096,11 +31183,6 @@
       <c r="AA265" t="inlineStr">
         <is>
           <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC265" t="inlineStr">
-        <is>
-          <t>Vid en bäck.</t>
         </is>
       </c>
       <c r="AD265" t="b">
@@ -31133,7 +31215,7 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>134725028</v>
+        <v>134725024</v>
       </c>
       <c r="B266" t="n">
         <v>101293</v>
@@ -31179,7 +31261,7 @@
         <v>494513</v>
       </c>
       <c r="R266" t="n">
-        <v>7006578</v>
+        <v>7006628</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -31244,7 +31326,7 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>134725029</v>
+        <v>134725025</v>
       </c>
       <c r="B267" t="n">
         <v>101293</v>
@@ -31287,10 +31369,10 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>494499</v>
+        <v>494500</v>
       </c>
       <c r="R267" t="n">
-        <v>7006578</v>
+        <v>7006617</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -31323,6 +31405,11 @@
       <c r="AA267" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC267" t="inlineStr">
+        <is>
+          <t>Rikligt vid en bäck.</t>
         </is>
       </c>
       <c r="AD267" t="b">
@@ -31355,7 +31442,7 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>134725030</v>
+        <v>134725026</v>
       </c>
       <c r="B268" t="n">
         <v>101293</v>
@@ -31398,10 +31485,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>494569</v>
+        <v>494475</v>
       </c>
       <c r="R268" t="n">
-        <v>7006566</v>
+        <v>7006607</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -31434,6 +31521,11 @@
       <c r="AA268" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC268" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -31466,7 +31558,7 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>134725031</v>
+        <v>134725027</v>
       </c>
       <c r="B269" t="n">
         <v>101293</v>
@@ -31498,7 +31590,7 @@
       <c r="J269" t="inlineStr"/>
       <c r="K269" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L269" t="inlineStr"/>
@@ -31509,10 +31601,10 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>494575</v>
+        <v>494484</v>
       </c>
       <c r="R269" t="n">
-        <v>7006647</v>
+        <v>7006600</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -31545,6 +31637,11 @@
       <c r="AA269" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC269" t="inlineStr">
+        <is>
+          <t>Vid en bäck.</t>
         </is>
       </c>
       <c r="AD269" t="b">
@@ -31577,7 +31674,7 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>134725032</v>
+        <v>134725028</v>
       </c>
       <c r="B270" t="n">
         <v>101293</v>
@@ -31620,10 +31717,10 @@
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>494604</v>
+        <v>494513</v>
       </c>
       <c r="R270" t="n">
-        <v>7006546</v>
+        <v>7006578</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -31656,11 +31753,6 @@
       <c r="AA270" t="inlineStr">
         <is>
           <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC270" t="inlineStr">
-        <is>
-          <t>Relativt rikligt.</t>
         </is>
       </c>
       <c r="AD270" t="b">
@@ -31693,7 +31785,7 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>134725033</v>
+        <v>134725029</v>
       </c>
       <c r="B271" t="n">
         <v>101293</v>
@@ -31725,7 +31817,7 @@
       <c r="J271" t="inlineStr"/>
       <c r="K271" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L271" t="inlineStr"/>
@@ -31736,10 +31828,10 @@
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>494563</v>
+        <v>494499</v>
       </c>
       <c r="R271" t="n">
-        <v>7006546</v>
+        <v>7006578</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -31804,7 +31896,7 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>134725034</v>
+        <v>134725030</v>
       </c>
       <c r="B272" t="n">
         <v>101293</v>
@@ -31836,7 +31928,7 @@
       <c r="J272" t="inlineStr"/>
       <c r="K272" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L272" t="inlineStr"/>
@@ -31847,10 +31939,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>494549</v>
+        <v>494569</v>
       </c>
       <c r="R272" t="n">
-        <v>7006531</v>
+        <v>7006566</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -31915,7 +32007,7 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>134725035</v>
+        <v>134725031</v>
       </c>
       <c r="B273" t="n">
         <v>101293</v>
@@ -31958,10 +32050,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>494406</v>
+        <v>494575</v>
       </c>
       <c r="R273" t="n">
-        <v>7006357</v>
+        <v>7006647</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -32026,7 +32118,7 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>134725036</v>
+        <v>134725032</v>
       </c>
       <c r="B274" t="n">
         <v>101293</v>
@@ -32069,10 +32161,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>494388</v>
+        <v>494604</v>
       </c>
       <c r="R274" t="n">
-        <v>7006347</v>
+        <v>7006546</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -32105,6 +32197,11 @@
       <c r="AA274" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC274" t="inlineStr">
+        <is>
+          <t>Relativt rikligt.</t>
         </is>
       </c>
       <c r="AD274" t="b">
@@ -32137,7 +32234,7 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>134725037</v>
+        <v>134725033</v>
       </c>
       <c r="B275" t="n">
         <v>101293</v>
@@ -32169,7 +32266,7 @@
       <c r="J275" t="inlineStr"/>
       <c r="K275" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L275" t="inlineStr"/>
@@ -32180,10 +32277,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>494401</v>
+        <v>494563</v>
       </c>
       <c r="R275" t="n">
-        <v>7006327</v>
+        <v>7006546</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -32216,11 +32313,6 @@
       <c r="AA275" t="inlineStr">
         <is>
           <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC275" t="inlineStr">
-        <is>
-          <t>Rikligt med nordisk stormhatt i ett högörtsstråk i en lucka i granskogen.</t>
         </is>
       </c>
       <c r="AD275" t="b">
@@ -32253,7 +32345,7 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>134725038</v>
+        <v>134725034</v>
       </c>
       <c r="B276" t="n">
         <v>101293</v>
@@ -32296,10 +32388,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>494394</v>
+        <v>494549</v>
       </c>
       <c r="R276" t="n">
-        <v>7006324</v>
+        <v>7006531</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -32364,7 +32456,7 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>134725039</v>
+        <v>134725035</v>
       </c>
       <c r="B277" t="n">
         <v>101293</v>
@@ -32407,10 +32499,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>494370</v>
+        <v>494406</v>
       </c>
       <c r="R277" t="n">
-        <v>7006343</v>
+        <v>7006357</v>
       </c>
       <c r="S277" t="n">
         <v>10</v>
@@ -32475,7 +32567,7 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>134725040</v>
+        <v>134725036</v>
       </c>
       <c r="B278" t="n">
         <v>101293</v>
@@ -32507,7 +32599,7 @@
       <c r="J278" t="inlineStr"/>
       <c r="K278" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L278" t="inlineStr"/>
@@ -32518,10 +32610,10 @@
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>494386</v>
+        <v>494388</v>
       </c>
       <c r="R278" t="n">
-        <v>7006443</v>
+        <v>7006347</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -32586,7 +32678,7 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>134725041</v>
+        <v>134725037</v>
       </c>
       <c r="B279" t="n">
         <v>101293</v>
@@ -32618,7 +32710,7 @@
       <c r="J279" t="inlineStr"/>
       <c r="K279" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L279" t="inlineStr"/>
@@ -32629,10 +32721,10 @@
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>494417</v>
+        <v>494401</v>
       </c>
       <c r="R279" t="n">
-        <v>7006459</v>
+        <v>7006327</v>
       </c>
       <c r="S279" t="n">
         <v>10</v>
@@ -32665,6 +32757,11 @@
       <c r="AA279" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC279" t="inlineStr">
+        <is>
+          <t>Rikligt med nordisk stormhatt i ett högörtsstråk i en lucka i granskogen.</t>
         </is>
       </c>
       <c r="AD279" t="b">
@@ -32697,7 +32794,7 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>134725042</v>
+        <v>134725038</v>
       </c>
       <c r="B280" t="n">
         <v>101293</v>
@@ -32740,10 +32837,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>494440</v>
+        <v>494394</v>
       </c>
       <c r="R280" t="n">
-        <v>7006462</v>
+        <v>7006324</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -32808,7 +32905,7 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>134725043</v>
+        <v>134725039</v>
       </c>
       <c r="B281" t="n">
         <v>101293</v>
@@ -32840,7 +32937,7 @@
       <c r="J281" t="inlineStr"/>
       <c r="K281" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L281" t="inlineStr"/>
@@ -32851,10 +32948,10 @@
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>494466</v>
+        <v>494370</v>
       </c>
       <c r="R281" t="n">
-        <v>7006455</v>
+        <v>7006343</v>
       </c>
       <c r="S281" t="n">
         <v>10</v>
@@ -32916,6 +33013,450 @@
         </is>
       </c>
       <c r="AY281" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>134725040</v>
+      </c>
+      <c r="B282" t="n">
+        <v>101293</v>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E282" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr"/>
+      <c r="J282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr"/>
+      <c r="N282" t="inlineStr"/>
+      <c r="P282" t="inlineStr">
+        <is>
+          <t>Bergmyren-Barnsängbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q282" t="n">
+        <v>494386</v>
+      </c>
+      <c r="R282" t="n">
+        <v>7006443</v>
+      </c>
+      <c r="S282" t="n">
+        <v>10</v>
+      </c>
+      <c r="T282" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U282" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V282" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W282" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y282" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD282" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE282" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF282" t="inlineStr"/>
+      <c r="AG282" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH282" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT282" t="inlineStr"/>
+      <c r="AW282" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX282" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY282" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>134725041</v>
+      </c>
+      <c r="B283" t="n">
+        <v>101293</v>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E283" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr"/>
+      <c r="J283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr"/>
+      <c r="N283" t="inlineStr"/>
+      <c r="P283" t="inlineStr">
+        <is>
+          <t>Bergmyren-Barnsängbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q283" t="n">
+        <v>494417</v>
+      </c>
+      <c r="R283" t="n">
+        <v>7006459</v>
+      </c>
+      <c r="S283" t="n">
+        <v>10</v>
+      </c>
+      <c r="T283" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U283" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V283" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W283" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y283" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AA283" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD283" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE283" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF283" t="inlineStr"/>
+      <c r="AG283" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH283" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT283" t="inlineStr"/>
+      <c r="AW283" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX283" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY283" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>134725042</v>
+      </c>
+      <c r="B284" t="n">
+        <v>101293</v>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E284" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr"/>
+      <c r="J284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr"/>
+      <c r="N284" t="inlineStr"/>
+      <c r="P284" t="inlineStr">
+        <is>
+          <t>Bergmyren-Barnsängbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q284" t="n">
+        <v>494440</v>
+      </c>
+      <c r="R284" t="n">
+        <v>7006462</v>
+      </c>
+      <c r="S284" t="n">
+        <v>10</v>
+      </c>
+      <c r="T284" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U284" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V284" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W284" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y284" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AA284" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD284" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE284" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF284" t="inlineStr"/>
+      <c r="AG284" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH284" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT284" t="inlineStr"/>
+      <c r="AW284" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX284" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY284" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>134725043</v>
+      </c>
+      <c r="B285" t="n">
+        <v>101293</v>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E285" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr"/>
+      <c r="J285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr"/>
+      <c r="N285" t="inlineStr"/>
+      <c r="P285" t="inlineStr">
+        <is>
+          <t>Bergmyren-Barnsängbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q285" t="n">
+        <v>494466</v>
+      </c>
+      <c r="R285" t="n">
+        <v>7006455</v>
+      </c>
+      <c r="S285" t="n">
+        <v>10</v>
+      </c>
+      <c r="T285" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U285" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V285" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W285" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y285" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AA285" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD285" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE285" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF285" t="inlineStr"/>
+      <c r="AG285" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH285" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT285" t="inlineStr"/>
+      <c r="AW285" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX285" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY285" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5791-2026 artfynd.xlsx
+++ b/artfynd/A 5791-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY285"/>
+  <dimension ref="A1:AZ285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -807,6 +812,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725214</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -939,6 +949,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122361219</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1046,6 +1061,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725123</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1153,6 +1173,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725124</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1260,6 +1285,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725126</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1367,6 +1397,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725127</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1474,6 +1509,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725128</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1581,6 +1621,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725129</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1688,6 +1733,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725130</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1795,6 +1845,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725131</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1902,6 +1957,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725132</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2009,6 +2069,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725133</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2116,6 +2181,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725134</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2223,6 +2293,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725135</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2330,6 +2405,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725136</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2437,6 +2517,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725137</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2544,6 +2629,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725138</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2651,6 +2741,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725139</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2758,6 +2853,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725141</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2865,6 +2965,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725142</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2972,6 +3077,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725144</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3079,6 +3189,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725145</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3191,6 +3306,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725147</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3298,6 +3418,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725149</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3405,6 +3530,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725150</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3512,6 +3642,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725152</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3619,6 +3754,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725153</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3736,6 +3876,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129402385</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3853,6 +3998,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129402404</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3970,6 +4120,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129402526</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4092,6 +4247,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122355540</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4214,6 +4374,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122355933</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4336,6 +4501,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122358929</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4458,6 +4628,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122359011</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4580,6 +4755,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122359691</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4702,6 +4882,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122360218</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4824,6 +5009,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122361005</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4946,6 +5136,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122361037</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5073,6 +5268,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122361274</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5195,6 +5395,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122405719</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5317,6 +5522,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122406150</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5439,6 +5649,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122406373</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5561,6 +5776,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122406516</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5683,6 +5903,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122406983</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5805,6 +6030,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122407975</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5932,6 +6162,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122360161</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6059,6 +6294,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122360599</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6191,6 +6431,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122361119</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6322,6 +6567,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725049</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6449,6 +6699,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122360113</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6576,6 +6831,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122360490</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6706,6 +6966,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724971</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6836,6 +7101,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724972</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6966,6 +7236,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724973</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7093,6 +7368,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122360500</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7230,6 +7510,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122354497</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7367,6 +7652,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122355606</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7504,6 +7794,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122357658</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7641,6 +7936,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122359111</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7778,6 +8078,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122407942</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7915,6 +8220,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122355822</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -8059,6 +8369,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122364212</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8199,6 +8514,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122364318</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8343,6 +8663,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122364537</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8487,6 +8812,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122364729</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8624,6 +8954,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122407432</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8761,6 +9096,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122407671</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8903,6 +9243,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129430383</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -9038,6 +9383,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724952</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -9173,6 +9523,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724953</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -9312,6 +9667,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724954</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9444,6 +9804,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724955</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9567,6 +9932,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725187</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9683,6 +10053,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122355645</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9799,6 +10174,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122357863</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9917,6 +10297,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724963</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -10045,6 +10430,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725219</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -10169,6 +10559,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725220</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -10280,6 +10675,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725224</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -10391,6 +10791,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725225</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -10502,6 +10907,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725090</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -10613,6 +11023,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725091</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10724,6 +11139,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725093</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10835,6 +11255,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725095</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10946,6 +11371,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725096</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -11057,6 +11487,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725098</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -11168,6 +11603,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725100</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -11284,6 +11724,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725101</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -11395,6 +11840,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725102</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -11506,6 +11956,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725104</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -11617,6 +12072,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725105</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11728,6 +12188,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725107</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11839,6 +12304,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725108</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11950,6 +12420,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725109</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -12061,6 +12536,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725110</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -12172,6 +12652,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725111</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -12283,6 +12768,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725112</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -12394,6 +12884,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725113</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -12505,6 +13000,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725114</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -12616,6 +13116,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725115</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -12727,6 +13232,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725116</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12843,6 +13353,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725117</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12954,6 +13469,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725118</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -13065,6 +13585,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725119</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -13181,6 +13706,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725120</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -13292,6 +13822,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725121</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -13403,6 +13938,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725122</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -13514,6 +14054,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725226</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -13625,6 +14170,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725227</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -13744,6 +14294,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725155</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13863,6 +14418,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725156</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13974,6 +14534,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725068</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -14085,6 +14650,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725069</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -14196,6 +14766,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725070</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -14307,6 +14882,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725071</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -14418,6 +14998,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725072</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -14529,6 +15114,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725073</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -14640,6 +15230,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725075</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -14751,6 +15346,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725076</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -14862,6 +15462,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725078</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14973,6 +15578,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725079</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -15084,6 +15694,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725081</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -15195,6 +15810,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725082</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -15306,6 +15926,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725083</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -15417,6 +16042,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725085</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -15528,6 +16158,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725087</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -15639,6 +16274,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725088</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -15750,6 +16390,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725050</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -15861,6 +16506,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725051</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15972,6 +16622,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725052</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -16088,6 +16743,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725053</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -16199,6 +16859,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725054</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -16310,6 +16975,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725055</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -16421,6 +17091,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725056</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -16532,6 +17207,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725057</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -16643,6 +17323,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725058</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -16754,6 +17439,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725059</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -16865,6 +17555,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725060</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -16976,6 +17671,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725061</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -17087,6 +17787,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725063</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -17198,6 +17903,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725064</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -17329,6 +18039,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129402814</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -17453,6 +18168,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725158</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -17577,6 +18297,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725159</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -17701,6 +18426,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725161</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -17825,6 +18555,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725162</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -17949,6 +18684,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725164</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -18073,6 +18813,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725165</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -18197,6 +18942,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725167</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -18321,6 +19071,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725169</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -18445,6 +19200,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725171</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -18569,6 +19329,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725172</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -18693,6 +19458,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725174</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -18817,6 +19587,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725176</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -18941,6 +19716,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725177</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -19065,6 +19845,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725179</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -19189,6 +19974,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725180</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -19313,6 +20103,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725183</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -19437,6 +20232,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725184</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -19548,6 +20348,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724956</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -19659,6 +20464,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724957</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -19770,6 +20580,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724958</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -19881,6 +20696,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724959</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -19992,6 +20812,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724960</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -20103,6 +20928,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724961</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -20214,6 +21044,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724962</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -20338,6 +21173,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724939</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -20454,6 +21294,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724940</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -20570,6 +21415,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724941</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -20686,6 +21536,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724942</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -20805,6 +21660,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724943</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -20924,6 +21784,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724944</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -21035,6 +21900,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724945</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -21146,6 +22016,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724947</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -21262,6 +22137,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724948</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -21386,6 +22266,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724949</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -21510,6 +22395,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724950</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -21621,6 +22511,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724951</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -21733,6 +22628,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725000</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -21840,6 +22740,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725001</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -21951,6 +22856,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724974</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -22062,6 +22972,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724975</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -22173,6 +23088,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724976</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -22284,6 +23204,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724977</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -22395,6 +23320,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724978</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -22506,6 +23436,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724979</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -22617,6 +23552,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724980</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -22728,6 +23668,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724981</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -22839,6 +23784,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724982</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -22950,6 +23900,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724983</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -23061,6 +24016,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724984</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -23172,6 +24132,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724985</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -23283,6 +24248,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724986</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -23394,6 +24364,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724987</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -23505,6 +24480,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724988</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -23616,6 +24596,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724989</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -23727,6 +24712,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724990</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -23838,6 +24828,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724991</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -23949,6 +24944,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724992</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -24060,6 +25060,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724993</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -24171,6 +25176,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724994</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -24290,6 +25300,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724964</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -24407,6 +25422,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129402373</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -24524,6 +25544,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129402502</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -24635,6 +25660,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725228</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -24746,6 +25776,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725229</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -24857,6 +25892,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725230</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -24968,6 +26008,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725231</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -25079,6 +26124,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725232</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -25190,6 +26240,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725233</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -25301,6 +26356,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725234</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -25412,6 +26472,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725235</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -25523,6 +26588,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725237</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -25634,6 +26704,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725238</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -25745,6 +26820,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725239</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -25856,6 +26936,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725240</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -25967,6 +27052,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725241</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -26078,6 +27168,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725242</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -26189,6 +27284,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724965</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -26300,6 +27400,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724967</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -26424,6 +27529,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724970</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -26535,6 +27645,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725065</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -26646,6 +27761,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725066</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -26757,6 +27877,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725067</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -26868,6 +27993,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725222</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -26979,6 +28109,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725223</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -27090,6 +28225,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725190</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -27201,6 +28341,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725192</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -27312,6 +28457,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725002</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -27423,6 +28573,11 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725003</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -27534,6 +28689,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725004</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -27645,6 +28805,11 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725005</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -27756,6 +28921,11 @@
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725006</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -27867,6 +29037,11 @@
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725007</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -27978,6 +29153,11 @@
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725008</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -28089,6 +29269,11 @@
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725009</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -28200,6 +29385,11 @@
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725010</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -28311,6 +29501,11 @@
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725011</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -28422,6 +29617,11 @@
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725012</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -28533,6 +29733,11 @@
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725013</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -28644,6 +29849,11 @@
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725014</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -28755,6 +29965,11 @@
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725015</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -28866,6 +30081,11 @@
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725016</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -28977,6 +30197,11 @@
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725017</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -29088,6 +30313,11 @@
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725018</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -29199,6 +30429,11 @@
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725194</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -29315,6 +30550,11 @@
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725195</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -29426,6 +30666,11 @@
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725197</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -29537,6 +30782,11 @@
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725198</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -29648,6 +30898,11 @@
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725200</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -29759,6 +31014,11 @@
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725201</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -29870,6 +31130,11 @@
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725203</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -29986,6 +31251,11 @@
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725205</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -30102,6 +31372,11 @@
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725206</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -30213,6 +31488,11 @@
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725208</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -30324,6 +31604,11 @@
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725209</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -30435,6 +31720,11 @@
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725211</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -30546,6 +31836,11 @@
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725212</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -30657,6 +31952,11 @@
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725213</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -30768,6 +32068,11 @@
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725019</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -30879,6 +32184,11 @@
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725020</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -30990,6 +32300,11 @@
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725021</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -31101,6 +32416,11 @@
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725022</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -31212,6 +32532,11 @@
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725023</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -31323,6 +32648,11 @@
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725024</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -31439,6 +32769,11 @@
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725025</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -31555,6 +32890,11 @@
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
+      <c r="AZ268" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725026</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -31671,6 +33011,11 @@
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725027</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -31782,6 +33127,11 @@
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725028</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -31893,6 +33243,11 @@
         </is>
       </c>
       <c r="AY271" t="inlineStr"/>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725029</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -32004,6 +33359,11 @@
         </is>
       </c>
       <c r="AY272" t="inlineStr"/>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725030</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -32115,6 +33475,11 @@
         </is>
       </c>
       <c r="AY273" t="inlineStr"/>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725031</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -32231,6 +33596,11 @@
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725032</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -32342,6 +33712,11 @@
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725033</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -32453,6 +33828,11 @@
         </is>
       </c>
       <c r="AY276" t="inlineStr"/>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725034</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -32564,6 +33944,11 @@
         </is>
       </c>
       <c r="AY277" t="inlineStr"/>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725035</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -32675,6 +34060,11 @@
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
+      <c r="AZ278" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725036</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -32791,6 +34181,11 @@
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725037</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -32902,6 +34297,11 @@
         </is>
       </c>
       <c r="AY280" t="inlineStr"/>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725038</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -33013,6 +34413,11 @@
         </is>
       </c>
       <c r="AY281" t="inlineStr"/>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725039</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -33124,6 +34529,11 @@
         </is>
       </c>
       <c r="AY282" t="inlineStr"/>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725040</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -33235,6 +34645,11 @@
         </is>
       </c>
       <c r="AY283" t="inlineStr"/>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725041</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -33346,6 +34761,11 @@
         </is>
       </c>
       <c r="AY284" t="inlineStr"/>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725042</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -33457,8 +34877,299 @@
         </is>
       </c>
       <c r="AY285" t="inlineStr"/>
+      <c r="AZ285" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725043</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ285" r:id="rId284"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 5791-2026 artfynd.xlsx
+++ b/artfynd/A 5791-2026 artfynd.xlsx
@@ -9254,7 +9254,7 @@
         <v>134724952</v>
       </c>
       <c r="B70" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9394,7 +9394,7 @@
         <v>134724953</v>
       </c>
       <c r="B71" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
         <v>134724954</v>
       </c>
       <c r="B72" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         <v>134724955</v>
       </c>
       <c r="B73" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
